--- a/docs/PipeDetailedDimensions.xlsx
+++ b/docs/PipeDetailedDimensions.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\organ\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\organ\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6F97089-06D9-47BB-B8D0-2C42B8EDB583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DE240E3-473D-426A-8CB1-D8E0B3C2D57D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="31920" xr2:uid="{847D2A02-6D2F-45FA-AC97-53CF17BA2C7B}"/>
+    <workbookView xWindow="315" yWindow="2745" windowWidth="55605" windowHeight="23445" xr2:uid="{847D2A02-6D2F-45FA-AC97-53CF17BA2C7B}"/>
   </bookViews>
   <sheets>
     <sheet name="AncientBourdon" sheetId="1" r:id="rId1"/>
@@ -309,7 +309,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -346,8 +346,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -386,6 +393,11 @@
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -450,45 +462,41 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="2"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="2" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="2" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="4"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="2"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="5"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="5" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="5" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="6">
     <cellStyle name="20% - Accent4" xfId="3" builtinId="42"/>
     <cellStyle name="20% - Accent5" xfId="4" builtinId="46"/>
+    <cellStyle name="Bad" xfId="5" builtinId="27"/>
     <cellStyle name="Calculation" xfId="2" builtinId="22"/>
     <cellStyle name="Neutral" xfId="1" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2046,6 +2054,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="691914672"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -4426,70 +4435,83 @@
       <c r="D3" s="2">
         <v>0.88</v>
       </c>
-      <c r="E3" s="21">
+      <c r="E3">
         <v>1.71</v>
       </c>
-      <c r="F3" s="21">
+      <c r="F3">
         <v>2.64</v>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="1">
         <f t="shared" ref="G3:G34" si="0">E3</f>
         <v>1.71</v>
       </c>
-      <c r="H3" s="21">
+      <c r="H3">
         <v>3.42</v>
       </c>
-      <c r="I3" s="23">
+      <c r="I3" s="2">
         <v>3.85</v>
       </c>
       <c r="J3" s="2">
         <v>6</v>
       </c>
-      <c r="K3" s="23">
+      <c r="K3" s="2">
         <v>0.4</v>
       </c>
-      <c r="L3" s="23">
-        <v>1</v>
-      </c>
-      <c r="N3" s="22">
+      <c r="L3" s="2">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="N3" s="1">
         <f>E3</f>
         <v>1.71</v>
       </c>
-      <c r="O3" s="21">
+      <c r="O3">
         <v>2.64</v>
       </c>
       <c r="P3">
         <v>8</v>
       </c>
-      <c r="Q3" s="22">
+      <c r="Q3" s="1">
         <f t="shared" ref="Q3:Q34" si="1">M3</f>
-        <v>0</v>
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="R3" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="S3" s="17">
+        <v>1.5</v>
       </c>
       <c r="T3" s="1">
         <f>AG3</f>
         <v>0.85</v>
       </c>
-      <c r="U3" s="23">
+      <c r="U3" s="2">
         <v>0.44</v>
       </c>
-      <c r="V3" s="23">
+      <c r="V3" s="2">
         <v>2.16</v>
       </c>
-      <c r="W3" s="23">
+      <c r="W3" s="2">
         <v>0.85</v>
       </c>
-      <c r="X3" s="23">
+      <c r="X3" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y3" s="21">
+      <c r="Y3">
         <v>21</v>
       </c>
       <c r="Z3" s="2">
         <v>1.5</v>
       </c>
+      <c r="AA3" s="17">
+        <f>AF3*0.377</f>
+        <v>3.2987500000000001</v>
+      </c>
       <c r="AB3" s="1">
         <f t="shared" ref="AB3:AB35" si="2">AA3</f>
-        <v>0</v>
+        <v>3.2987500000000001</v>
       </c>
       <c r="AC3" s="1">
         <f t="shared" ref="AC3:AC35" si="3">AF3-(AG3*2)</f>
@@ -4525,6 +4547,17 @@
       <c r="AM3" s="2">
         <v>1.62</v>
       </c>
+      <c r="AN3" s="17">
+        <f>AG3*0.8</f>
+        <v>0.68</v>
+      </c>
+      <c r="AO3">
+        <f>AG3*4.18</f>
+        <v>3.5529999999999995</v>
+      </c>
+      <c r="AP3">
+        <v>1</v>
+      </c>
       <c r="AS3">
         <f t="shared" ref="AS3:AS35" si="4">AD3/AF3</f>
         <v>1.1142857142857143</v>
@@ -4536,7 +4569,7 @@
         <f>8*12</f>
         <v>96</v>
       </c>
-      <c r="AW3" s="16"/>
+      <c r="AW3" s="11"/>
       <c r="AY3">
         <f>AF3-(2*AG3)</f>
         <v>7.05</v>
@@ -4549,7 +4582,7 @@
         <f>AY3*AZ3</f>
         <v>56.752500000000005</v>
       </c>
-      <c r="BB3" s="21">
+      <c r="BB3">
         <f>BC3</f>
         <v>8.5</v>
       </c>
@@ -4592,70 +4625,83 @@
       <c r="D4" s="2">
         <v>0.88</v>
       </c>
-      <c r="E4" s="21">
+      <c r="E4">
         <v>1.71</v>
       </c>
-      <c r="F4" s="21">
+      <c r="F4">
         <v>2.64</v>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="1">
         <f t="shared" si="0"/>
         <v>1.71</v>
       </c>
-      <c r="H4" s="21">
+      <c r="H4">
         <v>3.42</v>
       </c>
-      <c r="I4" s="23">
+      <c r="I4" s="2">
         <v>3.85</v>
       </c>
-      <c r="J4" s="23">
+      <c r="J4" s="2">
         <v>6</v>
       </c>
-      <c r="K4" s="23">
+      <c r="K4" s="2">
         <v>0.4</v>
       </c>
-      <c r="L4" s="23">
-        <v>1</v>
-      </c>
-      <c r="N4" s="22">
+      <c r="L4" s="2">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="N4" s="1">
         <f t="shared" ref="N4:N34" si="6">E4</f>
         <v>1.71</v>
       </c>
-      <c r="O4" s="21">
+      <c r="O4">
         <v>2.64</v>
       </c>
       <c r="P4">
         <v>8</v>
       </c>
-      <c r="Q4" s="22">
+      <c r="Q4" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="R4" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="S4" s="17">
+        <v>1.5</v>
       </c>
       <c r="T4" s="1">
-        <f t="shared" ref="T4:T35" si="7">AG4</f>
+        <f t="shared" ref="T4:T34" si="7">AG4</f>
         <v>0.85</v>
       </c>
-      <c r="U4" s="23">
+      <c r="U4" s="2">
         <v>0.44</v>
       </c>
-      <c r="V4" s="23">
+      <c r="V4" s="2">
         <v>2.16</v>
       </c>
-      <c r="W4" s="23">
+      <c r="W4" s="2">
         <v>0.85</v>
       </c>
-      <c r="X4" s="23">
+      <c r="X4" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y4" s="21">
+      <c r="Y4">
         <v>24</v>
       </c>
       <c r="Z4" s="2">
         <v>1.5</v>
       </c>
+      <c r="AA4" s="17">
+        <f t="shared" ref="AA4:AA5" si="8">AF4*0.377</f>
+        <v>3.1102500000000002</v>
+      </c>
       <c r="AB4" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.1102500000000002</v>
       </c>
       <c r="AC4" s="1">
         <f t="shared" si="3"/>
@@ -4691,6 +4737,17 @@
       <c r="AM4" s="2">
         <v>1.62</v>
       </c>
+      <c r="AN4" s="17">
+        <f t="shared" ref="AN4:AN5" si="9">AG4*0.8</f>
+        <v>0.68</v>
+      </c>
+      <c r="AO4">
+        <f t="shared" ref="AO4:AO5" si="10">AG4*4.18</f>
+        <v>3.5529999999999995</v>
+      </c>
+      <c r="AP4">
+        <v>1</v>
+      </c>
       <c r="AS4">
         <f t="shared" si="4"/>
         <v>1.1515151515151516</v>
@@ -4703,46 +4760,46 @@
         <v>90.61</v>
       </c>
       <c r="AY4">
-        <f t="shared" ref="AY4:AY34" si="8">AF4-(2*AG4)</f>
+        <f t="shared" ref="AY4:AY34" si="11">AF4-(2*AG4)</f>
         <v>6.55</v>
       </c>
       <c r="AZ4">
-        <f t="shared" ref="AZ4:AZ34" si="9">AD4-(T4+B4)</f>
+        <f t="shared" ref="AZ4:AZ34" si="12">AD4-(T4+B4)</f>
         <v>7.8</v>
       </c>
       <c r="BA4">
-        <f t="shared" ref="BA4:BA34" si="10">AY4*AZ4</f>
+        <f t="shared" ref="BA4:BA34" si="13">AY4*AZ4</f>
         <v>51.089999999999996</v>
       </c>
-      <c r="BB4" s="21">
-        <f t="shared" ref="BB4:BB34" si="11">ROUND($BC$3*POWER(2,-AT4/BD4),2)</f>
+      <c r="BB4">
+        <f t="shared" ref="BB4:BB34" si="14">ROUND($BC$3*POWER(2,-AT4/BD4),2)</f>
         <v>8.09</v>
       </c>
-      <c r="BC4" s="21">
-        <f t="shared" ref="BC4:BC34" si="12">ROUND(2*SQRT(BA4/3.14157),2)</f>
+      <c r="BC4">
+        <f t="shared" ref="BC4:BC34" si="15">ROUND(2*SQRT(BA4/3.14157),2)</f>
         <v>8.07</v>
       </c>
-      <c r="BD4" s="21">
+      <c r="BD4">
         <v>14</v>
       </c>
-      <c r="BE4" s="21">
-        <f t="shared" ref="BE4:BE34" si="13">ROUND(BC4-BB4,1)</f>
+      <c r="BE4">
+        <f t="shared" ref="BE4:BE34" si="16">ROUND(BC4-BB4,1)</f>
         <v>0</v>
       </c>
-      <c r="BG4" s="21">
-        <f t="shared" ref="BG4:BG34" si="14">Y4+V4</f>
+      <c r="BG4">
+        <f t="shared" ref="BG4:BG34" si="17">Y4+V4</f>
         <v>26.16</v>
       </c>
-      <c r="BH4" s="21">
-        <f t="shared" ref="BH4:BH34" si="15">AE4+(P4-L4)</f>
+      <c r="BH4">
+        <f t="shared" ref="BH4:BH34" si="18">AE4+(P4-L4)</f>
         <v>93.25</v>
       </c>
-      <c r="BI4" s="21">
-        <f t="shared" ref="BI4:BI34" si="16">AE4-BG4</f>
+      <c r="BI4">
+        <f t="shared" ref="BI4:BI34" si="19">AE4-BG4</f>
         <v>60.09</v>
       </c>
-      <c r="BJ4" s="21">
-        <f t="shared" ref="BJ4:BJ34" si="17">BH4-BG4</f>
+      <c r="BJ4">
+        <f t="shared" ref="BJ4:BJ34" si="20">BH4-BG4</f>
         <v>67.09</v>
       </c>
     </row>
@@ -4760,71 +4817,84 @@
       <c r="D5" s="2">
         <v>0.88</v>
       </c>
-      <c r="E5" s="21">
+      <c r="E5">
         <v>1.71</v>
       </c>
-      <c r="F5" s="21">
+      <c r="F5">
         <v>2.64</v>
       </c>
-      <c r="G5" s="22">
+      <c r="G5" s="1">
         <f t="shared" si="0"/>
         <v>1.71</v>
       </c>
-      <c r="H5" s="21">
+      <c r="H5">
         <v>3.42</v>
       </c>
-      <c r="I5" s="23">
+      <c r="I5" s="2">
         <v>3.85</v>
       </c>
-      <c r="J5" s="23">
+      <c r="J5" s="2">
         <v>6</v>
       </c>
-      <c r="K5" s="23">
+      <c r="K5" s="2">
         <v>0.4</v>
       </c>
-      <c r="L5" s="23">
-        <v>1</v>
-      </c>
-      <c r="N5" s="22">
+      <c r="L5" s="2">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="N5" s="1">
         <f t="shared" si="6"/>
         <v>1.71</v>
       </c>
-      <c r="O5" s="21">
+      <c r="O5">
         <v>2.64</v>
       </c>
       <c r="P5">
         <v>8</v>
       </c>
-      <c r="Q5" s="22">
+      <c r="Q5" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="R5" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="S5" s="17">
+        <v>1.5</v>
       </c>
       <c r="T5" s="1">
         <f t="shared" si="7"/>
         <v>0.85</v>
       </c>
-      <c r="U5" s="23">
+      <c r="U5" s="2">
         <v>0.44</v>
       </c>
-      <c r="V5" s="23">
+      <c r="V5" s="2">
         <v>2.16</v>
       </c>
-      <c r="W5" s="23">
+      <c r="W5" s="2">
         <v>0.85</v>
       </c>
-      <c r="X5" s="23">
+      <c r="X5" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y5" s="21">
+      <c r="Y5">
         <f>22+7/8</f>
         <v>22.875</v>
       </c>
       <c r="Z5" s="2">
         <v>1.5</v>
       </c>
+      <c r="AA5" s="17">
+        <f t="shared" si="8"/>
+        <v>3.016</v>
+      </c>
       <c r="AB5" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.016</v>
       </c>
       <c r="AC5" s="1">
         <f t="shared" si="3"/>
@@ -4860,6 +4930,17 @@
       <c r="AM5" s="2">
         <v>1.62</v>
       </c>
+      <c r="AN5" s="17">
+        <f t="shared" si="9"/>
+        <v>0.68</v>
+      </c>
+      <c r="AO5">
+        <f t="shared" si="10"/>
+        <v>3.5529999999999995</v>
+      </c>
+      <c r="AP5">
+        <v>1</v>
+      </c>
       <c r="AS5">
         <f t="shared" si="4"/>
         <v>1.1375</v>
@@ -4868,50 +4949,50 @@
         <v>2</v>
       </c>
       <c r="AU5">
-        <f t="shared" ref="AU5:AU34" si="18">ROUND($AU$3 * POWER(2,-AT5/12),2)</f>
+        <f t="shared" ref="AU5:AU34" si="21">ROUND($AU$3 * POWER(2,-AT5/12),2)</f>
         <v>85.53</v>
       </c>
       <c r="AY5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>6.3</v>
       </c>
       <c r="AZ5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>7.3999999999999995</v>
       </c>
       <c r="BA5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>46.62</v>
       </c>
-      <c r="BB5" s="21">
-        <f t="shared" si="11"/>
+      <c r="BB5">
+        <f t="shared" si="14"/>
         <v>7.7</v>
       </c>
-      <c r="BC5" s="21">
-        <f t="shared" si="12"/>
+      <c r="BC5">
+        <f t="shared" si="15"/>
         <v>7.7</v>
       </c>
-      <c r="BD5" s="21">
+      <c r="BD5">
         <v>14</v>
       </c>
-      <c r="BE5" s="21">
-        <f t="shared" si="13"/>
+      <c r="BE5">
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BG5" s="21">
-        <f t="shared" si="14"/>
+      <c r="BG5">
+        <f t="shared" si="17"/>
         <v>25.035</v>
       </c>
-      <c r="BH5" s="21">
-        <f t="shared" si="15"/>
+      <c r="BH5">
+        <f t="shared" si="18"/>
         <v>88.25</v>
       </c>
-      <c r="BI5" s="21">
-        <f t="shared" si="16"/>
+      <c r="BI5">
+        <f t="shared" si="19"/>
         <v>56.215000000000003</v>
       </c>
-      <c r="BJ5" s="21">
-        <f t="shared" si="17"/>
+      <c r="BJ5">
+        <f t="shared" si="20"/>
         <v>63.215000000000003</v>
       </c>
     </row>
@@ -4935,29 +5016,29 @@
       <c r="F6">
         <v>2.64</v>
       </c>
-      <c r="G6" s="22">
+      <c r="G6" s="1">
         <f>E6</f>
         <v>1.71</v>
       </c>
       <c r="H6">
         <v>3.42</v>
       </c>
-      <c r="I6" s="23">
+      <c r="I6" s="2">
         <v>3.85</v>
       </c>
-      <c r="J6" s="23">
+      <c r="J6" s="2">
         <v>6</v>
       </c>
-      <c r="K6" s="23">
+      <c r="K6" s="2">
         <v>0.4</v>
       </c>
-      <c r="L6" s="23">
+      <c r="L6" s="2">
         <v>1</v>
       </c>
       <c r="M6">
         <v>2.2599999999999998</v>
       </c>
-      <c r="N6" s="22">
+      <c r="N6" s="1">
         <f t="shared" si="6"/>
         <v>1.71</v>
       </c>
@@ -4967,7 +5048,7 @@
       <c r="P6">
         <v>8</v>
       </c>
-      <c r="Q6" s="22">
+      <c r="Q6" s="1">
         <f>M6</f>
         <v>2.2599999999999998</v>
       </c>
@@ -4981,25 +5062,25 @@
         <f t="shared" si="7"/>
         <v>0.85</v>
       </c>
-      <c r="U6" s="23">
+      <c r="U6" s="2">
         <v>0.44</v>
       </c>
-      <c r="V6" s="23">
+      <c r="V6" s="2">
         <v>2.16</v>
       </c>
-      <c r="W6" s="23">
+      <c r="W6" s="2">
         <v>0.85</v>
       </c>
-      <c r="X6" s="23">
+      <c r="X6" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y6" s="21">
+      <c r="Y6">
         <v>32.25</v>
       </c>
       <c r="Z6" s="2">
         <v>1.5</v>
       </c>
-      <c r="AA6">
+      <c r="AA6" s="17">
         <v>2.875</v>
       </c>
       <c r="AB6" s="1">
@@ -5047,6 +5128,9 @@
       <c r="AO6">
         <v>3.55</v>
       </c>
+      <c r="AP6">
+        <v>1</v>
+      </c>
       <c r="AS6">
         <f>AD6/AF6</f>
         <v>1.1475409836065573</v>
@@ -5055,11 +5139,11 @@
         <v>3</v>
       </c>
       <c r="AU6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>80.73</v>
       </c>
       <c r="AV6">
-        <f t="shared" ref="AV4:AV34" si="19">AE6-C6</f>
+        <f t="shared" ref="AV6:AV34" si="22">AE6-C6</f>
         <v>81.875</v>
       </c>
       <c r="AW6">
@@ -5067,46 +5151,46 @@
         <v>1.144999999999996</v>
       </c>
       <c r="AY6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>5.9249999999999998</v>
       </c>
       <c r="AZ6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>7.05</v>
       </c>
       <c r="BA6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>41.771249999999995</v>
       </c>
-      <c r="BB6" s="21">
-        <f t="shared" si="11"/>
+      <c r="BB6">
+        <f t="shared" si="14"/>
         <v>7.24</v>
       </c>
-      <c r="BC6" s="21">
-        <f t="shared" si="12"/>
+      <c r="BC6">
+        <f t="shared" si="15"/>
         <v>7.29</v>
       </c>
-      <c r="BD6" s="21">
+      <c r="BD6">
         <v>13</v>
       </c>
-      <c r="BE6" s="21">
-        <f t="shared" si="13"/>
+      <c r="BE6">
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BG6" s="21">
-        <f t="shared" si="14"/>
+      <c r="BG6">
+        <f t="shared" si="17"/>
         <v>34.409999999999997</v>
       </c>
-      <c r="BH6" s="21">
-        <f t="shared" si="15"/>
+      <c r="BH6">
+        <f t="shared" si="18"/>
         <v>93.75</v>
       </c>
-      <c r="BI6" s="21">
-        <f t="shared" si="16"/>
+      <c r="BI6">
+        <f t="shared" si="19"/>
         <v>52.34</v>
       </c>
-      <c r="BJ6" s="21">
-        <f t="shared" si="17"/>
+      <c r="BJ6">
+        <f t="shared" si="20"/>
         <v>59.34</v>
       </c>
     </row>
@@ -5124,55 +5208,88 @@
       <c r="D7" s="2">
         <v>0.88</v>
       </c>
-      <c r="G7" s="22">
+      <c r="E7" s="17">
+        <f>AF7*0.224</f>
+        <v>1.68</v>
+      </c>
+      <c r="F7" s="17">
+        <f>E7+0.6</f>
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="G7" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I7" s="23">
+        <v>1.68</v>
+      </c>
+      <c r="H7" s="17">
+        <f>(P7-1)/2</f>
+        <v>3</v>
+      </c>
+      <c r="I7" s="2">
         <v>3.85</v>
       </c>
-      <c r="J7" s="23">
+      <c r="J7" s="2">
         <v>6</v>
       </c>
-      <c r="K7" s="23">
+      <c r="K7" s="2">
         <v>0.4</v>
       </c>
-      <c r="L7" s="23">
-        <v>1</v>
-      </c>
-      <c r="N7" s="22">
+      <c r="L7" s="2">
+        <v>1</v>
+      </c>
+      <c r="M7" s="17">
+        <f>O7-0.4</f>
+        <v>2.08</v>
+      </c>
+      <c r="N7" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q7" s="22">
+        <v>1.68</v>
+      </c>
+      <c r="O7" s="17">
+        <f>E7+0.8</f>
+        <v>2.48</v>
+      </c>
+      <c r="P7">
+        <v>7</v>
+      </c>
+      <c r="Q7" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.08</v>
+      </c>
+      <c r="R7" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="S7" s="20">
+        <v>1.5</v>
       </c>
       <c r="T7" s="1">
         <f t="shared" si="7"/>
         <v>0.85</v>
       </c>
-      <c r="U7" s="23">
+      <c r="U7" s="2">
         <v>0.44</v>
       </c>
-      <c r="V7" s="23">
+      <c r="V7" s="2">
         <v>2.16</v>
       </c>
-      <c r="W7" s="23">
+      <c r="W7" s="2">
         <v>0.85</v>
       </c>
-      <c r="X7" s="23">
+      <c r="X7" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y7" s="21">
+      <c r="Y7">
         <v>31.25</v>
       </c>
       <c r="Z7" s="2">
         <v>1.5</v>
       </c>
+      <c r="AA7" s="17">
+        <f>AF7*0.377</f>
+        <v>2.8275000000000001</v>
+      </c>
       <c r="AB7" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.8275000000000001</v>
       </c>
       <c r="AC7" s="1">
         <f t="shared" si="3"/>
@@ -5209,6 +5326,17 @@
       <c r="AM7" s="2">
         <v>1.62</v>
       </c>
+      <c r="AN7" s="17">
+        <f>AG7*0.8</f>
+        <v>0.68</v>
+      </c>
+      <c r="AO7">
+        <f>AG7*4.18</f>
+        <v>3.5529999999999995</v>
+      </c>
+      <c r="AP7">
+        <v>1</v>
+      </c>
       <c r="AS7">
         <f t="shared" si="4"/>
         <v>1.1166666666666667</v>
@@ -5217,59 +5345,59 @@
         <v>4</v>
       </c>
       <c r="AU7">
+        <f t="shared" si="21"/>
+        <v>76.2</v>
+      </c>
+      <c r="AV7">
+        <f t="shared" si="22"/>
+        <v>79.125</v>
+      </c>
+      <c r="AW7">
+        <f t="shared" ref="AW7:AW34" si="23">AV7-AU7</f>
+        <v>2.9249999999999972</v>
+      </c>
+      <c r="AY7">
+        <f t="shared" si="11"/>
+        <v>5.8</v>
+      </c>
+      <c r="AZ7">
+        <f t="shared" si="12"/>
+        <v>6.6749999999999998</v>
+      </c>
+      <c r="BA7">
+        <f t="shared" si="13"/>
+        <v>38.714999999999996</v>
+      </c>
+      <c r="BB7">
+        <f t="shared" si="14"/>
+        <v>7.02</v>
+      </c>
+      <c r="BC7">
+        <f t="shared" si="15"/>
+        <v>7.02</v>
+      </c>
+      <c r="BD7">
+        <v>14.5</v>
+      </c>
+      <c r="BE7">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="BG7">
+        <f t="shared" si="17"/>
+        <v>33.409999999999997</v>
+      </c>
+      <c r="BH7">
         <f t="shared" si="18"/>
-        <v>76.2</v>
-      </c>
-      <c r="AV7">
+        <v>90</v>
+      </c>
+      <c r="BI7">
         <f t="shared" si="19"/>
-        <v>79.125</v>
-      </c>
-      <c r="AW7">
-        <f t="shared" ref="AW7:AW34" si="20">AV7-AU7</f>
-        <v>2.9249999999999972</v>
-      </c>
-      <c r="AY7">
-        <f t="shared" si="8"/>
-        <v>5.8</v>
-      </c>
-      <c r="AZ7">
-        <f t="shared" si="9"/>
-        <v>6.6749999999999998</v>
-      </c>
-      <c r="BA7">
-        <f t="shared" si="10"/>
-        <v>38.714999999999996</v>
-      </c>
-      <c r="BB7" s="21">
-        <f t="shared" si="11"/>
-        <v>7.02</v>
-      </c>
-      <c r="BC7" s="21">
-        <f t="shared" si="12"/>
-        <v>7.02</v>
-      </c>
-      <c r="BD7" s="21">
-        <v>14.5</v>
-      </c>
-      <c r="BE7" s="21">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="BG7" s="21">
-        <f t="shared" si="14"/>
-        <v>33.409999999999997</v>
-      </c>
-      <c r="BH7" s="21">
-        <f t="shared" si="15"/>
-        <v>83</v>
-      </c>
-      <c r="BI7" s="21">
-        <f t="shared" si="16"/>
         <v>50.59</v>
       </c>
-      <c r="BJ7" s="21">
-        <f t="shared" si="17"/>
-        <v>49.59</v>
+      <c r="BJ7">
+        <f t="shared" si="20"/>
+        <v>56.59</v>
       </c>
     </row>
     <row r="8" spans="1:62" x14ac:dyDescent="0.25">
@@ -5286,55 +5414,88 @@
       <c r="D8" s="2">
         <v>0.88</v>
       </c>
-      <c r="G8" s="22">
+      <c r="E8" s="17">
+        <f t="shared" ref="E8:E34" si="24">AF8*0.224</f>
+        <v>1.5960000000000001</v>
+      </c>
+      <c r="F8" s="17">
+        <f t="shared" ref="F8:F24" si="25">E8+0.6</f>
+        <v>2.1960000000000002</v>
+      </c>
+      <c r="G8" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I8" s="23">
+        <v>1.5960000000000001</v>
+      </c>
+      <c r="H8" s="17">
+        <f t="shared" ref="H8:H34" si="26">(P8-1)/2</f>
+        <v>8.875</v>
+      </c>
+      <c r="I8" s="2">
         <v>3.85</v>
       </c>
-      <c r="J8" s="23">
+      <c r="J8" s="2">
         <v>6</v>
       </c>
-      <c r="K8" s="23">
+      <c r="K8" s="2">
         <v>0.4</v>
       </c>
-      <c r="L8" s="23">
-        <v>1</v>
-      </c>
-      <c r="N8" s="22">
+      <c r="L8" s="2">
+        <v>1</v>
+      </c>
+      <c r="M8" s="17">
+        <f t="shared" ref="M8:M24" si="27">O8-0.4</f>
+        <v>1.996</v>
+      </c>
+      <c r="N8" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q8" s="22">
+        <v>1.5960000000000001</v>
+      </c>
+      <c r="O8" s="17">
+        <f t="shared" ref="O8:O24" si="28">E8+0.8</f>
+        <v>2.3959999999999999</v>
+      </c>
+      <c r="P8">
+        <v>18.75</v>
+      </c>
+      <c r="Q8" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.996</v>
+      </c>
+      <c r="R8" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="S8" s="20">
+        <v>1.5</v>
       </c>
       <c r="T8" s="1">
         <f t="shared" si="7"/>
         <v>0.85</v>
       </c>
-      <c r="U8" s="23">
+      <c r="U8" s="2">
         <v>0.44</v>
       </c>
-      <c r="V8" s="23">
+      <c r="V8" s="2">
         <v>2.16</v>
       </c>
-      <c r="W8" s="23">
+      <c r="W8" s="2">
         <v>0.85</v>
       </c>
-      <c r="X8" s="23">
+      <c r="X8" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y8" s="19">
+      <c r="Y8" s="14">
         <v>10.5</v>
       </c>
       <c r="Z8" s="2">
         <v>1.5</v>
       </c>
+      <c r="AA8" s="17">
+        <f t="shared" ref="AA8:AA24" si="29">AF8*0.377</f>
+        <v>2.6861250000000001</v>
+      </c>
       <c r="AB8" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.6861250000000001</v>
       </c>
       <c r="AC8" s="1">
         <f t="shared" si="3"/>
@@ -5371,6 +5532,17 @@
       <c r="AM8" s="2">
         <v>1.62</v>
       </c>
+      <c r="AN8" s="17">
+        <f t="shared" ref="AN8:AN24" si="30">AG8*0.8</f>
+        <v>0.68</v>
+      </c>
+      <c r="AO8">
+        <f t="shared" ref="AO8:AO24" si="31">AG8*4.18</f>
+        <v>3.5529999999999995</v>
+      </c>
+      <c r="AP8">
+        <v>1</v>
+      </c>
       <c r="AS8">
         <f t="shared" si="4"/>
         <v>1.1403508771929824</v>
@@ -5379,221 +5551,269 @@
         <v>5</v>
       </c>
       <c r="AU8">
+        <f t="shared" si="21"/>
+        <v>71.92</v>
+      </c>
+      <c r="AV8">
+        <f t="shared" si="22"/>
+        <v>74.625</v>
+      </c>
+      <c r="AW8">
+        <f t="shared" si="23"/>
+        <v>2.7049999999999983</v>
+      </c>
+      <c r="AY8">
+        <f t="shared" si="11"/>
+        <v>5.4249999999999998</v>
+      </c>
+      <c r="AZ8">
+        <f t="shared" si="12"/>
+        <v>6.4249999999999998</v>
+      </c>
+      <c r="BA8">
+        <f t="shared" si="13"/>
+        <v>34.855624999999996</v>
+      </c>
+      <c r="BB8">
+        <f t="shared" si="14"/>
+        <v>6.67</v>
+      </c>
+      <c r="BC8">
+        <f t="shared" si="15"/>
+        <v>6.66</v>
+      </c>
+      <c r="BD8">
+        <v>14.3</v>
+      </c>
+      <c r="BE8">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="BG8">
+        <f t="shared" si="17"/>
+        <v>12.66</v>
+      </c>
+      <c r="BH8">
         <f t="shared" si="18"/>
-        <v>71.92</v>
-      </c>
-      <c r="AV8">
+        <v>97.25</v>
+      </c>
+      <c r="BI8">
         <f t="shared" si="19"/>
-        <v>74.625</v>
-      </c>
-      <c r="AW8">
+        <v>66.84</v>
+      </c>
+      <c r="BJ8">
         <f t="shared" si="20"/>
-        <v>2.7049999999999983</v>
-      </c>
-      <c r="AY8">
-        <f t="shared" si="8"/>
-        <v>5.4249999999999998</v>
-      </c>
-      <c r="AZ8">
-        <f t="shared" si="9"/>
-        <v>6.4249999999999998</v>
-      </c>
-      <c r="BA8">
-        <f t="shared" si="10"/>
-        <v>34.855624999999996</v>
-      </c>
-      <c r="BB8" s="21">
-        <f t="shared" si="11"/>
-        <v>6.67</v>
-      </c>
-      <c r="BC8" s="21">
-        <f t="shared" si="12"/>
-        <v>6.66</v>
-      </c>
-      <c r="BD8" s="21">
-        <v>14.3</v>
-      </c>
-      <c r="BE8" s="21">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="BG8" s="21">
-        <f t="shared" si="14"/>
-        <v>12.66</v>
-      </c>
-      <c r="BH8" s="21">
-        <f t="shared" si="15"/>
-        <v>78.5</v>
-      </c>
-      <c r="BI8" s="21">
-        <f t="shared" si="16"/>
-        <v>66.84</v>
-      </c>
-      <c r="BJ8" s="21">
-        <f t="shared" si="17"/>
-        <v>65.84</v>
+        <v>84.59</v>
       </c>
     </row>
-    <row r="9" spans="1:62" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+    <row r="9" spans="1:62" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="8">
         <f t="shared" si="5"/>
         <v>0.85</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="7">
         <v>4.875</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="9">
         <v>0.88</v>
       </c>
-      <c r="G9" s="22">
+      <c r="E9" s="17">
+        <f t="shared" si="24"/>
+        <v>1.526</v>
+      </c>
+      <c r="F9" s="17">
+        <f t="shared" si="25"/>
+        <v>2.1259999999999999</v>
+      </c>
+      <c r="G9" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I9" s="23">
+        <v>1.526</v>
+      </c>
+      <c r="H9" s="17">
+        <f t="shared" si="26"/>
+        <v>3</v>
+      </c>
+      <c r="I9" s="2">
         <v>3.85</v>
       </c>
-      <c r="J9" s="23">
+      <c r="J9" s="2">
         <v>6</v>
       </c>
-      <c r="K9" s="23">
+      <c r="K9" s="2">
         <v>0.4</v>
       </c>
-      <c r="L9" s="23">
-        <v>1</v>
-      </c>
-      <c r="N9" s="22">
+      <c r="L9" s="2">
+        <v>1</v>
+      </c>
+      <c r="M9" s="17">
+        <f t="shared" si="27"/>
+        <v>1.9260000000000002</v>
+      </c>
+      <c r="N9" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q9" s="22">
+        <v>1.526</v>
+      </c>
+      <c r="O9" s="17">
+        <f t="shared" si="28"/>
+        <v>2.3260000000000001</v>
+      </c>
+      <c r="P9" s="7">
+        <v>7</v>
+      </c>
+      <c r="Q9" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T9" s="11">
+        <v>1.9260000000000002</v>
+      </c>
+      <c r="R9" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="S9" s="20">
+        <v>1.5</v>
+      </c>
+      <c r="T9" s="8">
         <f t="shared" si="7"/>
         <v>0.85</v>
       </c>
-      <c r="U9" s="23">
+      <c r="U9" s="2">
         <v>0.44</v>
       </c>
-      <c r="V9" s="23">
+      <c r="V9" s="2">
         <v>2.16</v>
       </c>
-      <c r="W9" s="23">
+      <c r="W9" s="2">
         <v>0.85</v>
       </c>
-      <c r="X9" s="23">
+      <c r="X9" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y9" s="20"/>
-      <c r="Z9" s="12">
+      <c r="Y9" s="17">
+        <v>26</v>
+      </c>
+      <c r="Z9" s="9">
         <v>1.5</v>
       </c>
-      <c r="AB9" s="11">
+      <c r="AA9">
+        <f t="shared" si="29"/>
+        <v>2.5683125000000002</v>
+      </c>
+      <c r="AB9" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC9" s="11">
+        <v>2.5683125000000002</v>
+      </c>
+      <c r="AC9" s="8">
         <f t="shared" si="3"/>
         <v>5.1124999999999998</v>
       </c>
-      <c r="AD9" s="17">
+      <c r="AD9" s="12">
         <f>AD10+(AD8-AD10)/2</f>
         <v>7.75</v>
       </c>
-      <c r="AE9" s="17">
+      <c r="AE9" s="12">
         <f>AE10+(AE8-AE10)/2</f>
         <v>75.1875</v>
       </c>
-      <c r="AF9" s="17">
+      <c r="AF9" s="12">
         <f>AF10+(AF8-AF10)/2</f>
         <v>6.8125</v>
       </c>
-      <c r="AG9" s="12">
+      <c r="AG9" s="9">
         <v>0.85</v>
       </c>
-      <c r="AH9" s="12">
+      <c r="AH9" s="9">
         <v>1.75</v>
       </c>
-      <c r="AI9" s="12">
+      <c r="AI9" s="9">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AJ9" s="12">
+      <c r="AJ9" s="9">
         <v>4.7</v>
       </c>
-      <c r="AK9" s="12">
-        <v>1</v>
-      </c>
-      <c r="AL9" s="12">
+      <c r="AK9" s="9">
+        <v>1</v>
+      </c>
+      <c r="AL9" s="9">
         <v>0.1</v>
       </c>
-      <c r="AM9" s="12">
+      <c r="AM9" s="9">
         <v>1.62</v>
       </c>
-      <c r="AS9" s="10">
+      <c r="AN9" s="17">
+        <f t="shared" si="30"/>
+        <v>0.68</v>
+      </c>
+      <c r="AO9">
+        <f t="shared" si="31"/>
+        <v>3.5529999999999995</v>
+      </c>
+      <c r="AP9">
+        <v>1</v>
+      </c>
+      <c r="AQ9"/>
+      <c r="AR9"/>
+      <c r="AS9" s="7">
         <f t="shared" si="4"/>
         <v>1.1376146788990826</v>
       </c>
-      <c r="AT9" s="10">
+      <c r="AT9" s="7">
         <v>6</v>
       </c>
-      <c r="AU9" s="10">
+      <c r="AU9" s="7">
+        <f t="shared" si="21"/>
+        <v>67.88</v>
+      </c>
+      <c r="AV9" s="13">
+        <f t="shared" si="22"/>
+        <v>70.3125</v>
+      </c>
+      <c r="AW9" s="7">
+        <f t="shared" si="23"/>
+        <v>2.4325000000000045</v>
+      </c>
+      <c r="AY9">
+        <f t="shared" si="11"/>
+        <v>5.1124999999999998</v>
+      </c>
+      <c r="AZ9">
+        <f t="shared" si="12"/>
+        <v>6.05</v>
+      </c>
+      <c r="BA9">
+        <f t="shared" si="13"/>
+        <v>30.930624999999999</v>
+      </c>
+      <c r="BB9">
+        <f t="shared" si="14"/>
+        <v>6.27</v>
+      </c>
+      <c r="BC9">
+        <f t="shared" si="15"/>
+        <v>6.28</v>
+      </c>
+      <c r="BD9">
+        <v>13.7</v>
+      </c>
+      <c r="BE9">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="BG9">
+        <f t="shared" si="17"/>
+        <v>28.16</v>
+      </c>
+      <c r="BH9">
         <f t="shared" si="18"/>
-        <v>67.88</v>
-      </c>
-      <c r="AV9" s="18">
+        <v>81.1875</v>
+      </c>
+      <c r="BI9">
         <f t="shared" si="19"/>
-        <v>70.3125</v>
-      </c>
-      <c r="AW9" s="25">
+        <v>47.027500000000003</v>
+      </c>
+      <c r="BJ9">
         <f t="shared" si="20"/>
-        <v>2.4325000000000045</v>
-      </c>
-      <c r="AY9">
-        <f t="shared" si="8"/>
-        <v>5.1124999999999998</v>
-      </c>
-      <c r="AZ9">
-        <f t="shared" si="9"/>
-        <v>6.05</v>
-      </c>
-      <c r="BA9">
-        <f t="shared" si="10"/>
-        <v>30.930624999999999</v>
-      </c>
-      <c r="BB9" s="21">
-        <f t="shared" si="11"/>
-        <v>6.27</v>
-      </c>
-      <c r="BC9" s="21">
-        <f t="shared" si="12"/>
-        <v>6.28</v>
-      </c>
-      <c r="BD9" s="21">
-        <v>13.7</v>
-      </c>
-      <c r="BE9" s="21">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="BG9" s="21">
-        <f t="shared" si="14"/>
-        <v>2.16</v>
-      </c>
-      <c r="BH9" s="21">
-        <f t="shared" si="15"/>
-        <v>74.1875</v>
-      </c>
-      <c r="BI9" s="21">
-        <f t="shared" si="16"/>
-        <v>73.027500000000003</v>
-      </c>
-      <c r="BJ9" s="21">
-        <f t="shared" si="17"/>
-        <v>72.027500000000003</v>
+        <v>53.027500000000003</v>
       </c>
     </row>
     <row r="10" spans="1:62" x14ac:dyDescent="0.25">
@@ -5610,55 +5830,88 @@
       <c r="D10" s="2">
         <v>0.75</v>
       </c>
-      <c r="G10" s="22">
+      <c r="E10" s="17">
+        <f t="shared" si="24"/>
+        <v>1.456</v>
+      </c>
+      <c r="F10" s="17">
+        <f t="shared" si="25"/>
+        <v>2.056</v>
+      </c>
+      <c r="G10" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I10" s="23">
+        <v>1.456</v>
+      </c>
+      <c r="H10" s="17">
+        <f t="shared" si="26"/>
+        <v>8.875</v>
+      </c>
+      <c r="I10" s="2">
         <v>3.85</v>
       </c>
-      <c r="J10" s="23">
+      <c r="J10" s="2">
         <v>6</v>
       </c>
-      <c r="K10" s="23">
+      <c r="K10" s="2">
         <v>0.4</v>
       </c>
-      <c r="L10" s="23">
-        <v>1</v>
-      </c>
-      <c r="N10" s="22">
+      <c r="L10" s="2">
+        <v>1</v>
+      </c>
+      <c r="M10" s="17">
+        <f t="shared" si="27"/>
+        <v>1.8560000000000003</v>
+      </c>
+      <c r="N10" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q10" s="22">
+        <v>1.456</v>
+      </c>
+      <c r="O10" s="17">
+        <f t="shared" si="28"/>
+        <v>2.2560000000000002</v>
+      </c>
+      <c r="P10">
+        <v>18.75</v>
+      </c>
+      <c r="Q10" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.8560000000000003</v>
+      </c>
+      <c r="R10" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="S10" s="20">
+        <v>1.5</v>
       </c>
       <c r="T10" s="1">
         <f t="shared" si="7"/>
         <v>0.75</v>
       </c>
-      <c r="U10" s="23">
+      <c r="U10" s="2">
         <v>0.44</v>
       </c>
-      <c r="V10" s="23">
+      <c r="V10" s="2">
         <v>2.16</v>
       </c>
-      <c r="W10" s="23">
+      <c r="W10" s="2">
         <v>0.85</v>
       </c>
-      <c r="X10" s="23">
+      <c r="X10" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y10" s="19">
+      <c r="Y10" s="14">
         <v>7.25</v>
       </c>
       <c r="Z10" s="2">
         <v>1.5</v>
       </c>
+      <c r="AA10" s="17">
+        <f t="shared" si="29"/>
+        <v>2.4504999999999999</v>
+      </c>
       <c r="AB10" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.4504999999999999</v>
       </c>
       <c r="AC10" s="1">
         <f t="shared" si="3"/>
@@ -5696,6 +5949,17 @@
       <c r="AM10" s="2">
         <v>1</v>
       </c>
+      <c r="AN10" s="17">
+        <f t="shared" si="30"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="AO10">
+        <f t="shared" si="31"/>
+        <v>3.1349999999999998</v>
+      </c>
+      <c r="AP10">
+        <v>1</v>
+      </c>
       <c r="AS10">
         <f t="shared" si="4"/>
         <v>1.1346153846153846</v>
@@ -5704,59 +5968,59 @@
         <v>7</v>
       </c>
       <c r="AU10">
+        <f t="shared" si="21"/>
+        <v>64.069999999999993</v>
+      </c>
+      <c r="AV10">
+        <f t="shared" si="22"/>
+        <v>66</v>
+      </c>
+      <c r="AW10">
+        <f t="shared" si="23"/>
+        <v>1.9300000000000068</v>
+      </c>
+      <c r="AY10">
+        <f t="shared" si="11"/>
+        <v>5</v>
+      </c>
+      <c r="AZ10">
+        <f t="shared" si="12"/>
+        <v>5.875</v>
+      </c>
+      <c r="BA10">
+        <f t="shared" si="13"/>
+        <v>29.375</v>
+      </c>
+      <c r="BB10">
+        <f t="shared" si="14"/>
+        <v>6.15</v>
+      </c>
+      <c r="BC10">
+        <f t="shared" si="15"/>
+        <v>6.12</v>
+      </c>
+      <c r="BD10">
+        <v>15</v>
+      </c>
+      <c r="BE10">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="BG10">
+        <f t="shared" si="17"/>
+        <v>9.41</v>
+      </c>
+      <c r="BH10">
         <f t="shared" si="18"/>
-        <v>64.069999999999993</v>
-      </c>
-      <c r="AV10">
+        <v>88.625</v>
+      </c>
+      <c r="BI10">
         <f t="shared" si="19"/>
-        <v>66</v>
-      </c>
-      <c r="AW10" s="21">
+        <v>61.465000000000003</v>
+      </c>
+      <c r="BJ10">
         <f t="shared" si="20"/>
-        <v>1.9300000000000068</v>
-      </c>
-      <c r="AY10">
-        <f t="shared" si="8"/>
-        <v>5</v>
-      </c>
-      <c r="AZ10">
-        <f t="shared" si="9"/>
-        <v>5.875</v>
-      </c>
-      <c r="BA10">
-        <f t="shared" si="10"/>
-        <v>29.375</v>
-      </c>
-      <c r="BB10" s="21">
-        <f t="shared" si="11"/>
-        <v>6.15</v>
-      </c>
-      <c r="BC10" s="21">
-        <f t="shared" si="12"/>
-        <v>6.12</v>
-      </c>
-      <c r="BD10" s="21">
-        <v>15</v>
-      </c>
-      <c r="BE10" s="21">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="BG10" s="21">
-        <f t="shared" si="14"/>
-        <v>9.41</v>
-      </c>
-      <c r="BH10" s="21">
-        <f t="shared" si="15"/>
-        <v>69.875</v>
-      </c>
-      <c r="BI10" s="21">
-        <f t="shared" si="16"/>
-        <v>61.465000000000003</v>
-      </c>
-      <c r="BJ10" s="21">
-        <f t="shared" si="17"/>
-        <v>60.465000000000003</v>
+        <v>79.215000000000003</v>
       </c>
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.25">
@@ -5773,55 +6037,88 @@
       <c r="D11" s="2">
         <v>0.75</v>
       </c>
-      <c r="G11" s="22">
+      <c r="E11" s="17">
+        <f t="shared" si="24"/>
+        <v>1.4000000000000001</v>
+      </c>
+      <c r="F11" s="17">
+        <f t="shared" si="25"/>
+        <v>2</v>
+      </c>
+      <c r="G11" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I11" s="23">
+        <v>1.4000000000000001</v>
+      </c>
+      <c r="H11" s="17">
+        <f t="shared" si="26"/>
+        <v>3</v>
+      </c>
+      <c r="I11" s="2">
         <v>3.85</v>
       </c>
-      <c r="J11" s="23">
+      <c r="J11" s="2">
         <v>6</v>
       </c>
-      <c r="K11" s="23">
+      <c r="K11" s="2">
         <v>0.4</v>
       </c>
-      <c r="L11" s="23">
-        <v>1</v>
-      </c>
-      <c r="N11" s="22">
+      <c r="L11" s="2">
+        <v>1</v>
+      </c>
+      <c r="M11" s="17">
+        <f t="shared" si="27"/>
+        <v>1.8000000000000003</v>
+      </c>
+      <c r="N11" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q11" s="22">
+        <v>1.4000000000000001</v>
+      </c>
+      <c r="O11" s="17">
+        <f t="shared" si="28"/>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="P11">
+        <v>7</v>
+      </c>
+      <c r="Q11" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.8000000000000003</v>
+      </c>
+      <c r="R11" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="S11" s="20">
+        <v>1.5</v>
       </c>
       <c r="T11" s="1">
         <f t="shared" si="7"/>
         <v>0.75</v>
       </c>
-      <c r="U11" s="23">
+      <c r="U11" s="2">
         <v>0.44</v>
       </c>
-      <c r="V11" s="23">
+      <c r="V11" s="2">
         <v>2.16</v>
       </c>
-      <c r="W11" s="23">
+      <c r="W11" s="2">
         <v>0.85</v>
       </c>
-      <c r="X11" s="23">
+      <c r="X11" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y11" s="20">
+      <c r="Y11" s="15">
         <v>21.25</v>
       </c>
       <c r="Z11" s="2">
         <v>1.5</v>
       </c>
+      <c r="AA11" s="17">
+        <f t="shared" si="29"/>
+        <v>2.3562500000000002</v>
+      </c>
       <c r="AB11" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.3562500000000002</v>
       </c>
       <c r="AC11" s="1">
         <f t="shared" si="3"/>
@@ -5859,6 +6156,17 @@
       <c r="AM11" s="2">
         <v>1</v>
       </c>
+      <c r="AN11" s="17">
+        <f t="shared" si="30"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="AO11">
+        <f t="shared" si="31"/>
+        <v>3.1349999999999998</v>
+      </c>
+      <c r="AP11">
+        <v>1</v>
+      </c>
       <c r="AS11">
         <f t="shared" si="4"/>
         <v>1.1399999999999999</v>
@@ -5867,60 +6175,60 @@
         <v>8</v>
       </c>
       <c r="AU11">
+        <f t="shared" si="21"/>
+        <v>60.48</v>
+      </c>
+      <c r="AV11">
+        <f t="shared" si="22"/>
+        <v>62.375</v>
+      </c>
+      <c r="AW11">
+        <f t="shared" si="23"/>
+        <v>1.8950000000000031</v>
+      </c>
+      <c r="AY11">
+        <f t="shared" si="11"/>
+        <v>4.75</v>
+      </c>
+      <c r="AZ11">
+        <f t="shared" si="12"/>
+        <v>5.625</v>
+      </c>
+      <c r="BA11">
+        <f t="shared" si="13"/>
+        <v>26.71875</v>
+      </c>
+      <c r="BB11">
+        <f t="shared" si="14"/>
+        <v>5.87</v>
+      </c>
+      <c r="BC11">
+        <f t="shared" si="15"/>
+        <v>5.83</v>
+      </c>
+      <c r="BD11">
+        <f t="shared" ref="BD11:BD34" si="32">BD10</f>
+        <v>15</v>
+      </c>
+      <c r="BE11">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="BG11">
+        <f t="shared" si="17"/>
+        <v>23.41</v>
+      </c>
+      <c r="BH11">
         <f t="shared" si="18"/>
-        <v>60.48</v>
-      </c>
-      <c r="AV11">
+        <v>73.25</v>
+      </c>
+      <c r="BI11">
         <f t="shared" si="19"/>
-        <v>62.375</v>
-      </c>
-      <c r="AW11" s="21">
+        <v>43.84</v>
+      </c>
+      <c r="BJ11">
         <f t="shared" si="20"/>
-        <v>1.8950000000000031</v>
-      </c>
-      <c r="AY11">
-        <f t="shared" si="8"/>
-        <v>4.75</v>
-      </c>
-      <c r="AZ11">
-        <f t="shared" si="9"/>
-        <v>5.625</v>
-      </c>
-      <c r="BA11">
-        <f t="shared" si="10"/>
-        <v>26.71875</v>
-      </c>
-      <c r="BB11" s="21">
-        <f t="shared" si="11"/>
-        <v>5.87</v>
-      </c>
-      <c r="BC11" s="21">
-        <f t="shared" si="12"/>
-        <v>5.83</v>
-      </c>
-      <c r="BD11" s="21">
-        <f t="shared" ref="BD11:BD34" si="21">BD10</f>
-        <v>15</v>
-      </c>
-      <c r="BE11" s="21">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="BG11" s="21">
-        <f t="shared" si="14"/>
-        <v>23.41</v>
-      </c>
-      <c r="BH11" s="21">
-        <f t="shared" si="15"/>
-        <v>66.25</v>
-      </c>
-      <c r="BI11" s="21">
-        <f t="shared" si="16"/>
-        <v>43.84</v>
-      </c>
-      <c r="BJ11" s="21">
-        <f t="shared" si="17"/>
-        <v>42.84</v>
+        <v>49.84</v>
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.25">
@@ -5937,55 +6245,88 @@
       <c r="D12" s="2">
         <v>0.75</v>
       </c>
-      <c r="G12" s="22">
+      <c r="E12" s="17">
+        <f t="shared" si="24"/>
+        <v>1.3160000000000001</v>
+      </c>
+      <c r="F12" s="17">
+        <f t="shared" si="25"/>
+        <v>1.9159999999999999</v>
+      </c>
+      <c r="G12" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I12" s="23">
+        <v>1.3160000000000001</v>
+      </c>
+      <c r="H12" s="17">
+        <f t="shared" si="26"/>
+        <v>8.875</v>
+      </c>
+      <c r="I12" s="2">
         <v>3.85</v>
       </c>
-      <c r="J12" s="23">
+      <c r="J12" s="2">
         <v>6</v>
       </c>
-      <c r="K12" s="23">
+      <c r="K12" s="2">
         <v>0.4</v>
       </c>
-      <c r="L12" s="23">
-        <v>1</v>
-      </c>
-      <c r="N12" s="22">
+      <c r="L12" s="2">
+        <v>1</v>
+      </c>
+      <c r="M12" s="17">
+        <f t="shared" si="27"/>
+        <v>1.7160000000000002</v>
+      </c>
+      <c r="N12" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q12" s="22">
+        <v>1.3160000000000001</v>
+      </c>
+      <c r="O12" s="17">
+        <f t="shared" si="28"/>
+        <v>2.1160000000000001</v>
+      </c>
+      <c r="P12">
+        <v>18.75</v>
+      </c>
+      <c r="Q12" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.7160000000000002</v>
+      </c>
+      <c r="R12" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="S12" s="20">
+        <v>1.5</v>
       </c>
       <c r="T12" s="1">
         <f t="shared" si="7"/>
         <v>0.75</v>
       </c>
-      <c r="U12" s="23">
+      <c r="U12" s="2">
         <v>0.44</v>
       </c>
-      <c r="V12" s="23">
+      <c r="V12" s="2">
         <v>2.16</v>
       </c>
-      <c r="W12" s="23">
+      <c r="W12" s="2">
         <v>0.85</v>
       </c>
-      <c r="X12" s="23">
+      <c r="X12" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y12" s="19">
+      <c r="Y12" s="14">
         <v>5.5</v>
       </c>
       <c r="Z12" s="2">
         <v>1.25</v>
       </c>
+      <c r="AA12" s="17">
+        <f t="shared" si="29"/>
+        <v>2.2148750000000001</v>
+      </c>
       <c r="AB12" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.2148750000000001</v>
       </c>
       <c r="AC12" s="1">
         <f t="shared" si="3"/>
@@ -6024,6 +6365,17 @@
       <c r="AM12" s="2">
         <v>1</v>
       </c>
+      <c r="AN12" s="17">
+        <f t="shared" si="30"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="AO12">
+        <f t="shared" si="31"/>
+        <v>3.1349999999999998</v>
+      </c>
+      <c r="AP12">
+        <v>1</v>
+      </c>
       <c r="AS12">
         <f t="shared" si="4"/>
         <v>1.1702127659574468</v>
@@ -6032,322 +6384,416 @@
         <v>9</v>
       </c>
       <c r="AU12">
+        <f t="shared" si="21"/>
+        <v>57.08</v>
+      </c>
+      <c r="AV12">
+        <f t="shared" si="22"/>
+        <v>59</v>
+      </c>
+      <c r="AW12">
+        <f t="shared" si="23"/>
+        <v>1.9200000000000017</v>
+      </c>
+      <c r="AY12">
+        <f t="shared" si="11"/>
+        <v>4.375</v>
+      </c>
+      <c r="AZ12">
+        <f t="shared" si="12"/>
+        <v>5.375</v>
+      </c>
+      <c r="BA12">
+        <f t="shared" si="13"/>
+        <v>23.515625</v>
+      </c>
+      <c r="BB12">
+        <f t="shared" si="14"/>
+        <v>5.44</v>
+      </c>
+      <c r="BC12">
+        <f t="shared" si="15"/>
+        <v>5.47</v>
+      </c>
+      <c r="BD12">
+        <v>14</v>
+      </c>
+      <c r="BE12">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="BG12">
+        <f t="shared" si="17"/>
+        <v>7.66</v>
+      </c>
+      <c r="BH12">
         <f t="shared" si="18"/>
-        <v>57.08</v>
-      </c>
-      <c r="AV12">
+        <v>81.625</v>
+      </c>
+      <c r="BI12">
         <f t="shared" si="19"/>
-        <v>59</v>
-      </c>
-      <c r="AW12" s="21">
+        <v>56.215000000000003</v>
+      </c>
+      <c r="BJ12">
         <f t="shared" si="20"/>
-        <v>1.9200000000000017</v>
-      </c>
-      <c r="AY12">
-        <f t="shared" si="8"/>
-        <v>4.375</v>
-      </c>
-      <c r="AZ12">
-        <f t="shared" si="9"/>
-        <v>5.375</v>
-      </c>
-      <c r="BA12">
-        <f t="shared" si="10"/>
-        <v>23.515625</v>
-      </c>
-      <c r="BB12" s="21">
-        <f t="shared" si="11"/>
-        <v>5.44</v>
-      </c>
-      <c r="BC12" s="21">
-        <f t="shared" si="12"/>
-        <v>5.47</v>
-      </c>
-      <c r="BD12" s="21">
-        <v>14</v>
-      </c>
-      <c r="BE12" s="21">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="BG12" s="21">
-        <f t="shared" si="14"/>
-        <v>7.66</v>
-      </c>
-      <c r="BH12" s="21">
-        <f t="shared" si="15"/>
-        <v>62.875</v>
-      </c>
-      <c r="BI12" s="21">
-        <f t="shared" si="16"/>
-        <v>56.215000000000003</v>
-      </c>
-      <c r="BJ12" s="21">
-        <f t="shared" si="17"/>
-        <v>55.215000000000003</v>
+        <v>73.965000000000003</v>
       </c>
     </row>
-    <row r="13" spans="1:62" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
+    <row r="13" spans="1:62" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="8">
         <f t="shared" si="5"/>
         <v>0.75</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="7">
         <v>4.875</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="9">
         <v>0.75</v>
       </c>
-      <c r="G13" s="22">
+      <c r="E13" s="17">
+        <f t="shared" si="24"/>
+        <v>1.2768000000000002</v>
+      </c>
+      <c r="F13" s="17">
+        <f t="shared" si="25"/>
+        <v>1.8768000000000002</v>
+      </c>
+      <c r="G13" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I13" s="23">
+        <v>1.2768000000000002</v>
+      </c>
+      <c r="H13" s="17">
+        <f t="shared" si="26"/>
+        <v>3</v>
+      </c>
+      <c r="I13" s="2">
         <v>3.85</v>
       </c>
-      <c r="J13" s="23">
+      <c r="J13" s="2">
         <v>6</v>
       </c>
-      <c r="K13" s="23">
+      <c r="K13" s="2">
         <v>0.4</v>
       </c>
-      <c r="L13" s="23">
-        <v>1</v>
-      </c>
-      <c r="N13" s="22">
+      <c r="L13" s="2">
+        <v>1</v>
+      </c>
+      <c r="M13" s="17">
+        <f t="shared" si="27"/>
+        <v>1.6768000000000005</v>
+      </c>
+      <c r="N13" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q13" s="22">
+        <v>1.2768000000000002</v>
+      </c>
+      <c r="O13" s="17">
+        <f t="shared" si="28"/>
+        <v>2.0768000000000004</v>
+      </c>
+      <c r="P13" s="7">
+        <v>7</v>
+      </c>
+      <c r="Q13" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T13" s="11">
+        <v>1.6768000000000005</v>
+      </c>
+      <c r="R13" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="S13" s="20">
+        <v>1.5</v>
+      </c>
+      <c r="T13" s="8">
         <f t="shared" si="7"/>
         <v>0.75</v>
       </c>
-      <c r="U13" s="23">
+      <c r="U13" s="2">
         <v>0.44</v>
       </c>
-      <c r="V13" s="23">
+      <c r="V13" s="2">
         <v>2.16</v>
       </c>
-      <c r="W13" s="23">
+      <c r="W13" s="2">
         <v>0.85</v>
       </c>
-      <c r="X13" s="23">
+      <c r="X13" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y13" s="20"/>
-      <c r="Z13" s="12">
+      <c r="Y13" s="17">
+        <v>17.5</v>
+      </c>
+      <c r="Z13" s="9">
         <v>1.25</v>
       </c>
-      <c r="AB13" s="11">
+      <c r="AA13" s="17">
+        <f t="shared" si="29"/>
+        <v>2.1489000000000003</v>
+      </c>
+      <c r="AB13" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC13" s="11">
+        <v>2.1489000000000003</v>
+      </c>
+      <c r="AC13" s="8">
         <f t="shared" si="3"/>
         <v>4.2</v>
       </c>
-      <c r="AD13" s="17">
+      <c r="AD13" s="12">
         <v>6.65</v>
       </c>
-      <c r="AE13" s="17">
+      <c r="AE13" s="12">
         <f>AE14+(AE12-AE14)/2</f>
         <v>60.5</v>
       </c>
-      <c r="AF13" s="17">
+      <c r="AF13" s="12">
         <v>5.7</v>
       </c>
-      <c r="AG13" s="12">
+      <c r="AG13" s="9">
         <v>0.75</v>
       </c>
-      <c r="AH13" s="12">
+      <c r="AH13" s="9">
         <v>1.25</v>
       </c>
-      <c r="AI13" s="12">
+      <c r="AI13" s="9">
         <v>0.7</v>
       </c>
-      <c r="AJ13" s="12">
+      <c r="AJ13" s="9">
         <v>4.0999999999999996</v>
       </c>
-      <c r="AK13" s="12">
-        <v>1</v>
-      </c>
-      <c r="AL13" s="12">
+      <c r="AK13" s="9">
+        <v>1</v>
+      </c>
+      <c r="AL13" s="9">
         <v>0.1</v>
       </c>
-      <c r="AM13" s="12">
-        <v>1</v>
-      </c>
-      <c r="AS13" s="10">
+      <c r="AM13" s="9">
+        <v>1</v>
+      </c>
+      <c r="AN13" s="17">
+        <f t="shared" si="30"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="AO13">
+        <f t="shared" si="31"/>
+        <v>3.1349999999999998</v>
+      </c>
+      <c r="AP13">
+        <v>1</v>
+      </c>
+      <c r="AQ13"/>
+      <c r="AR13"/>
+      <c r="AS13" s="7">
         <f t="shared" si="4"/>
         <v>1.1666666666666667</v>
       </c>
-      <c r="AT13" s="10">
+      <c r="AT13" s="7">
         <v>10</v>
       </c>
-      <c r="AU13" s="10">
+      <c r="AU13" s="7">
+        <f t="shared" si="21"/>
+        <v>53.88</v>
+      </c>
+      <c r="AV13" s="13">
+        <f t="shared" si="22"/>
+        <v>55.625</v>
+      </c>
+      <c r="AW13" s="7">
+        <f t="shared" si="23"/>
+        <v>1.7449999999999974</v>
+      </c>
+      <c r="AY13">
+        <f t="shared" si="11"/>
+        <v>4.2</v>
+      </c>
+      <c r="AZ13">
+        <f t="shared" si="12"/>
+        <v>5.15</v>
+      </c>
+      <c r="BA13">
+        <f t="shared" si="13"/>
+        <v>21.630000000000003</v>
+      </c>
+      <c r="BB13">
+        <f t="shared" si="14"/>
+        <v>5.35</v>
+      </c>
+      <c r="BC13">
+        <f t="shared" si="15"/>
+        <v>5.25</v>
+      </c>
+      <c r="BD13">
+        <v>15</v>
+      </c>
+      <c r="BE13">
+        <f t="shared" si="16"/>
+        <v>-0.1</v>
+      </c>
+      <c r="BG13">
+        <f t="shared" si="17"/>
+        <v>19.66</v>
+      </c>
+      <c r="BH13">
         <f t="shared" si="18"/>
-        <v>53.88</v>
-      </c>
-      <c r="AV13" s="18">
+        <v>66.5</v>
+      </c>
+      <c r="BI13">
         <f t="shared" si="19"/>
-        <v>55.625</v>
-      </c>
-      <c r="AW13" s="25">
+        <v>40.840000000000003</v>
+      </c>
+      <c r="BJ13">
         <f t="shared" si="20"/>
-        <v>1.7449999999999974</v>
-      </c>
-      <c r="AY13">
-        <f t="shared" si="8"/>
-        <v>4.2</v>
-      </c>
-      <c r="AZ13">
-        <f t="shared" si="9"/>
-        <v>5.15</v>
-      </c>
-      <c r="BA13">
-        <f t="shared" si="10"/>
-        <v>21.630000000000003</v>
-      </c>
-      <c r="BB13" s="21">
-        <f t="shared" si="11"/>
-        <v>5.35</v>
-      </c>
-      <c r="BC13" s="21">
-        <f t="shared" si="12"/>
-        <v>5.25</v>
-      </c>
-      <c r="BD13" s="21">
-        <v>15</v>
-      </c>
-      <c r="BE13" s="21">
-        <f t="shared" si="13"/>
-        <v>-0.1</v>
-      </c>
-      <c r="BG13" s="21">
-        <f t="shared" si="14"/>
-        <v>2.16</v>
-      </c>
-      <c r="BH13" s="21">
-        <f t="shared" si="15"/>
-        <v>59.5</v>
-      </c>
-      <c r="BI13" s="21">
-        <f t="shared" si="16"/>
-        <v>58.34</v>
-      </c>
-      <c r="BJ13" s="21">
-        <f t="shared" si="17"/>
-        <v>57.34</v>
+        <v>46.84</v>
       </c>
     </row>
-    <row r="14" spans="1:62" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+    <row r="14" spans="1:62" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B14" s="6">
         <f t="shared" si="5"/>
         <v>0.75</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="3">
         <v>4.875</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="4">
         <v>0.75</v>
       </c>
-      <c r="G14" s="22">
+      <c r="E14" s="17">
+        <f t="shared" si="24"/>
+        <v>1.26</v>
+      </c>
+      <c r="F14" s="17">
+        <f t="shared" si="25"/>
+        <v>1.8599999999999999</v>
+      </c>
+      <c r="G14" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="23">
+        <v>1.26</v>
+      </c>
+      <c r="H14" s="17">
+        <f t="shared" si="26"/>
+        <v>8.875</v>
+      </c>
+      <c r="I14" s="2">
         <v>3.85</v>
       </c>
-      <c r="J14" s="23">
+      <c r="J14" s="2">
         <v>6</v>
       </c>
-      <c r="K14" s="23">
+      <c r="K14" s="2">
         <v>0.4</v>
       </c>
-      <c r="L14" s="23">
-        <v>1</v>
-      </c>
-      <c r="N14" s="22">
+      <c r="L14" s="2">
+        <v>1</v>
+      </c>
+      <c r="M14" s="17">
+        <f t="shared" si="27"/>
+        <v>1.6600000000000001</v>
+      </c>
+      <c r="N14" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="22">
+        <v>1.26</v>
+      </c>
+      <c r="O14" s="17">
+        <f t="shared" si="28"/>
+        <v>2.06</v>
+      </c>
+      <c r="P14" s="3">
+        <v>18.75</v>
+      </c>
+      <c r="Q14" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T14" s="9">
+        <v>1.6600000000000001</v>
+      </c>
+      <c r="R14" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="S14" s="20">
+        <v>1.5</v>
+      </c>
+      <c r="T14" s="6">
         <f t="shared" si="7"/>
         <v>0.75</v>
       </c>
-      <c r="U14" s="23">
+      <c r="U14" s="2">
         <v>0.44</v>
       </c>
-      <c r="V14" s="23">
+      <c r="V14" s="2">
         <v>2.16</v>
       </c>
-      <c r="W14" s="23">
+      <c r="W14" s="2">
         <v>0.85</v>
       </c>
-      <c r="X14" s="23">
+      <c r="X14" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y14" s="19">
+      <c r="Y14" s="14">
         <v>3.5</v>
       </c>
-      <c r="Z14" s="5">
+      <c r="Z14" s="4">
         <v>1.25</v>
       </c>
-      <c r="AB14" s="9">
+      <c r="AA14" s="17">
+        <f t="shared" si="29"/>
+        <v>2.120625</v>
+      </c>
+      <c r="AB14" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC14" s="9">
+        <v>2.120625</v>
+      </c>
+      <c r="AC14" s="6">
         <f t="shared" si="3"/>
         <v>4.125</v>
       </c>
-      <c r="AD14" s="4">
+      <c r="AD14" s="3">
         <v>6.5</v>
       </c>
-      <c r="AE14" s="4">
+      <c r="AE14" s="3">
         <f>57+1/8</f>
         <v>57.125</v>
       </c>
-      <c r="AF14" s="4">
+      <c r="AF14" s="3">
         <f>5+5/8</f>
         <v>5.625</v>
       </c>
-      <c r="AG14" s="5">
+      <c r="AG14" s="4">
         <v>0.75</v>
       </c>
-      <c r="AH14" s="5">
+      <c r="AH14" s="4">
         <v>1.25</v>
       </c>
-      <c r="AI14" s="5">
+      <c r="AI14" s="4">
         <v>0.7</v>
       </c>
-      <c r="AJ14" s="5">
+      <c r="AJ14" s="4">
         <v>4.0999999999999996</v>
       </c>
-      <c r="AK14" s="5">
-        <v>1</v>
-      </c>
-      <c r="AL14" s="5">
+      <c r="AK14" s="4">
+        <v>1</v>
+      </c>
+      <c r="AL14" s="4">
         <v>0.1</v>
       </c>
-      <c r="AM14" s="5">
-        <v>1</v>
-      </c>
-      <c r="AS14" s="4">
+      <c r="AM14" s="4">
+        <v>1</v>
+      </c>
+      <c r="AN14" s="17">
+        <f t="shared" si="30"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="AO14">
+        <f t="shared" si="31"/>
+        <v>3.1349999999999998</v>
+      </c>
+      <c r="AP14">
+        <v>1</v>
+      </c>
+      <c r="AQ14"/>
+      <c r="AR14"/>
+      <c r="AS14" s="3">
         <f t="shared" si="4"/>
         <v>1.1555555555555554</v>
       </c>
@@ -6355,137 +6801,170 @@
         <v>11</v>
       </c>
       <c r="AU14">
+        <f t="shared" si="21"/>
+        <v>50.85</v>
+      </c>
+      <c r="AV14">
+        <f t="shared" si="22"/>
+        <v>52.25</v>
+      </c>
+      <c r="AW14">
+        <f t="shared" si="23"/>
+        <v>1.3999999999999986</v>
+      </c>
+      <c r="AY14">
+        <f t="shared" si="11"/>
+        <v>4.125</v>
+      </c>
+      <c r="AZ14">
+        <f t="shared" si="12"/>
+        <v>5</v>
+      </c>
+      <c r="BA14">
+        <f t="shared" si="13"/>
+        <v>20.625</v>
+      </c>
+      <c r="BB14">
+        <f t="shared" si="14"/>
+        <v>5.1100000000000003</v>
+      </c>
+      <c r="BC14">
+        <f t="shared" si="15"/>
+        <v>5.12</v>
+      </c>
+      <c r="BD14">
+        <f t="shared" si="32"/>
+        <v>15</v>
+      </c>
+      <c r="BE14">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="BG14">
+        <f t="shared" si="17"/>
+        <v>5.66</v>
+      </c>
+      <c r="BH14">
         <f t="shared" si="18"/>
-        <v>50.85</v>
-      </c>
-      <c r="AV14">
+        <v>74.875</v>
+      </c>
+      <c r="BI14">
         <f t="shared" si="19"/>
-        <v>52.25</v>
-      </c>
-      <c r="AW14" s="21">
+        <v>51.465000000000003</v>
+      </c>
+      <c r="BJ14">
         <f t="shared" si="20"/>
-        <v>1.3999999999999986</v>
-      </c>
-      <c r="AY14">
-        <f t="shared" si="8"/>
-        <v>4.125</v>
-      </c>
-      <c r="AZ14">
-        <f t="shared" si="9"/>
-        <v>5</v>
-      </c>
-      <c r="BA14">
-        <f t="shared" si="10"/>
-        <v>20.625</v>
-      </c>
-      <c r="BB14" s="21">
-        <f t="shared" si="11"/>
-        <v>5.1100000000000003</v>
-      </c>
-      <c r="BC14" s="21">
-        <f t="shared" si="12"/>
-        <v>5.12</v>
-      </c>
-      <c r="BD14" s="21">
-        <f t="shared" si="21"/>
-        <v>15</v>
-      </c>
-      <c r="BE14" s="21">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="BG14" s="21">
-        <f t="shared" si="14"/>
-        <v>5.66</v>
-      </c>
-      <c r="BH14" s="21">
-        <f t="shared" si="15"/>
-        <v>56.125</v>
-      </c>
-      <c r="BI14" s="21">
-        <f t="shared" si="16"/>
-        <v>51.465000000000003</v>
-      </c>
-      <c r="BJ14" s="21">
-        <f t="shared" si="17"/>
-        <v>50.465000000000003</v>
+        <v>69.215000000000003</v>
       </c>
     </row>
-    <row r="15" spans="1:62" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+    <row r="15" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>53</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="5">
         <f t="shared" si="5"/>
         <v>0.63</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15">
         <v>4.3499999999999996</v>
       </c>
       <c r="D15" s="2">
         <v>0.75</v>
       </c>
-      <c r="G15" s="22">
+      <c r="E15" s="17">
+        <f t="shared" si="24"/>
+        <v>1.19</v>
+      </c>
+      <c r="F15" s="17">
+        <f t="shared" si="25"/>
+        <v>1.79</v>
+      </c>
+      <c r="G15" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I15" s="23">
+        <v>1.19</v>
+      </c>
+      <c r="H15" s="17">
+        <f t="shared" si="26"/>
+        <v>3</v>
+      </c>
+      <c r="I15" s="2">
         <v>3.85</v>
       </c>
-      <c r="J15" s="23">
+      <c r="J15" s="2">
         <v>6</v>
       </c>
-      <c r="K15" s="23">
+      <c r="K15" s="2">
         <v>0.35</v>
       </c>
-      <c r="L15" s="23">
-        <v>1</v>
-      </c>
-      <c r="N15" s="22">
+      <c r="L15" s="2">
+        <v>1</v>
+      </c>
+      <c r="M15" s="17">
+        <f t="shared" si="27"/>
+        <v>1.5899999999999999</v>
+      </c>
+      <c r="N15" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="22">
+        <v>1.19</v>
+      </c>
+      <c r="O15" s="17">
+        <f t="shared" si="28"/>
+        <v>1.99</v>
+      </c>
+      <c r="P15">
+        <v>7</v>
+      </c>
+      <c r="Q15" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T15" s="7">
+        <v>1.5899999999999999</v>
+      </c>
+      <c r="R15" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="S15" s="20">
+        <v>1.5</v>
+      </c>
+      <c r="T15" s="5">
         <f t="shared" si="7"/>
         <v>0.63</v>
       </c>
-      <c r="U15" s="23">
+      <c r="U15" s="2">
         <v>0.44</v>
       </c>
-      <c r="V15" s="23">
+      <c r="V15" s="2">
         <v>2.16</v>
       </c>
-      <c r="W15" s="23">
+      <c r="W15" s="2">
         <v>0.85</v>
       </c>
-      <c r="X15" s="23">
+      <c r="X15" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y15" s="20">
+      <c r="Y15" s="15">
         <v>14.25</v>
       </c>
       <c r="Z15" s="2">
         <v>1.25</v>
       </c>
-      <c r="AB15" s="7">
+      <c r="AA15" s="17">
+        <f>AF15*0.344</f>
+        <v>1.8274999999999999</v>
+      </c>
+      <c r="AB15" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC15" s="7">
+        <v>1.8274999999999999</v>
+      </c>
+      <c r="AC15" s="5">
         <f t="shared" si="3"/>
         <v>4.0525000000000002</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AD15">
         <v>6.25</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AE15">
         <v>53.5</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AF15">
         <f>5+5/16</f>
         <v>5.3125</v>
       </c>
@@ -6501,16 +6980,24 @@
       <c r="AJ15" s="2">
         <v>4.0999999999999996</v>
       </c>
-      <c r="AK15" s="8">
-        <v>1</v>
-      </c>
-      <c r="AL15" s="8">
+      <c r="AK15" s="2">
+        <v>1</v>
+      </c>
+      <c r="AL15" s="2">
         <v>0.1</v>
       </c>
-      <c r="AM15" s="8">
-        <v>1</v>
-      </c>
-      <c r="AP15" s="24">
+      <c r="AM15" s="2">
+        <v>1</v>
+      </c>
+      <c r="AN15" s="17">
+        <f t="shared" si="30"/>
+        <v>0.504</v>
+      </c>
+      <c r="AO15">
+        <f t="shared" si="31"/>
+        <v>2.6334</v>
+      </c>
+      <c r="AP15">
         <v>0</v>
       </c>
       <c r="AS15">
@@ -6521,59 +7008,59 @@
         <v>12</v>
       </c>
       <c r="AU15">
+        <f t="shared" si="21"/>
+        <v>48</v>
+      </c>
+      <c r="AV15">
+        <f t="shared" si="22"/>
+        <v>49.15</v>
+      </c>
+      <c r="AW15">
+        <f t="shared" si="23"/>
+        <v>1.1499999999999986</v>
+      </c>
+      <c r="AY15">
+        <f t="shared" si="11"/>
+        <v>4.0525000000000002</v>
+      </c>
+      <c r="AZ15">
+        <f t="shared" si="12"/>
+        <v>4.99</v>
+      </c>
+      <c r="BA15">
+        <f t="shared" si="13"/>
+        <v>20.221975</v>
+      </c>
+      <c r="BB15">
+        <f t="shared" si="14"/>
+        <v>5.05</v>
+      </c>
+      <c r="BC15">
+        <f t="shared" si="15"/>
+        <v>5.07</v>
+      </c>
+      <c r="BD15">
+        <v>16</v>
+      </c>
+      <c r="BE15">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="BG15">
+        <f t="shared" si="17"/>
+        <v>16.41</v>
+      </c>
+      <c r="BH15">
         <f t="shared" si="18"/>
-        <v>48</v>
-      </c>
-      <c r="AV15">
+        <v>59.5</v>
+      </c>
+      <c r="BI15">
         <f t="shared" si="19"/>
-        <v>49.15</v>
-      </c>
-      <c r="AW15" s="21">
+        <v>37.090000000000003</v>
+      </c>
+      <c r="BJ15">
         <f t="shared" si="20"/>
-        <v>1.1499999999999986</v>
-      </c>
-      <c r="AY15">
-        <f t="shared" si="8"/>
-        <v>4.0525000000000002</v>
-      </c>
-      <c r="AZ15">
-        <f t="shared" si="9"/>
-        <v>4.99</v>
-      </c>
-      <c r="BA15">
-        <f t="shared" si="10"/>
-        <v>20.221975</v>
-      </c>
-      <c r="BB15" s="21">
-        <f t="shared" si="11"/>
-        <v>5.05</v>
-      </c>
-      <c r="BC15" s="21">
-        <f t="shared" si="12"/>
-        <v>5.07</v>
-      </c>
-      <c r="BD15" s="21">
-        <v>16</v>
-      </c>
-      <c r="BE15" s="21">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="BG15" s="21">
-        <f t="shared" si="14"/>
-        <v>16.41</v>
-      </c>
-      <c r="BH15" s="21">
-        <f t="shared" si="15"/>
-        <v>52.5</v>
-      </c>
-      <c r="BI15" s="21">
-        <f t="shared" si="16"/>
-        <v>37.090000000000003</v>
-      </c>
-      <c r="BJ15" s="21">
-        <f t="shared" si="17"/>
-        <v>36.090000000000003</v>
+        <v>43.09</v>
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.25">
@@ -6584,62 +7071,95 @@
         <f t="shared" si="5"/>
         <v>0.63</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16">
         <v>4.3499999999999996</v>
       </c>
       <c r="D16" s="2">
         <v>0.75</v>
       </c>
-      <c r="G16" s="22">
+      <c r="E16" s="17">
+        <f t="shared" si="24"/>
+        <v>1.1480000000000001</v>
+      </c>
+      <c r="F16" s="17">
+        <f t="shared" si="25"/>
+        <v>1.7480000000000002</v>
+      </c>
+      <c r="G16" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="23">
+        <v>1.1480000000000001</v>
+      </c>
+      <c r="H16" s="17">
+        <f t="shared" si="26"/>
+        <v>8.875</v>
+      </c>
+      <c r="I16" s="2">
         <v>3.85</v>
       </c>
-      <c r="J16" s="23">
+      <c r="J16" s="2">
         <v>6</v>
       </c>
-      <c r="K16" s="23">
+      <c r="K16" s="2">
         <v>0.35</v>
       </c>
-      <c r="L16" s="23">
-        <v>1</v>
-      </c>
-      <c r="N16" s="22">
+      <c r="L16" s="2">
+        <v>1</v>
+      </c>
+      <c r="M16" s="17">
+        <f t="shared" si="27"/>
+        <v>1.548</v>
+      </c>
+      <c r="N16" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="22">
+        <v>1.1480000000000001</v>
+      </c>
+      <c r="O16" s="17">
+        <f t="shared" si="28"/>
+        <v>1.9480000000000002</v>
+      </c>
+      <c r="P16">
+        <v>18.75</v>
+      </c>
+      <c r="Q16" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.548</v>
+      </c>
+      <c r="R16" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="S16" s="20">
+        <v>1.5</v>
       </c>
       <c r="T16" s="1">
         <f t="shared" si="7"/>
         <v>0.63</v>
       </c>
-      <c r="U16" s="23">
+      <c r="U16" s="2">
         <v>0.44</v>
       </c>
-      <c r="V16" s="23">
+      <c r="V16" s="2">
         <v>2.16</v>
       </c>
-      <c r="W16" s="23">
+      <c r="W16" s="2">
         <v>0.85</v>
       </c>
-      <c r="X16" s="23">
+      <c r="X16" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y16" s="19">
+      <c r="Y16" s="14">
         <f>2+7/8</f>
         <v>2.875</v>
       </c>
       <c r="Z16" s="2">
         <v>1.25</v>
       </c>
+      <c r="AA16" s="17">
+        <f t="shared" ref="AA16:AA24" si="33">AF16*0.344</f>
+        <v>1.7629999999999999</v>
+      </c>
       <c r="AB16" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.7629999999999999</v>
       </c>
       <c r="AC16" s="1">
         <f t="shared" si="3"/>
@@ -6678,7 +7198,15 @@
       <c r="AM16" s="2">
         <v>1</v>
       </c>
-      <c r="AP16" s="23">
+      <c r="AN16" s="17">
+        <f t="shared" si="30"/>
+        <v>0.504</v>
+      </c>
+      <c r="AO16">
+        <f t="shared" si="31"/>
+        <v>2.6334</v>
+      </c>
+      <c r="AP16">
         <v>0</v>
       </c>
       <c r="AS16">
@@ -6689,59 +7217,59 @@
         <v>13</v>
       </c>
       <c r="AU16">
+        <f t="shared" si="21"/>
+        <v>45.31</v>
+      </c>
+      <c r="AV16">
+        <f t="shared" si="22"/>
+        <v>46.524999999999999</v>
+      </c>
+      <c r="AW16">
+        <f t="shared" si="23"/>
+        <v>1.2149999999999963</v>
+      </c>
+      <c r="AY16">
+        <f t="shared" si="11"/>
+        <v>3.8650000000000002</v>
+      </c>
+      <c r="AZ16">
+        <f t="shared" si="12"/>
+        <v>4.6150000000000002</v>
+      </c>
+      <c r="BA16">
+        <f t="shared" si="13"/>
+        <v>17.836975000000002</v>
+      </c>
+      <c r="BB16">
+        <f t="shared" si="14"/>
+        <v>4.75</v>
+      </c>
+      <c r="BC16">
+        <f t="shared" si="15"/>
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="BD16">
+        <v>15.5</v>
+      </c>
+      <c r="BE16">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="BG16">
+        <f t="shared" si="17"/>
+        <v>5.0350000000000001</v>
+      </c>
+      <c r="BH16">
         <f t="shared" si="18"/>
-        <v>45.31</v>
-      </c>
-      <c r="AV16">
+        <v>68.625</v>
+      </c>
+      <c r="BI16">
         <f t="shared" si="19"/>
-        <v>46.524999999999999</v>
-      </c>
-      <c r="AW16" s="21">
+        <v>45.84</v>
+      </c>
+      <c r="BJ16">
         <f t="shared" si="20"/>
-        <v>1.2149999999999963</v>
-      </c>
-      <c r="AY16">
-        <f t="shared" si="8"/>
-        <v>3.8650000000000002</v>
-      </c>
-      <c r="AZ16">
-        <f t="shared" si="9"/>
-        <v>4.6150000000000002</v>
-      </c>
-      <c r="BA16">
-        <f t="shared" si="10"/>
-        <v>17.836975000000002</v>
-      </c>
-      <c r="BB16" s="21">
-        <f t="shared" si="11"/>
-        <v>4.75</v>
-      </c>
-      <c r="BC16" s="21">
-        <f t="shared" si="12"/>
-        <v>4.7699999999999996</v>
-      </c>
-      <c r="BD16" s="21">
-        <v>15.5</v>
-      </c>
-      <c r="BE16" s="21">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="BG16" s="21">
-        <f t="shared" si="14"/>
-        <v>5.0350000000000001</v>
-      </c>
-      <c r="BH16" s="21">
-        <f t="shared" si="15"/>
-        <v>49.875</v>
-      </c>
-      <c r="BI16" s="21">
-        <f t="shared" si="16"/>
-        <v>45.84</v>
-      </c>
-      <c r="BJ16" s="21">
-        <f t="shared" si="17"/>
-        <v>44.84</v>
+        <v>63.59</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.25">
@@ -6752,61 +7280,94 @@
         <f t="shared" si="5"/>
         <v>0.63</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17">
         <v>4.3499999999999996</v>
       </c>
       <c r="D17" s="2">
         <v>0.75</v>
       </c>
-      <c r="G17" s="22">
+      <c r="E17" s="17">
+        <f t="shared" si="24"/>
+        <v>1.1060000000000001</v>
+      </c>
+      <c r="F17" s="17">
+        <f t="shared" si="25"/>
+        <v>1.706</v>
+      </c>
+      <c r="G17" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I17" s="23">
+        <v>1.1060000000000001</v>
+      </c>
+      <c r="H17" s="17">
+        <f t="shared" si="26"/>
+        <v>3</v>
+      </c>
+      <c r="I17" s="2">
         <v>3.85</v>
       </c>
-      <c r="J17" s="23">
+      <c r="J17" s="2">
         <v>6</v>
       </c>
-      <c r="K17" s="23">
+      <c r="K17" s="2">
         <v>0.35</v>
       </c>
-      <c r="L17" s="23">
-        <v>1</v>
-      </c>
-      <c r="N17" s="22">
+      <c r="L17" s="2">
+        <v>1</v>
+      </c>
+      <c r="M17" s="17">
+        <f t="shared" si="27"/>
+        <v>1.5060000000000002</v>
+      </c>
+      <c r="N17" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="22">
+        <v>1.1060000000000001</v>
+      </c>
+      <c r="O17" s="17">
+        <f t="shared" si="28"/>
+        <v>1.9060000000000001</v>
+      </c>
+      <c r="P17">
+        <v>7</v>
+      </c>
+      <c r="Q17" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.5060000000000002</v>
+      </c>
+      <c r="R17" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="S17" s="20">
+        <v>1.5</v>
       </c>
       <c r="T17" s="1">
         <f t="shared" si="7"/>
         <v>0.63</v>
       </c>
-      <c r="U17" s="23">
+      <c r="U17" s="2">
         <v>0.44</v>
       </c>
-      <c r="V17" s="23">
+      <c r="V17" s="2">
         <v>2.16</v>
       </c>
-      <c r="W17" s="23">
+      <c r="W17" s="2">
         <v>0.85</v>
       </c>
-      <c r="X17" s="23">
+      <c r="X17" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y17" s="20">
+      <c r="Y17" s="15">
         <v>11.25</v>
       </c>
       <c r="Z17" s="2">
         <v>1.25</v>
       </c>
+      <c r="AA17" s="17">
+        <f t="shared" si="33"/>
+        <v>1.6984999999999999</v>
+      </c>
       <c r="AB17" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.6984999999999999</v>
       </c>
       <c r="AC17" s="1">
         <f t="shared" si="3"/>
@@ -6845,7 +7406,15 @@
       <c r="AM17" s="2">
         <v>1</v>
       </c>
-      <c r="AP17" s="23">
+      <c r="AN17" s="17">
+        <f t="shared" si="30"/>
+        <v>0.504</v>
+      </c>
+      <c r="AO17">
+        <f t="shared" si="31"/>
+        <v>2.6334</v>
+      </c>
+      <c r="AP17">
         <v>0</v>
       </c>
       <c r="AS17">
@@ -6856,60 +7425,60 @@
         <v>14</v>
       </c>
       <c r="AU17">
+        <f t="shared" si="21"/>
+        <v>42.76</v>
+      </c>
+      <c r="AV17">
+        <f t="shared" si="22"/>
+        <v>43.65</v>
+      </c>
+      <c r="AW17">
+        <f t="shared" si="23"/>
+        <v>0.89000000000000057</v>
+      </c>
+      <c r="AY17">
+        <f t="shared" si="11"/>
+        <v>3.6775000000000002</v>
+      </c>
+      <c r="AZ17">
+        <f t="shared" si="12"/>
+        <v>4.4275000000000002</v>
+      </c>
+      <c r="BA17">
+        <f t="shared" si="13"/>
+        <v>16.282131250000003</v>
+      </c>
+      <c r="BB17">
+        <f t="shared" si="14"/>
+        <v>4.54</v>
+      </c>
+      <c r="BC17">
+        <f t="shared" si="15"/>
+        <v>4.55</v>
+      </c>
+      <c r="BD17">
+        <f t="shared" si="32"/>
+        <v>15.5</v>
+      </c>
+      <c r="BE17">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="BG17">
+        <f t="shared" si="17"/>
+        <v>13.41</v>
+      </c>
+      <c r="BH17">
         <f t="shared" si="18"/>
-        <v>42.76</v>
-      </c>
-      <c r="AV17">
+        <v>54</v>
+      </c>
+      <c r="BI17">
         <f t="shared" si="19"/>
-        <v>43.65</v>
-      </c>
-      <c r="AW17" s="21">
+        <v>34.590000000000003</v>
+      </c>
+      <c r="BJ17">
         <f t="shared" si="20"/>
-        <v>0.89000000000000057</v>
-      </c>
-      <c r="AY17">
-        <f t="shared" si="8"/>
-        <v>3.6775000000000002</v>
-      </c>
-      <c r="AZ17">
-        <f t="shared" si="9"/>
-        <v>4.4275000000000002</v>
-      </c>
-      <c r="BA17">
-        <f t="shared" si="10"/>
-        <v>16.282131250000003</v>
-      </c>
-      <c r="BB17" s="21">
-        <f t="shared" si="11"/>
-        <v>4.54</v>
-      </c>
-      <c r="BC17" s="21">
-        <f t="shared" si="12"/>
-        <v>4.55</v>
-      </c>
-      <c r="BD17" s="21">
-        <f t="shared" si="21"/>
-        <v>15.5</v>
-      </c>
-      <c r="BE17" s="21">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="BG17" s="21">
-        <f t="shared" si="14"/>
-        <v>13.41</v>
-      </c>
-      <c r="BH17" s="21">
-        <f t="shared" si="15"/>
-        <v>47</v>
-      </c>
-      <c r="BI17" s="21">
-        <f t="shared" si="16"/>
-        <v>34.590000000000003</v>
-      </c>
-      <c r="BJ17" s="21">
-        <f t="shared" si="17"/>
-        <v>33.590000000000003</v>
+        <v>40.590000000000003</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.25">
@@ -6920,61 +7489,94 @@
         <f t="shared" si="5"/>
         <v>0.63</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18">
         <v>4.3499999999999996</v>
       </c>
       <c r="D18" s="2">
         <v>0.75</v>
       </c>
-      <c r="G18" s="22">
+      <c r="E18" s="17">
+        <f t="shared" si="24"/>
+        <v>1.0640000000000001</v>
+      </c>
+      <c r="F18" s="17">
+        <f t="shared" si="25"/>
+        <v>1.6640000000000001</v>
+      </c>
+      <c r="G18" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I18" s="23">
+        <v>1.0640000000000001</v>
+      </c>
+      <c r="H18" s="17">
+        <f t="shared" si="26"/>
+        <v>8.875</v>
+      </c>
+      <c r="I18" s="2">
         <v>3.85</v>
       </c>
-      <c r="J18" s="23">
+      <c r="J18" s="2">
         <v>6</v>
       </c>
-      <c r="K18" s="23">
+      <c r="K18" s="2">
         <v>0.35</v>
       </c>
-      <c r="L18" s="23">
-        <v>1</v>
-      </c>
-      <c r="N18" s="22">
+      <c r="L18" s="2">
+        <v>1</v>
+      </c>
+      <c r="M18" s="17">
+        <f t="shared" si="27"/>
+        <v>1.464</v>
+      </c>
+      <c r="N18" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="22">
+        <v>1.0640000000000001</v>
+      </c>
+      <c r="O18" s="17">
+        <f t="shared" si="28"/>
+        <v>1.8640000000000001</v>
+      </c>
+      <c r="P18">
+        <v>18.75</v>
+      </c>
+      <c r="Q18" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.464</v>
+      </c>
+      <c r="R18" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="S18" s="20">
+        <v>1.5</v>
       </c>
       <c r="T18" s="1">
         <f t="shared" si="7"/>
         <v>0.63</v>
       </c>
-      <c r="U18" s="23">
+      <c r="U18" s="2">
         <v>0.44</v>
       </c>
-      <c r="V18" s="23">
+      <c r="V18" s="2">
         <v>2.16</v>
       </c>
-      <c r="W18" s="23">
+      <c r="W18" s="2">
         <v>0.85</v>
       </c>
-      <c r="X18" s="23">
+      <c r="X18" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y18" s="19">
+      <c r="Y18" s="14">
         <v>2</v>
       </c>
       <c r="Z18" s="2">
         <v>1.25</v>
       </c>
+      <c r="AA18" s="17">
+        <f t="shared" si="33"/>
+        <v>1.6339999999999999</v>
+      </c>
       <c r="AB18" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.6339999999999999</v>
       </c>
       <c r="AC18" s="1">
         <f t="shared" si="3"/>
@@ -7012,7 +7614,15 @@
       <c r="AM18" s="2">
         <v>1</v>
       </c>
-      <c r="AP18" s="23">
+      <c r="AN18" s="17">
+        <f t="shared" si="30"/>
+        <v>0.504</v>
+      </c>
+      <c r="AO18">
+        <f t="shared" si="31"/>
+        <v>2.6334</v>
+      </c>
+      <c r="AP18">
         <v>0</v>
       </c>
       <c r="AS18">
@@ -7023,60 +7633,60 @@
         <v>15</v>
       </c>
       <c r="AU18">
+        <f t="shared" si="21"/>
+        <v>40.36</v>
+      </c>
+      <c r="AV18">
+        <f t="shared" si="22"/>
+        <v>41.4</v>
+      </c>
+      <c r="AW18">
+        <f t="shared" si="23"/>
+        <v>1.0399999999999991</v>
+      </c>
+      <c r="AY18">
+        <f t="shared" si="11"/>
+        <v>3.49</v>
+      </c>
+      <c r="AZ18">
+        <f t="shared" si="12"/>
+        <v>4.24</v>
+      </c>
+      <c r="BA18">
+        <f t="shared" si="13"/>
+        <v>14.797600000000001</v>
+      </c>
+      <c r="BB18">
+        <f t="shared" si="14"/>
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="BC18">
+        <f t="shared" si="15"/>
+        <v>4.34</v>
+      </c>
+      <c r="BD18">
+        <f t="shared" si="32"/>
+        <v>15.5</v>
+      </c>
+      <c r="BE18">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="BG18">
+        <f t="shared" si="17"/>
+        <v>4.16</v>
+      </c>
+      <c r="BH18">
         <f t="shared" si="18"/>
-        <v>40.36</v>
-      </c>
-      <c r="AV18">
+        <v>63.5</v>
+      </c>
+      <c r="BI18">
         <f t="shared" si="19"/>
-        <v>41.4</v>
-      </c>
-      <c r="AW18" s="21">
+        <v>41.59</v>
+      </c>
+      <c r="BJ18">
         <f t="shared" si="20"/>
-        <v>1.0399999999999991</v>
-      </c>
-      <c r="AY18">
-        <f t="shared" si="8"/>
-        <v>3.49</v>
-      </c>
-      <c r="AZ18">
-        <f t="shared" si="9"/>
-        <v>4.24</v>
-      </c>
-      <c r="BA18">
-        <f t="shared" si="10"/>
-        <v>14.797600000000001</v>
-      </c>
-      <c r="BB18" s="21">
-        <f t="shared" si="11"/>
-        <v>4.3499999999999996</v>
-      </c>
-      <c r="BC18" s="21">
-        <f t="shared" si="12"/>
-        <v>4.34</v>
-      </c>
-      <c r="BD18" s="21">
-        <f t="shared" si="21"/>
-        <v>15.5</v>
-      </c>
-      <c r="BE18" s="21">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="BG18" s="21">
-        <f t="shared" si="14"/>
-        <v>4.16</v>
-      </c>
-      <c r="BH18" s="21">
-        <f t="shared" si="15"/>
-        <v>44.75</v>
-      </c>
-      <c r="BI18" s="21">
-        <f t="shared" si="16"/>
-        <v>41.59</v>
-      </c>
-      <c r="BJ18" s="21">
-        <f t="shared" si="17"/>
-        <v>40.590000000000003</v>
+        <v>59.34</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.25">
@@ -7087,61 +7697,94 @@
         <f t="shared" si="5"/>
         <v>0.63</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19">
         <v>4.05</v>
       </c>
       <c r="D19" s="2">
         <v>0.75</v>
       </c>
-      <c r="G19" s="22">
+      <c r="E19" s="17">
+        <f t="shared" si="24"/>
+        <v>1.022</v>
+      </c>
+      <c r="F19" s="17">
+        <f t="shared" si="25"/>
+        <v>1.6219999999999999</v>
+      </c>
+      <c r="G19" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I19" s="23">
+        <v>1.022</v>
+      </c>
+      <c r="H19" s="17">
+        <f t="shared" si="26"/>
+        <v>3</v>
+      </c>
+      <c r="I19" s="2">
         <v>3.1</v>
       </c>
-      <c r="J19" s="23">
+      <c r="J19" s="2">
         <v>5</v>
       </c>
-      <c r="K19" s="23">
+      <c r="K19" s="2">
         <v>0.35</v>
       </c>
-      <c r="L19" s="23">
-        <v>1</v>
-      </c>
-      <c r="N19" s="22">
+      <c r="L19" s="2">
+        <v>1</v>
+      </c>
+      <c r="M19" s="17">
+        <f t="shared" si="27"/>
+        <v>1.4220000000000002</v>
+      </c>
+      <c r="N19" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q19" s="22">
+        <v>1.022</v>
+      </c>
+      <c r="O19" s="17">
+        <f t="shared" si="28"/>
+        <v>1.8220000000000001</v>
+      </c>
+      <c r="P19">
+        <v>7</v>
+      </c>
+      <c r="Q19" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.4220000000000002</v>
+      </c>
+      <c r="R19" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="S19" s="20">
+        <v>1.5</v>
       </c>
       <c r="T19" s="1">
         <f t="shared" si="7"/>
         <v>0.63</v>
       </c>
-      <c r="U19" s="23">
+      <c r="U19" s="2">
         <v>0.44</v>
       </c>
-      <c r="V19" s="23">
+      <c r="V19" s="2">
         <v>2.16</v>
       </c>
-      <c r="W19" s="23">
+      <c r="W19" s="2">
         <v>0.85</v>
       </c>
-      <c r="X19" s="23">
+      <c r="X19" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y19" s="20">
+      <c r="Y19" s="15">
         <v>9.5</v>
       </c>
       <c r="Z19" s="2">
         <v>1.25</v>
       </c>
+      <c r="AA19" s="17">
+        <f t="shared" si="33"/>
+        <v>1.5694999999999999</v>
+      </c>
       <c r="AB19" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.5694999999999999</v>
       </c>
       <c r="AC19" s="1">
         <f t="shared" si="3"/>
@@ -7180,7 +7823,15 @@
       <c r="AM19" s="2">
         <v>1</v>
       </c>
-      <c r="AP19" s="23">
+      <c r="AN19" s="17">
+        <f t="shared" si="30"/>
+        <v>0.504</v>
+      </c>
+      <c r="AO19">
+        <f t="shared" si="31"/>
+        <v>2.6334</v>
+      </c>
+      <c r="AP19">
         <v>0</v>
       </c>
       <c r="AS19">
@@ -7191,60 +7842,60 @@
         <v>16</v>
       </c>
       <c r="AU19">
+        <f t="shared" si="21"/>
+        <v>38.1</v>
+      </c>
+      <c r="AV19">
+        <f t="shared" si="22"/>
+        <v>38.825000000000003</v>
+      </c>
+      <c r="AW19">
+        <f t="shared" si="23"/>
+        <v>0.72500000000000142</v>
+      </c>
+      <c r="AY19">
+        <f t="shared" si="11"/>
+        <v>3.3025000000000002</v>
+      </c>
+      <c r="AZ19">
+        <f t="shared" si="12"/>
+        <v>4.0525000000000002</v>
+      </c>
+      <c r="BA19">
+        <f t="shared" si="13"/>
+        <v>13.383381250000001</v>
+      </c>
+      <c r="BB19">
+        <f t="shared" si="14"/>
+        <v>4.16</v>
+      </c>
+      <c r="BC19">
+        <f t="shared" si="15"/>
+        <v>4.13</v>
+      </c>
+      <c r="BD19">
+        <f t="shared" si="32"/>
+        <v>15.5</v>
+      </c>
+      <c r="BE19">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="BG19">
+        <f t="shared" si="17"/>
+        <v>11.66</v>
+      </c>
+      <c r="BH19">
         <f t="shared" si="18"/>
-        <v>38.1</v>
-      </c>
-      <c r="AV19">
+        <v>48.875</v>
+      </c>
+      <c r="BI19">
         <f t="shared" si="19"/>
-        <v>38.825000000000003</v>
-      </c>
-      <c r="AW19" s="21">
+        <v>31.215</v>
+      </c>
+      <c r="BJ19">
         <f t="shared" si="20"/>
-        <v>0.72500000000000142</v>
-      </c>
-      <c r="AY19">
-        <f t="shared" si="8"/>
-        <v>3.3025000000000002</v>
-      </c>
-      <c r="AZ19">
-        <f t="shared" si="9"/>
-        <v>4.0525000000000002</v>
-      </c>
-      <c r="BA19">
-        <f t="shared" si="10"/>
-        <v>13.383381250000001</v>
-      </c>
-      <c r="BB19" s="21">
-        <f t="shared" si="11"/>
-        <v>4.16</v>
-      </c>
-      <c r="BC19" s="21">
-        <f t="shared" si="12"/>
-        <v>4.13</v>
-      </c>
-      <c r="BD19" s="21">
-        <f t="shared" si="21"/>
-        <v>15.5</v>
-      </c>
-      <c r="BE19" s="21">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="BG19" s="21">
-        <f t="shared" si="14"/>
-        <v>11.66</v>
-      </c>
-      <c r="BH19" s="21">
-        <f t="shared" si="15"/>
-        <v>41.875</v>
-      </c>
-      <c r="BI19" s="21">
-        <f t="shared" si="16"/>
-        <v>31.215</v>
-      </c>
-      <c r="BJ19" s="21">
-        <f t="shared" si="17"/>
-        <v>30.215</v>
+        <v>37.215000000000003</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.25">
@@ -7261,55 +7912,88 @@
       <c r="D20" s="2">
         <v>0.65</v>
       </c>
-      <c r="G20" s="22">
+      <c r="E20" s="17">
+        <f t="shared" si="24"/>
+        <v>0.98</v>
+      </c>
+      <c r="F20" s="17">
+        <f t="shared" si="25"/>
+        <v>1.58</v>
+      </c>
+      <c r="G20" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I20" s="23">
+        <v>0.98</v>
+      </c>
+      <c r="H20" s="17">
+        <f t="shared" si="26"/>
+        <v>8.875</v>
+      </c>
+      <c r="I20" s="2">
         <v>3.1</v>
       </c>
-      <c r="J20" s="23">
+      <c r="J20" s="2">
         <v>5</v>
       </c>
-      <c r="K20" s="23">
+      <c r="K20" s="2">
         <v>0.3</v>
       </c>
-      <c r="L20" s="23">
-        <v>1</v>
-      </c>
-      <c r="N20" s="22">
+      <c r="L20" s="2">
+        <v>1</v>
+      </c>
+      <c r="M20" s="17">
+        <f t="shared" si="27"/>
+        <v>1.38</v>
+      </c>
+      <c r="N20" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q20" s="22">
+        <v>0.98</v>
+      </c>
+      <c r="O20" s="17">
+        <f t="shared" si="28"/>
+        <v>1.78</v>
+      </c>
+      <c r="P20">
+        <v>18.75</v>
+      </c>
+      <c r="Q20" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.38</v>
+      </c>
+      <c r="R20" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="S20" s="20">
+        <v>1.5</v>
       </c>
       <c r="T20" s="1">
         <f t="shared" si="7"/>
         <v>0.63</v>
       </c>
-      <c r="U20" s="23">
+      <c r="U20" s="2">
         <v>0.44</v>
       </c>
-      <c r="V20" s="23">
+      <c r="V20" s="2">
         <v>2.16</v>
       </c>
-      <c r="W20" s="23">
+      <c r="W20" s="2">
         <v>0.85</v>
       </c>
-      <c r="X20" s="23">
+      <c r="X20" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y20" s="19">
+      <c r="Y20" s="14">
         <v>1.75</v>
       </c>
       <c r="Z20" s="2">
         <v>1.25</v>
       </c>
+      <c r="AA20" s="17">
+        <f t="shared" si="33"/>
+        <v>1.5049999999999999</v>
+      </c>
       <c r="AB20" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.5049999999999999</v>
       </c>
       <c r="AC20" s="1">
         <f t="shared" si="3"/>
@@ -7348,7 +8032,15 @@
       <c r="AM20" s="2">
         <v>1</v>
       </c>
-      <c r="AP20" s="23">
+      <c r="AN20" s="17">
+        <f t="shared" si="30"/>
+        <v>0.504</v>
+      </c>
+      <c r="AO20">
+        <f t="shared" si="31"/>
+        <v>2.6334</v>
+      </c>
+      <c r="AP20">
         <v>0</v>
       </c>
       <c r="AS20">
@@ -7359,59 +8051,59 @@
         <v>17</v>
       </c>
       <c r="AU20">
+        <f t="shared" si="21"/>
+        <v>35.96</v>
+      </c>
+      <c r="AV20">
+        <f t="shared" si="22"/>
+        <v>37.200000000000003</v>
+      </c>
+      <c r="AW20">
+        <f t="shared" si="23"/>
+        <v>1.240000000000002</v>
+      </c>
+      <c r="AY20">
+        <f t="shared" si="11"/>
+        <v>3.1150000000000002</v>
+      </c>
+      <c r="AZ20">
+        <f t="shared" si="12"/>
+        <v>3.8025000000000002</v>
+      </c>
+      <c r="BA20">
+        <f t="shared" si="13"/>
+        <v>11.844787500000001</v>
+      </c>
+      <c r="BB20">
+        <f t="shared" si="14"/>
+        <v>3.83</v>
+      </c>
+      <c r="BC20">
+        <f t="shared" si="15"/>
+        <v>3.88</v>
+      </c>
+      <c r="BD20">
+        <v>14.8</v>
+      </c>
+      <c r="BE20">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="BG20">
+        <f t="shared" si="17"/>
+        <v>3.91</v>
+      </c>
+      <c r="BH20">
         <f t="shared" si="18"/>
-        <v>35.96</v>
-      </c>
-      <c r="AV20">
+        <v>59</v>
+      </c>
+      <c r="BI20">
         <f t="shared" si="19"/>
-        <v>37.200000000000003</v>
-      </c>
-      <c r="AW20" s="21">
+        <v>37.340000000000003</v>
+      </c>
+      <c r="BJ20">
         <f t="shared" si="20"/>
-        <v>1.240000000000002</v>
-      </c>
-      <c r="AY20">
-        <f t="shared" si="8"/>
-        <v>3.1150000000000002</v>
-      </c>
-      <c r="AZ20">
-        <f t="shared" si="9"/>
-        <v>3.8025000000000002</v>
-      </c>
-      <c r="BA20">
-        <f t="shared" si="10"/>
-        <v>11.844787500000001</v>
-      </c>
-      <c r="BB20" s="21">
-        <f t="shared" si="11"/>
-        <v>3.83</v>
-      </c>
-      <c r="BC20" s="21">
-        <f t="shared" si="12"/>
-        <v>3.88</v>
-      </c>
-      <c r="BD20" s="21">
-        <v>14.8</v>
-      </c>
-      <c r="BE20" s="21">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="BG20" s="21">
-        <f t="shared" si="14"/>
-        <v>3.91</v>
-      </c>
-      <c r="BH20" s="21">
-        <f t="shared" si="15"/>
-        <v>40.25</v>
-      </c>
-      <c r="BI20" s="21">
-        <f t="shared" si="16"/>
-        <v>37.340000000000003</v>
-      </c>
-      <c r="BJ20" s="21">
-        <f t="shared" si="17"/>
-        <v>36.340000000000003</v>
+        <v>55.09</v>
       </c>
     </row>
     <row r="21" spans="1:62" x14ac:dyDescent="0.25">
@@ -7428,56 +8120,89 @@
       <c r="D21" s="2">
         <v>0.65</v>
       </c>
-      <c r="G21" s="22">
+      <c r="E21" s="17">
+        <f t="shared" si="24"/>
+        <v>0.95200000000000007</v>
+      </c>
+      <c r="F21" s="17">
+        <f t="shared" si="25"/>
+        <v>1.552</v>
+      </c>
+      <c r="G21" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I21" s="23">
+        <v>0.95200000000000007</v>
+      </c>
+      <c r="H21" s="17">
+        <f t="shared" si="26"/>
+        <v>3</v>
+      </c>
+      <c r="I21" s="2">
         <v>3.1</v>
       </c>
-      <c r="J21" s="23">
+      <c r="J21" s="2">
         <v>5</v>
       </c>
-      <c r="K21" s="23">
+      <c r="K21" s="2">
         <v>0.3</v>
       </c>
-      <c r="L21" s="23">
-        <v>1</v>
-      </c>
-      <c r="N21" s="22">
+      <c r="L21" s="2">
+        <v>1</v>
+      </c>
+      <c r="M21" s="17">
+        <f t="shared" si="27"/>
+        <v>1.3520000000000003</v>
+      </c>
+      <c r="N21" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q21" s="22">
+        <v>0.95200000000000007</v>
+      </c>
+      <c r="O21" s="17">
+        <f t="shared" si="28"/>
+        <v>1.7520000000000002</v>
+      </c>
+      <c r="P21">
+        <v>7</v>
+      </c>
+      <c r="Q21" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.3520000000000003</v>
+      </c>
+      <c r="R21" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="S21" s="20">
+        <v>1.5</v>
       </c>
       <c r="T21" s="1">
         <f t="shared" si="7"/>
         <v>0.63</v>
       </c>
-      <c r="U21" s="23">
+      <c r="U21" s="2">
         <v>0.44</v>
       </c>
-      <c r="V21" s="23">
+      <c r="V21" s="2">
         <v>2.16</v>
       </c>
-      <c r="W21" s="23">
+      <c r="W21" s="2">
         <v>0.85</v>
       </c>
-      <c r="X21" s="23">
+      <c r="X21" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y21" s="20">
+      <c r="Y21" s="15">
         <f>8+3/8</f>
         <v>8.375</v>
       </c>
       <c r="Z21" s="2">
         <v>1.25</v>
       </c>
+      <c r="AA21" s="17">
+        <f>AF21*0.322</f>
+        <v>1.3685</v>
+      </c>
       <c r="AB21" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.3685</v>
       </c>
       <c r="AC21" s="1">
         <f t="shared" si="3"/>
@@ -7515,7 +8240,15 @@
       <c r="AM21" s="2">
         <v>1</v>
       </c>
-      <c r="AP21" s="23">
+      <c r="AN21" s="17">
+        <f t="shared" si="30"/>
+        <v>0.504</v>
+      </c>
+      <c r="AO21">
+        <f t="shared" si="31"/>
+        <v>2.6334</v>
+      </c>
+      <c r="AP21">
         <v>0</v>
       </c>
       <c r="AS21">
@@ -7526,225 +8259,270 @@
         <v>18</v>
       </c>
       <c r="AU21">
+        <f t="shared" si="21"/>
+        <v>33.94</v>
+      </c>
+      <c r="AV21">
+        <f t="shared" si="22"/>
+        <v>35.200000000000003</v>
+      </c>
+      <c r="AW21">
+        <f t="shared" si="23"/>
+        <v>1.2600000000000051</v>
+      </c>
+      <c r="AY21">
+        <f t="shared" si="11"/>
+        <v>2.99</v>
+      </c>
+      <c r="AZ21">
+        <f t="shared" si="12"/>
+        <v>3.5525000000000002</v>
+      </c>
+      <c r="BA21">
+        <f t="shared" si="13"/>
+        <v>10.621975000000001</v>
+      </c>
+      <c r="BB21">
+        <f t="shared" si="14"/>
+        <v>3.66</v>
+      </c>
+      <c r="BC21">
+        <f t="shared" si="15"/>
+        <v>3.68</v>
+      </c>
+      <c r="BD21">
+        <f t="shared" si="32"/>
+        <v>14.8</v>
+      </c>
+      <c r="BE21">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="BG21">
+        <f t="shared" si="17"/>
+        <v>10.535</v>
+      </c>
+      <c r="BH21">
         <f t="shared" si="18"/>
-        <v>33.94</v>
-      </c>
-      <c r="AV21">
+        <v>45.25</v>
+      </c>
+      <c r="BI21">
         <f t="shared" si="19"/>
-        <v>35.200000000000003</v>
-      </c>
-      <c r="AW21" s="21">
+        <v>28.715</v>
+      </c>
+      <c r="BJ21">
         <f t="shared" si="20"/>
-        <v>1.2600000000000051</v>
-      </c>
-      <c r="AY21">
-        <f t="shared" si="8"/>
-        <v>2.99</v>
-      </c>
-      <c r="AZ21">
-        <f t="shared" si="9"/>
-        <v>3.5525000000000002</v>
-      </c>
-      <c r="BA21">
-        <f t="shared" si="10"/>
-        <v>10.621975000000001</v>
-      </c>
-      <c r="BB21" s="21">
-        <f t="shared" si="11"/>
-        <v>3.66</v>
-      </c>
-      <c r="BC21" s="21">
-        <f t="shared" si="12"/>
-        <v>3.68</v>
-      </c>
-      <c r="BD21" s="21">
-        <f t="shared" si="21"/>
-        <v>14.8</v>
-      </c>
-      <c r="BE21" s="21">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="BG21" s="21">
-        <f t="shared" si="14"/>
-        <v>10.535</v>
-      </c>
-      <c r="BH21" s="21">
-        <f t="shared" si="15"/>
-        <v>38.25</v>
-      </c>
-      <c r="BI21" s="21">
-        <f t="shared" si="16"/>
-        <v>28.715</v>
-      </c>
-      <c r="BJ21" s="21">
-        <f t="shared" si="17"/>
-        <v>27.715</v>
+        <v>34.715000000000003</v>
       </c>
     </row>
-    <row r="22" spans="1:62" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
+    <row r="22" spans="1:62" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="8">
         <f t="shared" si="5"/>
         <v>0.63</v>
       </c>
-      <c r="C22" s="10">
+      <c r="C22" s="7">
         <v>4.05</v>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" s="9">
         <v>0.65</v>
       </c>
-      <c r="G22" s="22">
+      <c r="E22" s="17">
+        <f t="shared" si="24"/>
+        <v>0.93100000000000005</v>
+      </c>
+      <c r="F22" s="17">
+        <f t="shared" si="25"/>
+        <v>1.5310000000000001</v>
+      </c>
+      <c r="G22" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I22" s="23">
+        <v>0.93100000000000005</v>
+      </c>
+      <c r="H22" s="17">
+        <f t="shared" si="26"/>
+        <v>8.875</v>
+      </c>
+      <c r="I22" s="2">
         <v>3.1</v>
       </c>
-      <c r="J22" s="23">
+      <c r="J22" s="2">
         <v>5</v>
       </c>
-      <c r="K22" s="23">
+      <c r="K22" s="2">
         <v>0.3</v>
       </c>
-      <c r="L22" s="23">
-        <v>1</v>
-      </c>
-      <c r="N22" s="22">
+      <c r="L22" s="2">
+        <v>1</v>
+      </c>
+      <c r="M22" s="17">
+        <f t="shared" si="27"/>
+        <v>1.331</v>
+      </c>
+      <c r="N22" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q22" s="22">
+        <v>0.93100000000000005</v>
+      </c>
+      <c r="O22" s="17">
+        <f t="shared" si="28"/>
+        <v>1.7310000000000001</v>
+      </c>
+      <c r="P22" s="7">
+        <v>18.75</v>
+      </c>
+      <c r="Q22" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T22" s="11">
+        <v>1.331</v>
+      </c>
+      <c r="R22" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="S22" s="20">
+        <v>1.5</v>
+      </c>
+      <c r="T22" s="8">
         <f t="shared" si="7"/>
         <v>0.63</v>
       </c>
-      <c r="U22" s="23">
+      <c r="U22" s="2">
         <v>0.44</v>
       </c>
-      <c r="V22" s="23">
+      <c r="V22" s="2">
         <v>2.16</v>
       </c>
-      <c r="W22" s="23">
+      <c r="W22" s="2">
         <v>0.85</v>
       </c>
-      <c r="X22" s="23">
+      <c r="X22" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y22" s="19"/>
-      <c r="Z22" s="12">
+      <c r="Y22" s="17">
         <v>1.25</v>
       </c>
-      <c r="AB22" s="11">
+      <c r="Z22" s="9">
+        <v>1.25</v>
+      </c>
+      <c r="AA22" s="17">
+        <f t="shared" ref="AA22:AA24" si="34">AF22*0.322</f>
+        <v>1.3383125</v>
+      </c>
+      <c r="AB22" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC22" s="11">
+        <v>1.3383125</v>
+      </c>
+      <c r="AC22" s="8">
         <f t="shared" si="3"/>
         <v>2.8962500000000002</v>
       </c>
-      <c r="AD22" s="17">
+      <c r="AD22" s="12">
         <f>AD23+(AD21-AD23)/2</f>
         <v>4.6875</v>
       </c>
-      <c r="AE22" s="17">
+      <c r="AE22" s="12">
         <f>AE23+(AE21-AE23)/2</f>
         <v>37</v>
       </c>
-      <c r="AF22" s="17">
+      <c r="AF22" s="12">
         <f>AF23+(AF21-AF23)/2</f>
         <v>4.15625</v>
       </c>
-      <c r="AG22" s="12">
+      <c r="AG22" s="9">
         <v>0.63</v>
       </c>
-      <c r="AH22" s="12">
+      <c r="AH22" s="9">
         <v>1.25</v>
       </c>
-      <c r="AI22" s="12">
+      <c r="AI22" s="9">
         <v>0.7</v>
       </c>
-      <c r="AJ22" s="12">
+      <c r="AJ22" s="9">
         <v>4.0999999999999996</v>
       </c>
-      <c r="AK22" s="12">
-        <v>1</v>
-      </c>
-      <c r="AL22" s="12">
+      <c r="AK22" s="9">
+        <v>1</v>
+      </c>
+      <c r="AL22" s="9">
         <v>0.1</v>
       </c>
-      <c r="AM22" s="12">
-        <v>1</v>
-      </c>
-      <c r="AP22" s="10">
+      <c r="AM22" s="9">
+        <v>1</v>
+      </c>
+      <c r="AN22" s="17">
+        <f t="shared" si="30"/>
+        <v>0.504</v>
+      </c>
+      <c r="AO22">
+        <f t="shared" si="31"/>
+        <v>2.6334</v>
+      </c>
+      <c r="AP22">
         <v>0</v>
       </c>
-      <c r="AS22" s="10">
+      <c r="AQ22"/>
+      <c r="AR22"/>
+      <c r="AS22" s="7">
         <f t="shared" si="4"/>
         <v>1.1278195488721805</v>
       </c>
-      <c r="AT22" s="10">
+      <c r="AT22" s="7">
         <v>19</v>
       </c>
-      <c r="AU22" s="10">
+      <c r="AU22" s="7">
+        <f t="shared" si="21"/>
+        <v>32.04</v>
+      </c>
+      <c r="AV22" s="13">
+        <f t="shared" si="22"/>
+        <v>32.950000000000003</v>
+      </c>
+      <c r="AW22" s="7">
+        <f t="shared" si="23"/>
+        <v>0.91000000000000369</v>
+      </c>
+      <c r="AY22">
+        <f t="shared" si="11"/>
+        <v>2.8962500000000002</v>
+      </c>
+      <c r="AZ22">
+        <f t="shared" si="12"/>
+        <v>3.4275000000000002</v>
+      </c>
+      <c r="BA22">
+        <f t="shared" si="13"/>
+        <v>9.9268968750000006</v>
+      </c>
+      <c r="BB22">
+        <f t="shared" si="14"/>
+        <v>3.53</v>
+      </c>
+      <c r="BC22">
+        <f t="shared" si="15"/>
+        <v>3.56</v>
+      </c>
+      <c r="BD22">
+        <v>15</v>
+      </c>
+      <c r="BE22">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="BG22">
+        <f t="shared" si="17"/>
+        <v>3.41</v>
+      </c>
+      <c r="BH22">
         <f t="shared" si="18"/>
-        <v>32.04</v>
-      </c>
-      <c r="AV22" s="18">
+        <v>54.75</v>
+      </c>
+      <c r="BI22">
         <f t="shared" si="19"/>
-        <v>32.950000000000003</v>
-      </c>
-      <c r="AW22" s="25">
+        <v>33.590000000000003</v>
+      </c>
+      <c r="BJ22">
         <f t="shared" si="20"/>
-        <v>0.91000000000000369</v>
-      </c>
-      <c r="AY22">
-        <f t="shared" si="8"/>
-        <v>2.8962500000000002</v>
-      </c>
-      <c r="AZ22">
-        <f t="shared" si="9"/>
-        <v>3.4275000000000002</v>
-      </c>
-      <c r="BA22">
-        <f t="shared" si="10"/>
-        <v>9.9268968750000006</v>
-      </c>
-      <c r="BB22" s="21">
-        <f t="shared" si="11"/>
-        <v>3.53</v>
-      </c>
-      <c r="BC22" s="21">
-        <f t="shared" si="12"/>
-        <v>3.56</v>
-      </c>
-      <c r="BD22" s="21">
-        <v>15</v>
-      </c>
-      <c r="BE22" s="21">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="BG22" s="21">
-        <f t="shared" si="14"/>
-        <v>2.16</v>
-      </c>
-      <c r="BH22" s="21">
-        <f t="shared" si="15"/>
-        <v>36</v>
-      </c>
-      <c r="BI22" s="21">
-        <f t="shared" si="16"/>
-        <v>34.840000000000003</v>
-      </c>
-      <c r="BJ22" s="21">
-        <f t="shared" si="17"/>
-        <v>33.840000000000003</v>
+        <v>51.34</v>
       </c>
     </row>
     <row r="23" spans="1:62" x14ac:dyDescent="0.25">
@@ -7761,55 +8539,88 @@
       <c r="D23" s="2">
         <v>0.65</v>
       </c>
-      <c r="G23" s="22">
+      <c r="E23" s="17">
+        <f t="shared" si="24"/>
+        <v>0.91</v>
+      </c>
+      <c r="F23" s="17">
+        <f t="shared" si="25"/>
+        <v>1.51</v>
+      </c>
+      <c r="G23" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I23" s="23">
+        <v>0.91</v>
+      </c>
+      <c r="H23" s="17">
+        <f t="shared" si="26"/>
+        <v>3</v>
+      </c>
+      <c r="I23" s="2">
         <v>3.1</v>
       </c>
-      <c r="J23" s="23">
+      <c r="J23" s="2">
         <v>5</v>
       </c>
-      <c r="K23" s="23">
+      <c r="K23" s="2">
         <v>0.3</v>
       </c>
-      <c r="L23" s="23">
-        <v>1</v>
-      </c>
-      <c r="N23" s="22">
+      <c r="L23" s="2">
+        <v>1</v>
+      </c>
+      <c r="M23" s="17">
+        <f t="shared" si="27"/>
+        <v>1.31</v>
+      </c>
+      <c r="N23" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q23" s="22">
+        <v>0.91</v>
+      </c>
+      <c r="O23" s="17">
+        <f t="shared" si="28"/>
+        <v>1.71</v>
+      </c>
+      <c r="P23">
+        <v>7</v>
+      </c>
+      <c r="Q23" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.31</v>
+      </c>
+      <c r="R23" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="S23" s="20">
+        <v>1.5</v>
       </c>
       <c r="T23" s="1">
         <f t="shared" si="7"/>
         <v>0.63</v>
       </c>
-      <c r="U23" s="23">
+      <c r="U23" s="2">
         <v>0.44</v>
       </c>
-      <c r="V23" s="23">
+      <c r="V23" s="2">
         <v>2.16</v>
       </c>
-      <c r="W23" s="23">
+      <c r="W23" s="2">
         <v>0.85</v>
       </c>
-      <c r="X23" s="23">
+      <c r="X23" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y23" s="20">
+      <c r="Y23" s="15">
         <v>5.75</v>
       </c>
       <c r="Z23" s="2">
         <v>1.25</v>
       </c>
+      <c r="AA23" s="17">
+        <f t="shared" si="34"/>
+        <v>1.308125</v>
+      </c>
       <c r="AB23" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.308125</v>
       </c>
       <c r="AC23" s="1">
         <f t="shared" si="3"/>
@@ -7847,7 +8658,15 @@
       <c r="AM23" s="2">
         <v>1</v>
       </c>
-      <c r="AP23" s="23">
+      <c r="AN23" s="17">
+        <f t="shared" si="30"/>
+        <v>0.504</v>
+      </c>
+      <c r="AO23">
+        <f t="shared" si="31"/>
+        <v>2.6334</v>
+      </c>
+      <c r="AP23">
         <v>0</v>
       </c>
       <c r="AS23">
@@ -7858,59 +8677,59 @@
         <v>20</v>
       </c>
       <c r="AU23">
+        <f t="shared" si="21"/>
+        <v>30.24</v>
+      </c>
+      <c r="AV23">
+        <f t="shared" si="22"/>
+        <v>31.05</v>
+      </c>
+      <c r="AW23">
+        <f t="shared" si="23"/>
+        <v>0.81000000000000227</v>
+      </c>
+      <c r="AY23">
+        <f t="shared" si="11"/>
+        <v>2.8025000000000002</v>
+      </c>
+      <c r="AZ23">
+        <f t="shared" si="12"/>
+        <v>3.3025000000000002</v>
+      </c>
+      <c r="BA23">
+        <f t="shared" si="13"/>
+        <v>9.2552562500000022</v>
+      </c>
+      <c r="BB23">
+        <f t="shared" si="14"/>
+        <v>3.41</v>
+      </c>
+      <c r="BC23">
+        <f t="shared" si="15"/>
+        <v>3.43</v>
+      </c>
+      <c r="BD23">
+        <v>15.2</v>
+      </c>
+      <c r="BE23">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="BG23">
+        <f t="shared" si="17"/>
+        <v>7.91</v>
+      </c>
+      <c r="BH23">
         <f t="shared" si="18"/>
-        <v>30.24</v>
-      </c>
-      <c r="AV23">
+        <v>40.75</v>
+      </c>
+      <c r="BI23">
         <f t="shared" si="19"/>
-        <v>31.05</v>
-      </c>
-      <c r="AW23" s="21">
+        <v>26.84</v>
+      </c>
+      <c r="BJ23">
         <f t="shared" si="20"/>
-        <v>0.81000000000000227</v>
-      </c>
-      <c r="AY23">
-        <f t="shared" si="8"/>
-        <v>2.8025000000000002</v>
-      </c>
-      <c r="AZ23">
-        <f t="shared" si="9"/>
-        <v>3.3025000000000002</v>
-      </c>
-      <c r="BA23">
-        <f t="shared" si="10"/>
-        <v>9.2552562500000022</v>
-      </c>
-      <c r="BB23" s="21">
-        <f t="shared" si="11"/>
-        <v>3.41</v>
-      </c>
-      <c r="BC23" s="21">
-        <f t="shared" si="12"/>
-        <v>3.43</v>
-      </c>
-      <c r="BD23" s="21">
-        <v>15.2</v>
-      </c>
-      <c r="BE23" s="21">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="BG23" s="21">
-        <f t="shared" si="14"/>
-        <v>7.91</v>
-      </c>
-      <c r="BH23" s="21">
-        <f t="shared" si="15"/>
-        <v>33.75</v>
-      </c>
-      <c r="BI23" s="21">
-        <f t="shared" si="16"/>
-        <v>26.84</v>
-      </c>
-      <c r="BJ23" s="21">
-        <f t="shared" si="17"/>
-        <v>25.84</v>
+        <v>32.840000000000003</v>
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.25">
@@ -7927,55 +8746,88 @@
       <c r="D24" s="2">
         <v>0.65</v>
       </c>
-      <c r="G24" s="22">
+      <c r="E24" s="17">
+        <f t="shared" si="24"/>
+        <v>0.89600000000000002</v>
+      </c>
+      <c r="F24" s="17">
+        <f t="shared" si="25"/>
+        <v>1.496</v>
+      </c>
+      <c r="G24" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I24" s="23">
+        <v>0.89600000000000002</v>
+      </c>
+      <c r="H24" s="17">
+        <f t="shared" si="26"/>
+        <v>8.875</v>
+      </c>
+      <c r="I24" s="2">
         <v>3.1</v>
       </c>
-      <c r="J24" s="23">
+      <c r="J24" s="2">
         <v>5</v>
       </c>
-      <c r="K24" s="23">
+      <c r="K24" s="2">
         <v>0.3</v>
       </c>
-      <c r="L24" s="23">
-        <v>1</v>
-      </c>
-      <c r="N24" s="22">
+      <c r="L24" s="2">
+        <v>1</v>
+      </c>
+      <c r="M24" s="17">
+        <f t="shared" si="27"/>
+        <v>1.2960000000000003</v>
+      </c>
+      <c r="N24" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q24" s="22">
+        <v>0.89600000000000002</v>
+      </c>
+      <c r="O24" s="17">
+        <f t="shared" si="28"/>
+        <v>1.6960000000000002</v>
+      </c>
+      <c r="P24">
+        <v>18.75</v>
+      </c>
+      <c r="Q24" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.2960000000000003</v>
+      </c>
+      <c r="R24" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="S24" s="20">
+        <v>1.5</v>
       </c>
       <c r="T24" s="1">
         <f t="shared" si="7"/>
         <v>0.63</v>
       </c>
-      <c r="U24" s="23">
+      <c r="U24" s="2">
         <v>0.44</v>
       </c>
-      <c r="V24" s="23">
+      <c r="V24" s="2">
         <v>2.16</v>
       </c>
-      <c r="W24" s="23">
+      <c r="W24" s="2">
         <v>0.85</v>
       </c>
-      <c r="X24" s="23">
+      <c r="X24" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y24" s="19">
+      <c r="Y24" s="14">
         <v>0.75</v>
       </c>
       <c r="Z24" s="2">
         <v>1</v>
+      </c>
+      <c r="AA24" s="17">
+        <f t="shared" si="34"/>
+        <v>1.288</v>
       </c>
       <c r="AB24" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.288</v>
       </c>
       <c r="AC24" s="1">
         <f t="shared" si="3"/>
@@ -8014,7 +8866,15 @@
       <c r="AM24" s="2">
         <v>1</v>
       </c>
-      <c r="AP24" s="23">
+      <c r="AN24" s="17">
+        <f t="shared" si="30"/>
+        <v>0.504</v>
+      </c>
+      <c r="AO24">
+        <f t="shared" si="31"/>
+        <v>2.6334</v>
+      </c>
+      <c r="AP24">
         <v>0</v>
       </c>
       <c r="AS24">
@@ -8025,60 +8885,60 @@
         <v>21</v>
       </c>
       <c r="AU24">
+        <f t="shared" si="21"/>
+        <v>28.54</v>
+      </c>
+      <c r="AV24">
+        <f t="shared" si="22"/>
+        <v>29.425000000000001</v>
+      </c>
+      <c r="AW24">
+        <f t="shared" si="23"/>
+        <v>0.88500000000000156</v>
+      </c>
+      <c r="AY24">
+        <f t="shared" si="11"/>
+        <v>2.74</v>
+      </c>
+      <c r="AZ24">
+        <f t="shared" si="12"/>
+        <v>3.1150000000000002</v>
+      </c>
+      <c r="BA24">
+        <f t="shared" si="13"/>
+        <v>8.5351000000000017</v>
+      </c>
+      <c r="BB24">
+        <f t="shared" si="14"/>
+        <v>3.26</v>
+      </c>
+      <c r="BC24">
+        <f t="shared" si="15"/>
+        <v>3.3</v>
+      </c>
+      <c r="BD24">
+        <f t="shared" si="32"/>
+        <v>15.2</v>
+      </c>
+      <c r="BE24">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="BG24">
+        <f t="shared" si="17"/>
+        <v>2.91</v>
+      </c>
+      <c r="BH24">
         <f t="shared" si="18"/>
-        <v>28.54</v>
-      </c>
-      <c r="AV24">
+        <v>50.875</v>
+      </c>
+      <c r="BI24">
         <f t="shared" si="19"/>
-        <v>29.425000000000001</v>
-      </c>
-      <c r="AW24" s="21">
+        <v>30.215</v>
+      </c>
+      <c r="BJ24">
         <f t="shared" si="20"/>
-        <v>0.88500000000000156</v>
-      </c>
-      <c r="AY24">
-        <f t="shared" si="8"/>
-        <v>2.74</v>
-      </c>
-      <c r="AZ24">
-        <f t="shared" si="9"/>
-        <v>3.1150000000000002</v>
-      </c>
-      <c r="BA24">
-        <f t="shared" si="10"/>
-        <v>8.5351000000000017</v>
-      </c>
-      <c r="BB24" s="21">
-        <f t="shared" si="11"/>
-        <v>3.26</v>
-      </c>
-      <c r="BC24" s="21">
-        <f t="shared" si="12"/>
-        <v>3.3</v>
-      </c>
-      <c r="BD24" s="21">
-        <f t="shared" si="21"/>
-        <v>15.2</v>
-      </c>
-      <c r="BE24" s="21">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="BG24" s="21">
-        <f t="shared" si="14"/>
-        <v>2.91</v>
-      </c>
-      <c r="BH24" s="21">
-        <f t="shared" si="15"/>
-        <v>32.125</v>
-      </c>
-      <c r="BI24" s="21">
-        <f t="shared" si="16"/>
-        <v>30.215</v>
-      </c>
-      <c r="BJ24" s="21">
-        <f t="shared" si="17"/>
-        <v>29.215</v>
+        <v>47.965000000000003</v>
       </c>
     </row>
     <row r="25" spans="1:62" x14ac:dyDescent="0.25">
@@ -8101,29 +8961,30 @@
       <c r="F25">
         <v>1.41</v>
       </c>
-      <c r="G25" s="22">
+      <c r="G25" s="1">
         <f t="shared" si="0"/>
         <v>0.85</v>
       </c>
       <c r="H25">
-        <v>3.03</v>
-      </c>
-      <c r="I25" s="23">
+        <f t="shared" si="26"/>
+        <v>3</v>
+      </c>
+      <c r="I25" s="2">
         <v>3.1</v>
       </c>
-      <c r="J25" s="23">
+      <c r="J25" s="2">
         <v>5</v>
       </c>
-      <c r="K25" s="23">
+      <c r="K25" s="2">
         <v>0.3</v>
       </c>
-      <c r="L25" s="23">
-        <v>1</v>
-      </c>
-      <c r="M25">
+      <c r="L25" s="2">
+        <v>1</v>
+      </c>
+      <c r="M25" s="19">
         <v>1.26</v>
       </c>
-      <c r="N25" s="22">
+      <c r="N25" s="1">
         <f t="shared" si="6"/>
         <v>0.85</v>
       </c>
@@ -8131,9 +8992,9 @@
         <v>1.54</v>
       </c>
       <c r="P25">
-        <v>6.94</v>
-      </c>
-      <c r="Q25" s="22">
+        <v>7</v>
+      </c>
+      <c r="Q25" s="1">
         <f t="shared" si="1"/>
         <v>1.26</v>
       </c>
@@ -8147,19 +9008,19 @@
         <f t="shared" si="7"/>
         <v>0.56999999999999995</v>
       </c>
-      <c r="U25" s="23">
+      <c r="U25" s="2">
         <v>0.44</v>
       </c>
-      <c r="V25" s="23">
+      <c r="V25" s="2">
         <v>2.16</v>
       </c>
-      <c r="W25" s="23">
+      <c r="W25" s="2">
         <v>0.85</v>
       </c>
-      <c r="X25" s="23">
+      <c r="X25" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y25" s="20">
+      <c r="Y25" s="15">
         <v>4.43</v>
       </c>
       <c r="Z25" s="2">
@@ -8212,7 +9073,7 @@
       <c r="AO25">
         <v>2.5</v>
       </c>
-      <c r="AP25" s="23">
+      <c r="AP25">
         <v>0</v>
       </c>
       <c r="AS25">
@@ -8223,166 +9084,209 @@
         <v>22</v>
       </c>
       <c r="AU25">
+        <f t="shared" si="21"/>
+        <v>26.94</v>
+      </c>
+      <c r="AV25">
+        <f t="shared" si="22"/>
+        <v>27.43</v>
+      </c>
+      <c r="AW25">
+        <f t="shared" si="23"/>
+        <v>0.48999999999999844</v>
+      </c>
+      <c r="AY25">
+        <f t="shared" si="11"/>
+        <v>2.6399999999999997</v>
+      </c>
+      <c r="AZ25">
+        <f t="shared" si="12"/>
+        <v>3.0300000000000002</v>
+      </c>
+      <c r="BA25">
+        <f t="shared" si="13"/>
+        <v>7.9992000000000001</v>
+      </c>
+      <c r="BB25">
+        <f t="shared" si="14"/>
+        <v>3.18</v>
+      </c>
+      <c r="BC25">
+        <f t="shared" si="15"/>
+        <v>3.19</v>
+      </c>
+      <c r="BD25">
+        <v>15.5</v>
+      </c>
+      <c r="BE25">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="BG25">
+        <f t="shared" si="17"/>
+        <v>6.59</v>
+      </c>
+      <c r="BH25">
         <f t="shared" si="18"/>
-        <v>26.94</v>
-      </c>
-      <c r="AV25">
+        <v>37.129999999999995</v>
+      </c>
+      <c r="BI25">
         <f t="shared" si="19"/>
-        <v>27.43</v>
-      </c>
-      <c r="AW25" s="21">
+        <v>24.54</v>
+      </c>
+      <c r="BJ25">
         <f t="shared" si="20"/>
-        <v>0.48999999999999844</v>
-      </c>
-      <c r="AY25">
-        <f t="shared" si="8"/>
-        <v>2.6399999999999997</v>
-      </c>
-      <c r="AZ25">
-        <f t="shared" si="9"/>
-        <v>3.0300000000000002</v>
-      </c>
-      <c r="BA25">
-        <f t="shared" si="10"/>
-        <v>7.9992000000000001</v>
-      </c>
-      <c r="BB25" s="21">
-        <f t="shared" si="11"/>
-        <v>3.18</v>
-      </c>
-      <c r="BC25" s="21">
-        <f t="shared" si="12"/>
-        <v>3.19</v>
-      </c>
-      <c r="BD25" s="21">
-        <v>15.5</v>
-      </c>
-      <c r="BE25" s="21">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="BG25" s="21">
-        <f t="shared" si="14"/>
-        <v>6.59</v>
-      </c>
-      <c r="BH25" s="21">
-        <f t="shared" si="15"/>
-        <v>37.07</v>
-      </c>
-      <c r="BI25" s="21">
-        <f t="shared" si="16"/>
-        <v>24.54</v>
-      </c>
-      <c r="BJ25" s="21">
-        <f t="shared" si="17"/>
-        <v>30.48</v>
+        <v>30.539999999999996</v>
       </c>
     </row>
-    <row r="26" spans="1:62" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
+    <row r="26" spans="1:62" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B26" s="9">
+      <c r="B26" s="6">
         <f t="shared" si="5"/>
         <v>0.56999999999999995</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="3">
         <v>3.7</v>
       </c>
-      <c r="D26" s="5">
+      <c r="D26" s="4">
         <v>0.65</v>
       </c>
-      <c r="G26" s="22">
+      <c r="E26" s="17">
+        <f t="shared" si="24"/>
+        <v>0.79800000000000004</v>
+      </c>
+      <c r="F26" s="3">
+        <f>E26+0.6</f>
+        <v>1.3980000000000001</v>
+      </c>
+      <c r="G26" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I26" s="23">
+        <v>0.79800000000000004</v>
+      </c>
+      <c r="H26" s="17">
+        <f t="shared" si="26"/>
+        <v>8.875</v>
+      </c>
+      <c r="I26" s="2">
         <v>3.1</v>
       </c>
-      <c r="J26" s="23">
+      <c r="J26" s="2">
         <v>5</v>
       </c>
-      <c r="K26" s="23">
+      <c r="K26" s="2">
         <v>0.3</v>
       </c>
-      <c r="L26" s="23">
-        <v>1</v>
-      </c>
-      <c r="N26" s="22">
+      <c r="L26" s="2">
+        <v>1</v>
+      </c>
+      <c r="M26" s="18">
+        <f>O26-0.4</f>
+        <v>1.0979999999999999</v>
+      </c>
+      <c r="N26" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q26" s="22">
+        <v>0.79800000000000004</v>
+      </c>
+      <c r="O26" s="18">
+        <f>E26+0.7</f>
+        <v>1.498</v>
+      </c>
+      <c r="P26" s="3">
+        <v>18.75</v>
+      </c>
+      <c r="Q26" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T26" s="9">
+        <v>1.0979999999999999</v>
+      </c>
+      <c r="R26" s="18">
+        <v>1.3</v>
+      </c>
+      <c r="S26" s="18">
+        <v>1.3</v>
+      </c>
+      <c r="T26" s="6">
         <f t="shared" si="7"/>
         <v>0.56999999999999995</v>
       </c>
-      <c r="U26" s="23">
+      <c r="U26" s="2">
         <v>0.44</v>
       </c>
-      <c r="V26" s="23">
+      <c r="V26" s="2">
         <v>2.16</v>
       </c>
-      <c r="W26" s="23">
+      <c r="W26" s="2">
         <v>0.85</v>
       </c>
-      <c r="X26" s="23">
+      <c r="X26" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y26" s="19">
+      <c r="Y26" s="14">
         <f>5/8</f>
         <v>0.625</v>
       </c>
-      <c r="Z26" s="5">
-        <v>1</v>
-      </c>
-      <c r="AB26" s="9">
+      <c r="Z26" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA26" s="18">
+        <f>AF26*0.311</f>
+        <v>1.1079375</v>
+      </c>
+      <c r="AB26" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC26" s="9">
+        <v>1.1079375</v>
+      </c>
+      <c r="AC26" s="6">
         <f t="shared" si="3"/>
         <v>2.4225000000000003</v>
       </c>
-      <c r="AD26" s="4">
+      <c r="AD26" s="3">
         <v>4</v>
       </c>
-      <c r="AE26" s="4">
+      <c r="AE26" s="3">
         <f>29+5/8</f>
         <v>29.625</v>
       </c>
-      <c r="AF26" s="4">
+      <c r="AF26" s="3">
         <f>3+9/16</f>
         <v>3.5625</v>
       </c>
-      <c r="AG26" s="5">
+      <c r="AG26" s="4">
         <v>0.56999999999999995</v>
       </c>
-      <c r="AH26" s="5">
+      <c r="AH26" s="4">
         <v>1.25</v>
       </c>
-      <c r="AI26" s="5">
+      <c r="AI26" s="4">
         <v>0.7</v>
       </c>
-      <c r="AJ26" s="5">
+      <c r="AJ26" s="4">
         <v>4.0999999999999996</v>
       </c>
-      <c r="AK26" s="5">
-        <v>1</v>
-      </c>
-      <c r="AL26" s="5">
+      <c r="AK26" s="4">
+        <v>1</v>
+      </c>
+      <c r="AL26" s="4">
         <v>0.1</v>
       </c>
-      <c r="AM26" s="5">
-        <v>1</v>
-      </c>
-      <c r="AP26" s="4">
+      <c r="AM26" s="4">
+        <v>1</v>
+      </c>
+      <c r="AN26" s="18">
+        <f>AG26*0.8</f>
+        <v>0.45599999999999996</v>
+      </c>
+      <c r="AO26" s="3">
+        <f>AG26*4.18</f>
+        <v>2.3825999999999996</v>
+      </c>
+      <c r="AP26">
         <v>0</v>
       </c>
-      <c r="AS26" s="4">
+      <c r="AQ26"/>
+      <c r="AR26"/>
+      <c r="AS26" s="3">
         <f t="shared" si="4"/>
         <v>1.1228070175438596</v>
       </c>
@@ -8390,224 +9294,269 @@
         <v>23</v>
       </c>
       <c r="AU26">
+        <f t="shared" si="21"/>
+        <v>25.43</v>
+      </c>
+      <c r="AV26">
+        <f t="shared" si="22"/>
+        <v>25.925000000000001</v>
+      </c>
+      <c r="AW26">
+        <f t="shared" si="23"/>
+        <v>0.49500000000000099</v>
+      </c>
+      <c r="AY26">
+        <f t="shared" si="11"/>
+        <v>2.4225000000000003</v>
+      </c>
+      <c r="AZ26">
+        <f t="shared" si="12"/>
+        <v>2.8600000000000003</v>
+      </c>
+      <c r="BA26">
+        <f t="shared" si="13"/>
+        <v>6.9283500000000018</v>
+      </c>
+      <c r="BB26">
+        <f t="shared" si="14"/>
+        <v>2.94</v>
+      </c>
+      <c r="BC26">
+        <f t="shared" si="15"/>
+        <v>2.97</v>
+      </c>
+      <c r="BD26">
+        <v>15</v>
+      </c>
+      <c r="BE26">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="BG26">
+        <f t="shared" si="17"/>
+        <v>2.7850000000000001</v>
+      </c>
+      <c r="BH26">
         <f t="shared" si="18"/>
-        <v>25.43</v>
-      </c>
-      <c r="AV26">
+        <v>47.375</v>
+      </c>
+      <c r="BI26">
         <f t="shared" si="19"/>
-        <v>25.925000000000001</v>
-      </c>
-      <c r="AW26" s="21">
+        <v>26.84</v>
+      </c>
+      <c r="BJ26">
         <f t="shared" si="20"/>
-        <v>0.49500000000000099</v>
-      </c>
-      <c r="AY26">
-        <f t="shared" si="8"/>
-        <v>2.4225000000000003</v>
-      </c>
-      <c r="AZ26">
-        <f t="shared" si="9"/>
-        <v>2.8600000000000003</v>
-      </c>
-      <c r="BA26">
-        <f t="shared" si="10"/>
-        <v>6.9283500000000018</v>
-      </c>
-      <c r="BB26" s="21">
-        <f t="shared" si="11"/>
-        <v>2.94</v>
-      </c>
-      <c r="BC26" s="21">
-        <f t="shared" si="12"/>
-        <v>2.97</v>
-      </c>
-      <c r="BD26" s="21">
-        <v>15</v>
-      </c>
-      <c r="BE26" s="21">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="BG26" s="21">
-        <f t="shared" si="14"/>
-        <v>2.7850000000000001</v>
-      </c>
-      <c r="BH26" s="21">
-        <f t="shared" si="15"/>
-        <v>28.625</v>
-      </c>
-      <c r="BI26" s="21">
-        <f t="shared" si="16"/>
-        <v>26.84</v>
-      </c>
-      <c r="BJ26" s="21">
-        <f t="shared" si="17"/>
-        <v>25.84</v>
+        <v>44.59</v>
       </c>
     </row>
-    <row r="27" spans="1:62" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="13" t="s">
+    <row r="27" spans="1:62" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B27" s="14">
+      <c r="B27" s="10">
         <f t="shared" si="5"/>
         <v>0.5</v>
       </c>
-      <c r="C27" s="13">
+      <c r="C27" s="7">
         <v>3.45</v>
       </c>
-      <c r="D27" s="12">
+      <c r="D27" s="9">
         <v>0.65</v>
       </c>
-      <c r="G27" s="22">
+      <c r="E27" s="17">
+        <f t="shared" si="24"/>
+        <v>0.77700000000000002</v>
+      </c>
+      <c r="F27" s="3">
+        <f t="shared" ref="F27:F34" si="35">E27+0.6</f>
+        <v>1.377</v>
+      </c>
+      <c r="G27" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I27" s="23">
+        <v>0.77700000000000002</v>
+      </c>
+      <c r="H27" s="17">
+        <f t="shared" si="26"/>
+        <v>3</v>
+      </c>
+      <c r="I27" s="2">
         <v>3.1</v>
       </c>
-      <c r="J27" s="23">
+      <c r="J27" s="2">
         <v>5</v>
       </c>
-      <c r="K27" s="23">
+      <c r="K27" s="2">
         <v>0.3</v>
       </c>
-      <c r="L27" s="23">
-        <v>1</v>
-      </c>
-      <c r="N27" s="22">
+      <c r="L27" s="2">
+        <v>1</v>
+      </c>
+      <c r="M27" s="18">
+        <f t="shared" ref="M27:M34" si="36">O27-0.4</f>
+        <v>1.077</v>
+      </c>
+      <c r="N27" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q27" s="22">
+        <v>0.77700000000000002</v>
+      </c>
+      <c r="O27" s="18">
+        <f t="shared" ref="O27:O34" si="37">E27+0.7</f>
+        <v>1.4769999999999999</v>
+      </c>
+      <c r="P27" s="7">
+        <v>7</v>
+      </c>
+      <c r="Q27" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T27" s="14">
+        <v>1.077</v>
+      </c>
+      <c r="R27" s="18">
+        <v>1.3</v>
+      </c>
+      <c r="S27" s="18">
+        <v>1.3</v>
+      </c>
+      <c r="T27" s="10">
         <f t="shared" si="7"/>
         <v>0.5</v>
       </c>
-      <c r="U27" s="23">
+      <c r="U27" s="2">
         <v>0.44</v>
       </c>
-      <c r="V27" s="23">
+      <c r="V27" s="2">
         <v>2.16</v>
       </c>
-      <c r="W27" s="23">
+      <c r="W27" s="2">
         <v>0.85</v>
       </c>
-      <c r="X27" s="23">
+      <c r="X27" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y27" s="20"/>
-      <c r="Z27" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB27" s="14">
+      <c r="Y27" s="17">
+        <v>3</v>
+      </c>
+      <c r="Z27" s="9">
+        <v>1</v>
+      </c>
+      <c r="AA27" s="18">
+        <f t="shared" ref="AA27:AA34" si="38">AF27*0.311</f>
+        <v>1.07878125</v>
+      </c>
+      <c r="AB27" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC27" s="14">
+        <v>1.07878125</v>
+      </c>
+      <c r="AC27" s="10">
         <f t="shared" si="3"/>
         <v>2.46875</v>
       </c>
-      <c r="AD27" s="26">
+      <c r="AD27" s="12">
         <f>AD28+(AD26-AD28)/2</f>
         <v>3.875</v>
       </c>
-      <c r="AE27" s="26">
+      <c r="AE27" s="12">
         <f>AE28+(AE26-AE28)/2</f>
         <v>28.0625</v>
       </c>
-      <c r="AF27" s="26">
+      <c r="AF27" s="12">
         <f>AF28+(AF26-AF28)/2</f>
         <v>3.46875</v>
       </c>
-      <c r="AG27" s="12">
+      <c r="AG27" s="9">
         <v>0.5</v>
       </c>
-      <c r="AH27" s="12">
+      <c r="AH27" s="9">
         <v>1.25</v>
       </c>
-      <c r="AI27" s="12">
+      <c r="AI27" s="9">
         <v>0.7</v>
       </c>
-      <c r="AJ27" s="12">
+      <c r="AJ27" s="9">
         <v>4.0999999999999996</v>
       </c>
-      <c r="AK27" s="15">
-        <v>1</v>
-      </c>
-      <c r="AL27" s="15">
+      <c r="AK27" s="9">
+        <v>1</v>
+      </c>
+      <c r="AL27" s="9">
         <v>0.1</v>
       </c>
-      <c r="AM27" s="15">
-        <v>1</v>
-      </c>
-      <c r="AP27" s="13">
+      <c r="AM27" s="9">
+        <v>1</v>
+      </c>
+      <c r="AN27" s="18">
+        <f t="shared" ref="AN27:AN34" si="39">AG27*0.8</f>
+        <v>0.4</v>
+      </c>
+      <c r="AO27" s="3">
+        <f t="shared" ref="AO27:AO34" si="40">AG27*4.18</f>
+        <v>2.09</v>
+      </c>
+      <c r="AP27">
         <v>0</v>
       </c>
-      <c r="AS27" s="10">
+      <c r="AQ27"/>
+      <c r="AR27"/>
+      <c r="AS27" s="7">
         <f t="shared" si="4"/>
         <v>1.117117117117117</v>
       </c>
-      <c r="AT27" s="10">
+      <c r="AT27" s="7">
         <v>24</v>
       </c>
-      <c r="AU27" s="10">
+      <c r="AU27" s="7">
+        <f t="shared" si="21"/>
+        <v>24</v>
+      </c>
+      <c r="AV27" s="13">
+        <f t="shared" si="22"/>
+        <v>24.612500000000001</v>
+      </c>
+      <c r="AW27" s="7">
+        <f t="shared" si="23"/>
+        <v>0.61250000000000071</v>
+      </c>
+      <c r="AY27">
+        <f t="shared" si="11"/>
+        <v>2.46875</v>
+      </c>
+      <c r="AZ27">
+        <f t="shared" si="12"/>
+        <v>2.875</v>
+      </c>
+      <c r="BA27">
+        <f t="shared" si="13"/>
+        <v>7.09765625</v>
+      </c>
+      <c r="BB27">
+        <f t="shared" si="14"/>
+        <v>3.01</v>
+      </c>
+      <c r="BC27">
+        <f t="shared" si="15"/>
+        <v>3.01</v>
+      </c>
+      <c r="BD27">
+        <v>16</v>
+      </c>
+      <c r="BE27">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="BG27">
+        <f t="shared" si="17"/>
+        <v>5.16</v>
+      </c>
+      <c r="BH27">
         <f t="shared" si="18"/>
-        <v>24</v>
-      </c>
-      <c r="AV27" s="18">
+        <v>34.0625</v>
+      </c>
+      <c r="BI27">
         <f t="shared" si="19"/>
-        <v>24.612500000000001</v>
-      </c>
-      <c r="AW27" s="25">
+        <v>22.9025</v>
+      </c>
+      <c r="BJ27">
         <f t="shared" si="20"/>
-        <v>0.61250000000000071</v>
-      </c>
-      <c r="AY27">
-        <f t="shared" si="8"/>
-        <v>2.46875</v>
-      </c>
-      <c r="AZ27">
-        <f t="shared" si="9"/>
-        <v>2.875</v>
-      </c>
-      <c r="BA27">
-        <f t="shared" si="10"/>
-        <v>7.09765625</v>
-      </c>
-      <c r="BB27" s="21">
-        <f t="shared" si="11"/>
-        <v>3.01</v>
-      </c>
-      <c r="BC27" s="21">
-        <f t="shared" si="12"/>
-        <v>3.01</v>
-      </c>
-      <c r="BD27" s="21">
-        <v>16</v>
-      </c>
-      <c r="BE27" s="21">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="BG27" s="21">
-        <f t="shared" si="14"/>
-        <v>2.16</v>
-      </c>
-      <c r="BH27" s="21">
-        <f t="shared" si="15"/>
-        <v>27.0625</v>
-      </c>
-      <c r="BI27" s="21">
-        <f t="shared" si="16"/>
-        <v>25.9025</v>
-      </c>
-      <c r="BJ27" s="21">
-        <f t="shared" si="17"/>
-        <v>24.9025</v>
+        <v>28.9025</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.25">
@@ -8618,62 +9567,95 @@
         <f t="shared" si="5"/>
         <v>0.49</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28">
         <v>3.45</v>
       </c>
       <c r="D28" s="2">
         <v>0.65</v>
       </c>
-      <c r="G28" s="22">
+      <c r="E28" s="17">
+        <f t="shared" si="24"/>
+        <v>0.75600000000000001</v>
+      </c>
+      <c r="F28" s="3">
+        <f t="shared" si="35"/>
+        <v>1.3559999999999999</v>
+      </c>
+      <c r="G28" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I28" s="23">
+        <v>0.75600000000000001</v>
+      </c>
+      <c r="H28" s="17">
+        <f t="shared" si="26"/>
+        <v>8.875</v>
+      </c>
+      <c r="I28" s="2">
         <v>3.1</v>
       </c>
-      <c r="J28" s="23">
+      <c r="J28" s="2">
         <v>5</v>
       </c>
-      <c r="K28" s="23">
+      <c r="K28" s="2">
         <v>0.3</v>
       </c>
-      <c r="L28" s="23">
-        <v>1</v>
-      </c>
-      <c r="N28" s="22">
+      <c r="L28" s="2">
+        <v>1</v>
+      </c>
+      <c r="M28" s="18">
+        <f t="shared" si="36"/>
+        <v>1.056</v>
+      </c>
+      <c r="N28" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q28" s="22">
+        <v>0.75600000000000001</v>
+      </c>
+      <c r="O28" s="18">
+        <f t="shared" si="37"/>
+        <v>1.456</v>
+      </c>
+      <c r="P28" s="16">
+        <v>18.75</v>
+      </c>
+      <c r="Q28" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.056</v>
+      </c>
+      <c r="R28" s="18">
+        <v>1.3</v>
+      </c>
+      <c r="S28" s="18">
+        <v>1.3</v>
       </c>
       <c r="T28" s="1">
         <f t="shared" si="7"/>
         <v>0.49</v>
       </c>
-      <c r="U28" s="23">
+      <c r="U28" s="2">
         <v>0.44</v>
       </c>
-      <c r="V28" s="23">
+      <c r="V28" s="2">
         <v>2.16</v>
       </c>
-      <c r="W28" s="23">
+      <c r="W28" s="2">
         <v>0.85</v>
       </c>
-      <c r="X28" s="23">
+      <c r="X28" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y28" s="19">
+      <c r="Y28" s="14">
         <f>3/8</f>
         <v>0.375</v>
       </c>
       <c r="Z28" s="2">
         <v>1</v>
       </c>
+      <c r="AA28" s="18">
+        <f t="shared" si="38"/>
+        <v>1.049625</v>
+      </c>
       <c r="AB28" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.049625</v>
       </c>
       <c r="AC28" s="1">
         <f t="shared" si="3"/>
@@ -8710,7 +9692,15 @@
       <c r="AM28" s="2">
         <v>1</v>
       </c>
-      <c r="AP28" s="23">
+      <c r="AN28" s="18">
+        <f t="shared" si="39"/>
+        <v>0.39200000000000002</v>
+      </c>
+      <c r="AO28" s="3">
+        <f t="shared" si="40"/>
+        <v>2.0482</v>
+      </c>
+      <c r="AP28">
         <v>0</v>
       </c>
       <c r="AS28">
@@ -8721,223 +9711,268 @@
         <v>25</v>
       </c>
       <c r="AU28">
+        <f t="shared" si="21"/>
+        <v>22.65</v>
+      </c>
+      <c r="AV28">
+        <f t="shared" si="22"/>
+        <v>23.05</v>
+      </c>
+      <c r="AW28">
+        <f t="shared" si="23"/>
+        <v>0.40000000000000213</v>
+      </c>
+      <c r="AY28">
+        <f t="shared" si="11"/>
+        <v>2.395</v>
+      </c>
+      <c r="AZ28">
+        <f t="shared" si="12"/>
+        <v>2.77</v>
+      </c>
+      <c r="BA28">
+        <f t="shared" si="13"/>
+        <v>6.63415</v>
+      </c>
+      <c r="BB28">
+        <f t="shared" si="14"/>
+        <v>2.88</v>
+      </c>
+      <c r="BC28">
+        <f t="shared" si="15"/>
+        <v>2.91</v>
+      </c>
+      <c r="BD28">
+        <f t="shared" si="32"/>
+        <v>16</v>
+      </c>
+      <c r="BE28">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="BG28">
+        <f t="shared" si="17"/>
+        <v>2.5350000000000001</v>
+      </c>
+      <c r="BH28">
         <f t="shared" si="18"/>
-        <v>22.65</v>
-      </c>
-      <c r="AV28">
+        <v>44.25</v>
+      </c>
+      <c r="BI28">
         <f t="shared" si="19"/>
-        <v>23.05</v>
-      </c>
-      <c r="AW28" s="21">
+        <v>23.965</v>
+      </c>
+      <c r="BJ28">
         <f t="shared" si="20"/>
-        <v>0.40000000000000213</v>
-      </c>
-      <c r="AY28">
-        <f t="shared" si="8"/>
-        <v>2.395</v>
-      </c>
-      <c r="AZ28">
-        <f t="shared" si="9"/>
-        <v>2.77</v>
-      </c>
-      <c r="BA28">
-        <f t="shared" si="10"/>
-        <v>6.63415</v>
-      </c>
-      <c r="BB28" s="21">
-        <f t="shared" si="11"/>
-        <v>2.88</v>
-      </c>
-      <c r="BC28" s="21">
-        <f t="shared" si="12"/>
-        <v>2.91</v>
-      </c>
-      <c r="BD28" s="21">
-        <f t="shared" si="21"/>
-        <v>16</v>
-      </c>
-      <c r="BE28" s="21">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="BG28" s="21">
-        <f t="shared" si="14"/>
-        <v>2.5350000000000001</v>
-      </c>
-      <c r="BH28" s="21">
-        <f t="shared" si="15"/>
-        <v>25.5</v>
-      </c>
-      <c r="BI28" s="21">
-        <f t="shared" si="16"/>
-        <v>23.965</v>
-      </c>
-      <c r="BJ28" s="21">
-        <f t="shared" si="17"/>
-        <v>22.965</v>
+        <v>41.715000000000003</v>
       </c>
     </row>
-    <row r="29" spans="1:62" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="10" t="s">
+    <row r="29" spans="1:62" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="B29" s="11">
+      <c r="B29" s="8">
         <f t="shared" si="5"/>
         <v>0.49</v>
       </c>
-      <c r="C29" s="10">
+      <c r="C29" s="7">
         <v>3.45</v>
       </c>
-      <c r="D29" s="12">
+      <c r="D29" s="9">
         <v>0.65</v>
       </c>
-      <c r="G29" s="22">
+      <c r="E29" s="17">
+        <f t="shared" si="24"/>
+        <v>0.73919999999999997</v>
+      </c>
+      <c r="F29" s="3">
+        <f t="shared" si="35"/>
+        <v>1.3391999999999999</v>
+      </c>
+      <c r="G29" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I29" s="23">
+        <v>0.73919999999999997</v>
+      </c>
+      <c r="H29" s="17">
+        <f t="shared" si="26"/>
+        <v>3</v>
+      </c>
+      <c r="I29" s="2">
         <v>3.1</v>
       </c>
-      <c r="J29" s="23">
+      <c r="J29" s="2">
         <v>5</v>
       </c>
-      <c r="K29" s="23">
+      <c r="K29" s="2">
         <v>0.3</v>
       </c>
-      <c r="L29" s="23">
-        <v>1</v>
-      </c>
-      <c r="N29" s="22">
+      <c r="L29" s="2">
+        <v>1</v>
+      </c>
+      <c r="M29" s="18">
+        <f t="shared" si="36"/>
+        <v>1.0392000000000001</v>
+      </c>
+      <c r="N29" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q29" s="22">
+        <v>0.73919999999999997</v>
+      </c>
+      <c r="O29" s="18">
+        <f t="shared" si="37"/>
+        <v>1.4392</v>
+      </c>
+      <c r="P29" s="7">
+        <v>7</v>
+      </c>
+      <c r="Q29" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T29" s="11">
+        <v>1.0392000000000001</v>
+      </c>
+      <c r="R29" s="18">
+        <v>1.3</v>
+      </c>
+      <c r="S29" s="18">
+        <v>1.3</v>
+      </c>
+      <c r="T29" s="8">
         <f t="shared" si="7"/>
         <v>0.49</v>
       </c>
-      <c r="U29" s="23">
+      <c r="U29" s="2">
         <v>0.44</v>
       </c>
-      <c r="V29" s="23">
+      <c r="V29" s="2">
         <v>2.16</v>
       </c>
-      <c r="W29" s="23">
+      <c r="W29" s="2">
         <v>0.85</v>
       </c>
-      <c r="X29" s="23">
+      <c r="X29" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y29" s="20"/>
-      <c r="Z29" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB29" s="11">
+      <c r="Y29" s="17">
+        <v>2.5</v>
+      </c>
+      <c r="Z29" s="9">
+        <v>1</v>
+      </c>
+      <c r="AA29" s="18">
+        <f t="shared" si="38"/>
+        <v>1.0263</v>
+      </c>
+      <c r="AB29" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC29" s="11">
+        <v>1.0263</v>
+      </c>
+      <c r="AC29" s="8">
         <f t="shared" si="3"/>
         <v>2.3199999999999998</v>
       </c>
-      <c r="AD29" s="26">
+      <c r="AD29" s="12">
         <v>3.75</v>
       </c>
-      <c r="AE29" s="26">
+      <c r="AE29" s="12">
         <f>AE30+(AE28-AE30)/2</f>
         <v>25.25</v>
       </c>
-      <c r="AF29" s="26">
+      <c r="AF29" s="12">
         <v>3.3</v>
       </c>
-      <c r="AG29" s="12">
+      <c r="AG29" s="9">
         <v>0.49</v>
       </c>
-      <c r="AH29" s="12">
+      <c r="AH29" s="9">
         <v>1.25</v>
       </c>
-      <c r="AI29" s="12">
+      <c r="AI29" s="9">
         <v>0.7</v>
       </c>
-      <c r="AJ29" s="12">
+      <c r="AJ29" s="9">
         <v>4.0999999999999996</v>
       </c>
-      <c r="AK29" s="12">
-        <v>1</v>
-      </c>
-      <c r="AL29" s="12">
+      <c r="AK29" s="9">
+        <v>1</v>
+      </c>
+      <c r="AL29" s="9">
         <v>0.1</v>
       </c>
-      <c r="AM29" s="12">
-        <v>1</v>
-      </c>
-      <c r="AP29" s="10">
+      <c r="AM29" s="9">
+        <v>1</v>
+      </c>
+      <c r="AN29" s="18">
+        <f t="shared" si="39"/>
+        <v>0.39200000000000002</v>
+      </c>
+      <c r="AO29" s="3">
+        <f t="shared" si="40"/>
+        <v>2.0482</v>
+      </c>
+      <c r="AP29">
         <v>0</v>
       </c>
-      <c r="AS29" s="10">
+      <c r="AQ29"/>
+      <c r="AR29"/>
+      <c r="AS29" s="7">
         <f t="shared" si="4"/>
         <v>1.1363636363636365</v>
       </c>
-      <c r="AT29" s="10">
+      <c r="AT29" s="7">
         <v>26</v>
       </c>
-      <c r="AU29" s="10">
+      <c r="AU29" s="7">
+        <f t="shared" si="21"/>
+        <v>21.38</v>
+      </c>
+      <c r="AV29" s="13">
+        <f t="shared" si="22"/>
+        <v>21.8</v>
+      </c>
+      <c r="AW29" s="7">
+        <f t="shared" si="23"/>
+        <v>0.42000000000000171</v>
+      </c>
+      <c r="AY29">
+        <f t="shared" si="11"/>
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="AZ29">
+        <f t="shared" si="12"/>
+        <v>2.77</v>
+      </c>
+      <c r="BA29">
+        <f t="shared" si="13"/>
+        <v>6.4263999999999992</v>
+      </c>
+      <c r="BB29">
+        <f t="shared" si="14"/>
+        <v>2.85</v>
+      </c>
+      <c r="BC29">
+        <f t="shared" si="15"/>
+        <v>2.86</v>
+      </c>
+      <c r="BD29">
+        <v>16.5</v>
+      </c>
+      <c r="BE29">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="BG29">
+        <f t="shared" si="17"/>
+        <v>4.66</v>
+      </c>
+      <c r="BH29">
         <f t="shared" si="18"/>
-        <v>21.38</v>
-      </c>
-      <c r="AV29" s="18">
+        <v>31.25</v>
+      </c>
+      <c r="BI29">
         <f t="shared" si="19"/>
-        <v>21.8</v>
-      </c>
-      <c r="AW29" s="25">
+        <v>20.59</v>
+      </c>
+      <c r="BJ29">
         <f t="shared" si="20"/>
-        <v>0.42000000000000171</v>
-      </c>
-      <c r="AY29">
-        <f t="shared" si="8"/>
-        <v>2.3199999999999998</v>
-      </c>
-      <c r="AZ29">
-        <f t="shared" si="9"/>
-        <v>2.77</v>
-      </c>
-      <c r="BA29">
-        <f t="shared" si="10"/>
-        <v>6.4263999999999992</v>
-      </c>
-      <c r="BB29" s="21">
-        <f t="shared" si="11"/>
-        <v>2.85</v>
-      </c>
-      <c r="BC29" s="21">
-        <f t="shared" si="12"/>
-        <v>2.86</v>
-      </c>
-      <c r="BD29" s="21">
-        <v>16.5</v>
-      </c>
-      <c r="BE29" s="21">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="BG29" s="21">
-        <f t="shared" si="14"/>
-        <v>2.16</v>
-      </c>
-      <c r="BH29" s="21">
-        <f t="shared" si="15"/>
-        <v>24.25</v>
-      </c>
-      <c r="BI29" s="21">
-        <f t="shared" si="16"/>
-        <v>23.09</v>
-      </c>
-      <c r="BJ29" s="21">
-        <f t="shared" si="17"/>
-        <v>22.09</v>
+        <v>26.59</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.25">
@@ -8954,56 +9989,89 @@
       <c r="D30" s="2">
         <v>0.65</v>
       </c>
-      <c r="G30" s="22">
+      <c r="E30" s="17">
+        <f t="shared" si="24"/>
+        <v>0.70000000000000007</v>
+      </c>
+      <c r="F30" s="3">
+        <f t="shared" si="35"/>
+        <v>1.3</v>
+      </c>
+      <c r="G30" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I30" s="23">
+        <v>0.70000000000000007</v>
+      </c>
+      <c r="H30" s="17">
+        <f t="shared" si="26"/>
+        <v>8.875</v>
+      </c>
+      <c r="I30" s="2">
         <v>3.1</v>
       </c>
-      <c r="J30" s="23">
+      <c r="J30" s="2">
         <v>5</v>
       </c>
-      <c r="K30" s="23">
+      <c r="K30" s="2">
         <v>0.3</v>
       </c>
-      <c r="L30" s="23">
-        <v>1</v>
-      </c>
-      <c r="N30" s="22">
+      <c r="L30" s="2">
+        <v>1</v>
+      </c>
+      <c r="M30" s="18">
+        <f t="shared" si="36"/>
+        <v>0.99999999999999989</v>
+      </c>
+      <c r="N30" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q30" s="22">
+        <v>0.70000000000000007</v>
+      </c>
+      <c r="O30" s="18">
+        <f t="shared" si="37"/>
+        <v>1.4</v>
+      </c>
+      <c r="P30" s="16">
+        <v>18.75</v>
+      </c>
+      <c r="Q30" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.99999999999999989</v>
+      </c>
+      <c r="R30" s="18">
+        <v>1.3</v>
+      </c>
+      <c r="S30" s="18">
+        <v>1.3</v>
       </c>
       <c r="T30" s="1">
         <f t="shared" si="7"/>
         <v>0.49</v>
       </c>
-      <c r="U30" s="23">
+      <c r="U30" s="2">
         <v>0.44</v>
       </c>
-      <c r="V30" s="23">
+      <c r="V30" s="2">
         <v>2.16</v>
       </c>
-      <c r="W30" s="23">
+      <c r="W30" s="2">
         <v>0.85</v>
       </c>
-      <c r="X30" s="23">
+      <c r="X30" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y30" s="19">
+      <c r="Y30" s="14">
         <f>1+1/8</f>
         <v>1.125</v>
       </c>
       <c r="Z30" s="2">
         <v>1</v>
       </c>
+      <c r="AA30" s="18">
+        <f t="shared" si="38"/>
+        <v>0.97187500000000004</v>
+      </c>
       <c r="AB30" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.97187500000000004</v>
       </c>
       <c r="AC30" s="1">
         <f t="shared" si="3"/>
@@ -9040,7 +10108,15 @@
       <c r="AM30" s="2">
         <v>1</v>
       </c>
-      <c r="AP30" s="23">
+      <c r="AN30" s="18">
+        <f t="shared" si="39"/>
+        <v>0.39200000000000002</v>
+      </c>
+      <c r="AO30" s="3">
+        <f t="shared" si="40"/>
+        <v>2.0482</v>
+      </c>
+      <c r="AP30">
         <v>0</v>
       </c>
       <c r="AS30">
@@ -9051,709 +10127,889 @@
         <v>27</v>
       </c>
       <c r="AU30">
+        <f t="shared" si="21"/>
+        <v>20.18</v>
+      </c>
+      <c r="AV30">
+        <f t="shared" si="22"/>
+        <v>20.59</v>
+      </c>
+      <c r="AW30">
+        <f t="shared" si="23"/>
+        <v>0.41000000000000014</v>
+      </c>
+      <c r="AY30">
+        <f t="shared" si="11"/>
+        <v>2.145</v>
+      </c>
+      <c r="AZ30">
+        <f t="shared" si="12"/>
+        <v>2.92</v>
+      </c>
+      <c r="BA30">
+        <f t="shared" si="13"/>
+        <v>6.2633999999999999</v>
+      </c>
+      <c r="BB30">
+        <f t="shared" si="14"/>
+        <v>2.79</v>
+      </c>
+      <c r="BC30">
+        <f t="shared" si="15"/>
+        <v>2.82</v>
+      </c>
+      <c r="BD30">
+        <v>16.8</v>
+      </c>
+      <c r="BE30">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="BG30">
+        <f t="shared" si="17"/>
+        <v>3.2850000000000001</v>
+      </c>
+      <c r="BH30">
         <f t="shared" si="18"/>
-        <v>20.18</v>
-      </c>
-      <c r="AV30">
+        <v>41.75</v>
+      </c>
+      <c r="BI30">
         <f t="shared" si="19"/>
-        <v>20.59</v>
-      </c>
-      <c r="AW30" s="21">
+        <v>20.715</v>
+      </c>
+      <c r="BJ30">
         <f t="shared" si="20"/>
-        <v>0.41000000000000014</v>
-      </c>
-      <c r="AY30">
-        <f t="shared" si="8"/>
-        <v>2.145</v>
-      </c>
-      <c r="AZ30">
-        <f t="shared" si="9"/>
-        <v>2.92</v>
-      </c>
-      <c r="BA30">
-        <f t="shared" si="10"/>
-        <v>6.2633999999999999</v>
-      </c>
-      <c r="BB30" s="21">
+        <v>38.465000000000003</v>
+      </c>
+    </row>
+    <row r="31" spans="1:62" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B31" s="8">
+        <f t="shared" si="5"/>
+        <v>0.49</v>
+      </c>
+      <c r="C31" s="7">
+        <v>3.4</v>
+      </c>
+      <c r="D31" s="9">
+        <v>0.65</v>
+      </c>
+      <c r="E31" s="17">
+        <f t="shared" si="24"/>
+        <v>0.67200000000000004</v>
+      </c>
+      <c r="F31" s="3">
+        <f t="shared" si="35"/>
+        <v>1.272</v>
+      </c>
+      <c r="G31" s="1">
+        <f t="shared" si="0"/>
+        <v>0.67200000000000004</v>
+      </c>
+      <c r="H31" s="17">
+        <f t="shared" si="26"/>
+        <v>3</v>
+      </c>
+      <c r="I31" s="2">
+        <v>3.1</v>
+      </c>
+      <c r="J31" s="2">
+        <v>5</v>
+      </c>
+      <c r="K31" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="L31" s="2">
+        <v>1</v>
+      </c>
+      <c r="M31" s="18">
+        <f t="shared" si="36"/>
+        <v>0.97199999999999986</v>
+      </c>
+      <c r="N31" s="1">
+        <f t="shared" si="6"/>
+        <v>0.67200000000000004</v>
+      </c>
+      <c r="O31" s="18">
+        <f t="shared" si="37"/>
+        <v>1.3719999999999999</v>
+      </c>
+      <c r="P31" s="7">
+        <v>7</v>
+      </c>
+      <c r="Q31" s="1">
+        <f t="shared" si="1"/>
+        <v>0.97199999999999986</v>
+      </c>
+      <c r="R31" s="18">
+        <v>1.3</v>
+      </c>
+      <c r="S31" s="18">
+        <v>1.3</v>
+      </c>
+      <c r="T31" s="8">
+        <f t="shared" si="7"/>
+        <v>0.49</v>
+      </c>
+      <c r="U31" s="2">
+        <v>0.44</v>
+      </c>
+      <c r="V31" s="2">
+        <v>2.16</v>
+      </c>
+      <c r="W31" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="X31" s="2">
+        <v>3.66</v>
+      </c>
+      <c r="Y31" s="17">
+        <v>2.25</v>
+      </c>
+      <c r="Z31" s="9">
+        <v>1</v>
+      </c>
+      <c r="AA31" s="18">
+        <f t="shared" si="38"/>
+        <v>0.93300000000000005</v>
+      </c>
+      <c r="AB31" s="8">
+        <f t="shared" si="2"/>
+        <v>0.93300000000000005</v>
+      </c>
+      <c r="AC31" s="8">
+        <f t="shared" si="3"/>
+        <v>2.02</v>
+      </c>
+      <c r="AD31" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="AE31" s="12">
+        <v>22.85</v>
+      </c>
+      <c r="AF31" s="12">
+        <v>3</v>
+      </c>
+      <c r="AG31" s="9">
+        <v>0.49</v>
+      </c>
+      <c r="AH31" s="9">
+        <v>1.25</v>
+      </c>
+      <c r="AI31" s="9">
+        <v>0.7</v>
+      </c>
+      <c r="AJ31" s="9">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="AK31" s="9">
+        <v>1</v>
+      </c>
+      <c r="AL31" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="AM31" s="9">
+        <v>1</v>
+      </c>
+      <c r="AN31" s="18">
+        <f t="shared" si="39"/>
+        <v>0.39200000000000002</v>
+      </c>
+      <c r="AO31" s="3">
+        <f t="shared" si="40"/>
+        <v>2.0482</v>
+      </c>
+      <c r="AP31">
+        <v>0</v>
+      </c>
+      <c r="AQ31"/>
+      <c r="AR31"/>
+      <c r="AS31" s="7">
+        <f t="shared" si="4"/>
+        <v>1.2666666666666666</v>
+      </c>
+      <c r="AT31" s="7">
+        <v>28</v>
+      </c>
+      <c r="AU31" s="7">
+        <f t="shared" si="21"/>
+        <v>19.05</v>
+      </c>
+      <c r="AV31" s="7">
+        <f t="shared" si="22"/>
+        <v>19.450000000000003</v>
+      </c>
+      <c r="AW31" s="7">
+        <f t="shared" si="23"/>
+        <v>0.40000000000000213</v>
+      </c>
+      <c r="AY31">
         <f t="shared" si="11"/>
-        <v>2.79</v>
-      </c>
-      <c r="BC30" s="21">
+        <v>2.02</v>
+      </c>
+      <c r="AZ31">
         <f t="shared" si="12"/>
         <v>2.82</v>
       </c>
-      <c r="BD30" s="21">
-        <v>16.8</v>
-      </c>
-      <c r="BE30" s="21">
+      <c r="BA31">
         <f t="shared" si="13"/>
+        <v>5.6963999999999997</v>
+      </c>
+      <c r="BB31">
+        <f t="shared" si="14"/>
+        <v>2.71</v>
+      </c>
+      <c r="BC31">
+        <f t="shared" si="15"/>
+        <v>2.69</v>
+      </c>
+      <c r="BD31">
+        <v>17</v>
+      </c>
+      <c r="BE31">
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BG30" s="21">
-        <f t="shared" si="14"/>
-        <v>3.2850000000000001</v>
-      </c>
-      <c r="BH30" s="21">
-        <f t="shared" si="15"/>
-        <v>23</v>
-      </c>
-      <c r="BI30" s="21">
-        <f t="shared" si="16"/>
-        <v>20.715</v>
-      </c>
-      <c r="BJ30" s="21">
+      <c r="BG31">
         <f t="shared" si="17"/>
-        <v>19.715</v>
+        <v>4.41</v>
+      </c>
+      <c r="BH31">
+        <f t="shared" si="18"/>
+        <v>28.85</v>
+      </c>
+      <c r="BI31">
+        <f t="shared" si="19"/>
+        <v>18.440000000000001</v>
+      </c>
+      <c r="BJ31">
+        <f t="shared" si="20"/>
+        <v>24.44</v>
       </c>
     </row>
-    <row r="31" spans="1:62" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="B31" s="11">
+    <row r="32" spans="1:62" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B32" s="8">
         <f t="shared" si="5"/>
         <v>0.49</v>
       </c>
-      <c r="C31" s="10">
+      <c r="C32" s="7">
         <v>3.4</v>
       </c>
-      <c r="D31" s="12">
+      <c r="D32" s="9">
         <v>0.65</v>
       </c>
-      <c r="G31" s="22">
+      <c r="E32" s="17">
+        <f t="shared" si="24"/>
+        <v>0.64959999999999996</v>
+      </c>
+      <c r="F32" s="3">
+        <f t="shared" si="35"/>
+        <v>1.2496</v>
+      </c>
+      <c r="G32" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I31" s="23">
+        <v>0.64959999999999996</v>
+      </c>
+      <c r="H32" s="17">
+        <f t="shared" si="26"/>
+        <v>8.875</v>
+      </c>
+      <c r="I32" s="2">
         <v>3.1</v>
       </c>
-      <c r="J31" s="23">
+      <c r="J32" s="2">
         <v>5</v>
       </c>
-      <c r="K31" s="23">
+      <c r="K32" s="2">
         <v>0.3</v>
       </c>
-      <c r="L31" s="23">
-        <v>1</v>
-      </c>
-      <c r="N31" s="22">
+      <c r="L32" s="2">
+        <v>1</v>
+      </c>
+      <c r="M32" s="18">
+        <f t="shared" si="36"/>
+        <v>0.94959999999999989</v>
+      </c>
+      <c r="N32" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q31" s="22">
+        <v>0.64959999999999996</v>
+      </c>
+      <c r="O32" s="18">
+        <f t="shared" si="37"/>
+        <v>1.3495999999999999</v>
+      </c>
+      <c r="P32" s="7">
+        <v>18.75</v>
+      </c>
+      <c r="Q32" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T31" s="11">
+        <v>0.94959999999999989</v>
+      </c>
+      <c r="R32" s="18">
+        <v>1.3</v>
+      </c>
+      <c r="S32" s="18">
+        <v>1.3</v>
+      </c>
+      <c r="T32" s="8">
         <f t="shared" si="7"/>
         <v>0.49</v>
       </c>
-      <c r="U31" s="23">
+      <c r="U32" s="2">
         <v>0.44</v>
       </c>
-      <c r="V31" s="23">
+      <c r="V32" s="2">
         <v>2.16</v>
       </c>
-      <c r="W31" s="23">
+      <c r="W32" s="2">
         <v>0.85</v>
       </c>
-      <c r="X31" s="23">
+      <c r="X32" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y31" s="20"/>
-      <c r="Z31" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB31" s="11">
+      <c r="Y32" s="17">
+        <v>0.8</v>
+      </c>
+      <c r="Z32" s="9">
+        <v>1</v>
+      </c>
+      <c r="AA32" s="18">
+        <f t="shared" si="38"/>
+        <v>0.90189999999999992</v>
+      </c>
+      <c r="AB32" s="8">
         <f t="shared" si="2"/>
+        <v>0.90189999999999992</v>
+      </c>
+      <c r="AC32" s="8">
+        <f t="shared" si="3"/>
+        <v>1.92</v>
+      </c>
+      <c r="AD32" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="AE32" s="12">
+        <v>21.78</v>
+      </c>
+      <c r="AF32" s="12">
+        <v>2.9</v>
+      </c>
+      <c r="AG32" s="9">
+        <v>0.49</v>
+      </c>
+      <c r="AH32" s="9">
+        <v>1.25</v>
+      </c>
+      <c r="AI32" s="9">
+        <v>0.7</v>
+      </c>
+      <c r="AJ32" s="9">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="AK32" s="9">
+        <v>1</v>
+      </c>
+      <c r="AL32" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="AM32" s="9">
+        <v>1</v>
+      </c>
+      <c r="AN32" s="18">
+        <f t="shared" si="39"/>
+        <v>0.39200000000000002</v>
+      </c>
+      <c r="AO32" s="3">
+        <f t="shared" si="40"/>
+        <v>2.0482</v>
+      </c>
+      <c r="AP32">
         <v>0</v>
       </c>
-      <c r="AC31" s="11">
-        <f t="shared" si="3"/>
-        <v>2.02</v>
-      </c>
-      <c r="AD31" s="26">
-        <v>3.8</v>
-      </c>
-      <c r="AE31" s="26">
-        <v>22.85</v>
-      </c>
-      <c r="AF31" s="26">
-        <v>3</v>
-      </c>
-      <c r="AG31" s="12">
-        <v>0.49</v>
-      </c>
-      <c r="AH31" s="12">
-        <v>1.25</v>
-      </c>
-      <c r="AI31" s="12">
-        <v>0.7</v>
-      </c>
-      <c r="AJ31" s="12">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="AK31" s="12">
-        <v>1</v>
-      </c>
-      <c r="AL31" s="12">
-        <v>0.1</v>
-      </c>
-      <c r="AM31" s="12">
-        <v>1</v>
-      </c>
-      <c r="AP31" s="10">
-        <v>0</v>
-      </c>
-      <c r="AS31" s="10">
+      <c r="AQ32"/>
+      <c r="AR32"/>
+      <c r="AS32" s="7">
         <f t="shared" si="4"/>
-        <v>1.2666666666666666</v>
-      </c>
-      <c r="AT31" s="10">
-        <v>28</v>
-      </c>
-      <c r="AU31" s="10">
+        <v>1.2758620689655173</v>
+      </c>
+      <c r="AT32" s="7">
+        <v>29</v>
+      </c>
+      <c r="AU32" s="7">
+        <f t="shared" si="21"/>
+        <v>17.98</v>
+      </c>
+      <c r="AV32" s="7">
+        <f t="shared" si="22"/>
+        <v>18.380000000000003</v>
+      </c>
+      <c r="AW32" s="7">
+        <f t="shared" si="23"/>
+        <v>0.40000000000000213</v>
+      </c>
+      <c r="AY32">
+        <f t="shared" si="11"/>
+        <v>1.92</v>
+      </c>
+      <c r="AZ32">
+        <f t="shared" si="12"/>
+        <v>2.72</v>
+      </c>
+      <c r="BA32">
+        <f t="shared" si="13"/>
+        <v>5.2224000000000004</v>
+      </c>
+      <c r="BB32">
+        <f t="shared" si="14"/>
+        <v>2.64</v>
+      </c>
+      <c r="BC32">
+        <f t="shared" si="15"/>
+        <v>2.58</v>
+      </c>
+      <c r="BD32">
+        <v>17.2</v>
+      </c>
+      <c r="BE32">
+        <f t="shared" si="16"/>
+        <v>-0.1</v>
+      </c>
+      <c r="BG32">
+        <f t="shared" si="17"/>
+        <v>2.96</v>
+      </c>
+      <c r="BH32">
         <f t="shared" si="18"/>
-        <v>19.05</v>
-      </c>
-      <c r="AV31" s="25">
+        <v>39.53</v>
+      </c>
+      <c r="BI32">
         <f t="shared" si="19"/>
-        <v>19.450000000000003</v>
-      </c>
-      <c r="AW31" s="25">
+        <v>18.82</v>
+      </c>
+      <c r="BJ32">
         <f t="shared" si="20"/>
-        <v>0.40000000000000213</v>
-      </c>
-      <c r="AY31">
-        <f t="shared" si="8"/>
-        <v>2.02</v>
-      </c>
-      <c r="AZ31">
-        <f t="shared" si="9"/>
-        <v>2.82</v>
-      </c>
-      <c r="BA31">
-        <f t="shared" si="10"/>
-        <v>5.6963999999999997</v>
-      </c>
-      <c r="BB31" s="21">
-        <f t="shared" si="11"/>
-        <v>2.71</v>
-      </c>
-      <c r="BC31" s="21">
-        <f t="shared" si="12"/>
-        <v>2.69</v>
-      </c>
-      <c r="BD31" s="21">
-        <v>17</v>
-      </c>
-      <c r="BE31" s="21">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="BG31" s="21">
-        <f t="shared" si="14"/>
-        <v>2.16</v>
-      </c>
-      <c r="BH31" s="21">
-        <f t="shared" si="15"/>
-        <v>21.85</v>
-      </c>
-      <c r="BI31" s="21">
-        <f t="shared" si="16"/>
-        <v>20.69</v>
-      </c>
-      <c r="BJ31" s="21">
-        <f t="shared" si="17"/>
-        <v>19.690000000000001</v>
+        <v>36.57</v>
       </c>
     </row>
-    <row r="32" spans="1:62" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B32" s="11">
+    <row r="33" spans="1:62" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B33" s="8">
         <f t="shared" si="5"/>
         <v>0.49</v>
       </c>
-      <c r="C32" s="10">
+      <c r="C33" s="7">
         <v>3.4</v>
       </c>
-      <c r="D32" s="12">
+      <c r="D33" s="9">
         <v>0.65</v>
       </c>
-      <c r="G32" s="22">
+      <c r="E33" s="17">
+        <f t="shared" si="24"/>
+        <v>0.63168000000000002</v>
+      </c>
+      <c r="F33" s="3">
+        <f t="shared" si="35"/>
+        <v>1.2316799999999999</v>
+      </c>
+      <c r="G33" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I32" s="23">
+        <v>0.63168000000000002</v>
+      </c>
+      <c r="H33" s="17">
+        <f t="shared" si="26"/>
+        <v>3</v>
+      </c>
+      <c r="I33" s="2">
         <v>3.1</v>
       </c>
-      <c r="J32" s="23">
+      <c r="J33" s="2">
         <v>5</v>
       </c>
-      <c r="K32" s="23">
+      <c r="K33" s="2">
         <v>0.3</v>
       </c>
-      <c r="L32" s="23">
-        <v>1</v>
-      </c>
-      <c r="N32" s="22">
+      <c r="L33" s="2">
+        <v>1</v>
+      </c>
+      <c r="M33" s="18">
+        <f t="shared" si="36"/>
+        <v>0.93167999999999995</v>
+      </c>
+      <c r="N33" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q32" s="22">
+        <v>0.63168000000000002</v>
+      </c>
+      <c r="O33" s="18">
+        <f t="shared" si="37"/>
+        <v>1.33168</v>
+      </c>
+      <c r="P33" s="7">
+        <v>7</v>
+      </c>
+      <c r="Q33" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T32" s="11">
+        <v>0.93167999999999995</v>
+      </c>
+      <c r="R33" s="18">
+        <v>1.3</v>
+      </c>
+      <c r="S33" s="18">
+        <v>1.3</v>
+      </c>
+      <c r="T33" s="8">
         <f t="shared" si="7"/>
         <v>0.49</v>
       </c>
-      <c r="U32" s="23">
+      <c r="U33" s="2">
         <v>0.44</v>
       </c>
-      <c r="V32" s="23">
+      <c r="V33" s="2">
         <v>2.16</v>
       </c>
-      <c r="W32" s="23">
+      <c r="W33" s="2">
         <v>0.85</v>
       </c>
-      <c r="X32" s="23">
+      <c r="X33" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y32" s="19"/>
-      <c r="Z32" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB32" s="11">
+      <c r="Y33" s="17">
+        <v>2</v>
+      </c>
+      <c r="Z33" s="9">
+        <v>1</v>
+      </c>
+      <c r="AA33" s="18">
+        <f t="shared" si="38"/>
+        <v>0.87701999999999991</v>
+      </c>
+      <c r="AB33" s="8">
         <f t="shared" si="2"/>
+        <v>0.87701999999999991</v>
+      </c>
+      <c r="AC33" s="8">
+        <f t="shared" si="3"/>
+        <v>1.8399999999999999</v>
+      </c>
+      <c r="AD33" s="12">
+        <v>3.65</v>
+      </c>
+      <c r="AE33" s="12">
+        <v>20.77</v>
+      </c>
+      <c r="AF33" s="12">
+        <v>2.82</v>
+      </c>
+      <c r="AG33" s="9">
+        <v>0.49</v>
+      </c>
+      <c r="AH33" s="9">
+        <v>1.25</v>
+      </c>
+      <c r="AI33" s="9">
+        <v>0.7</v>
+      </c>
+      <c r="AJ33" s="9">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="AK33" s="9">
+        <v>1</v>
+      </c>
+      <c r="AL33" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="AM33" s="9">
+        <v>1</v>
+      </c>
+      <c r="AN33" s="18">
+        <f t="shared" si="39"/>
+        <v>0.39200000000000002</v>
+      </c>
+      <c r="AO33" s="3">
+        <f t="shared" si="40"/>
+        <v>2.0482</v>
+      </c>
+      <c r="AP33">
         <v>0</v>
       </c>
-      <c r="AC32" s="11">
-        <f t="shared" si="3"/>
-        <v>1.92</v>
-      </c>
-      <c r="AD32" s="26">
-        <v>3.7</v>
-      </c>
-      <c r="AE32" s="26">
-        <v>21.78</v>
-      </c>
-      <c r="AF32" s="26">
-        <v>2.9</v>
-      </c>
-      <c r="AG32" s="12">
-        <v>0.49</v>
-      </c>
-      <c r="AH32" s="12">
-        <v>1.25</v>
-      </c>
-      <c r="AI32" s="12">
-        <v>0.7</v>
-      </c>
-      <c r="AJ32" s="12">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="AK32" s="12">
-        <v>1</v>
-      </c>
-      <c r="AL32" s="12">
-        <v>0.1</v>
-      </c>
-      <c r="AM32" s="12">
-        <v>1</v>
-      </c>
-      <c r="AP32" s="10">
+      <c r="AQ33"/>
+      <c r="AR33"/>
+      <c r="AS33" s="7">
+        <f t="shared" si="4"/>
+        <v>1.2943262411347518</v>
+      </c>
+      <c r="AT33" s="7">
+        <v>30</v>
+      </c>
+      <c r="AU33" s="7">
+        <f t="shared" si="21"/>
+        <v>16.97</v>
+      </c>
+      <c r="AV33" s="7">
+        <f t="shared" si="22"/>
+        <v>17.37</v>
+      </c>
+      <c r="AW33" s="7">
+        <f t="shared" si="23"/>
+        <v>0.40000000000000213</v>
+      </c>
+      <c r="AY33">
+        <f t="shared" si="11"/>
+        <v>1.8399999999999999</v>
+      </c>
+      <c r="AZ33">
+        <f t="shared" si="12"/>
+        <v>2.67</v>
+      </c>
+      <c r="BA33">
+        <f t="shared" si="13"/>
+        <v>4.9127999999999998</v>
+      </c>
+      <c r="BB33">
+        <f t="shared" si="14"/>
+        <v>2.54</v>
+      </c>
+      <c r="BC33">
+        <f t="shared" si="15"/>
+        <v>2.5</v>
+      </c>
+      <c r="BD33">
+        <f t="shared" si="32"/>
+        <v>17.2</v>
+      </c>
+      <c r="BE33">
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AS32" s="10">
-        <f t="shared" si="4"/>
-        <v>1.2758620689655173</v>
-      </c>
-      <c r="AT32" s="10">
-        <v>29</v>
-      </c>
-      <c r="AU32" s="10">
+      <c r="BG33">
+        <f t="shared" si="17"/>
+        <v>4.16</v>
+      </c>
+      <c r="BH33">
         <f t="shared" si="18"/>
-        <v>17.98</v>
-      </c>
-      <c r="AV32" s="25">
+        <v>26.77</v>
+      </c>
+      <c r="BI33">
         <f t="shared" si="19"/>
-        <v>18.380000000000003</v>
-      </c>
-      <c r="AW32" s="25">
+        <v>16.61</v>
+      </c>
+      <c r="BJ33">
         <f t="shared" si="20"/>
-        <v>0.40000000000000213</v>
-      </c>
-      <c r="AY32">
-        <f t="shared" si="8"/>
-        <v>1.92</v>
-      </c>
-      <c r="AZ32">
-        <f t="shared" si="9"/>
-        <v>2.72</v>
-      </c>
-      <c r="BA32">
-        <f t="shared" si="10"/>
-        <v>5.2224000000000004</v>
-      </c>
-      <c r="BB32" s="21">
-        <f t="shared" si="11"/>
-        <v>2.64</v>
-      </c>
-      <c r="BC32" s="21">
-        <f t="shared" si="12"/>
-        <v>2.58</v>
-      </c>
-      <c r="BD32" s="21">
-        <v>17.2</v>
-      </c>
-      <c r="BE32" s="21">
-        <f t="shared" si="13"/>
-        <v>-0.1</v>
-      </c>
-      <c r="BG32" s="21">
-        <f t="shared" si="14"/>
-        <v>2.16</v>
-      </c>
-      <c r="BH32" s="21">
-        <f t="shared" si="15"/>
-        <v>20.78</v>
-      </c>
-      <c r="BI32" s="21">
-        <f t="shared" si="16"/>
-        <v>19.62</v>
-      </c>
-      <c r="BJ32" s="21">
-        <f t="shared" si="17"/>
-        <v>18.62</v>
+        <v>22.61</v>
       </c>
     </row>
-    <row r="33" spans="1:62" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="B33" s="11">
+    <row r="34" spans="1:62" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B34" s="8">
         <f t="shared" si="5"/>
         <v>0.49</v>
       </c>
-      <c r="C33" s="10">
+      <c r="C34" s="7">
         <v>3.4</v>
       </c>
-      <c r="D33" s="12">
+      <c r="D34" s="9">
         <v>0.65</v>
       </c>
-      <c r="G33" s="22">
+      <c r="E34" s="17">
+        <f t="shared" si="24"/>
+        <v>0.61152000000000006</v>
+      </c>
+      <c r="F34" s="3">
+        <f t="shared" si="35"/>
+        <v>1.2115200000000002</v>
+      </c>
+      <c r="G34" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I33" s="23">
+        <v>0.61152000000000006</v>
+      </c>
+      <c r="H34" s="17">
+        <f t="shared" si="26"/>
+        <v>8.875</v>
+      </c>
+      <c r="I34" s="2">
         <v>3.1</v>
       </c>
-      <c r="J33" s="23">
+      <c r="J34" s="2">
         <v>5</v>
       </c>
-      <c r="K33" s="23">
+      <c r="K34" s="2">
         <v>0.3</v>
       </c>
-      <c r="L33" s="23">
-        <v>1</v>
-      </c>
-      <c r="N33" s="22">
+      <c r="L34" s="2">
+        <v>1</v>
+      </c>
+      <c r="M34" s="18">
+        <f t="shared" si="36"/>
+        <v>0.91152</v>
+      </c>
+      <c r="N34" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q33" s="22">
+        <v>0.61152000000000006</v>
+      </c>
+      <c r="O34" s="18">
+        <f t="shared" si="37"/>
+        <v>1.31152</v>
+      </c>
+      <c r="P34" s="7">
+        <v>18.75</v>
+      </c>
+      <c r="Q34" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T33" s="11">
+        <v>0.91152</v>
+      </c>
+      <c r="R34" s="18">
+        <v>1.3</v>
+      </c>
+      <c r="S34" s="18">
+        <v>1.3</v>
+      </c>
+      <c r="T34" s="8">
         <f t="shared" si="7"/>
         <v>0.49</v>
       </c>
-      <c r="U33" s="23">
+      <c r="U34" s="2">
         <v>0.44</v>
       </c>
-      <c r="V33" s="23">
+      <c r="V34" s="2">
         <v>2.16</v>
       </c>
-      <c r="W33" s="23">
+      <c r="W34" s="2">
         <v>0.85</v>
       </c>
-      <c r="X33" s="23">
+      <c r="X34" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y33" s="20"/>
-      <c r="Z33" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB33" s="11">
+      <c r="Y34" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="Z34" s="9">
+        <v>1</v>
+      </c>
+      <c r="AA34" s="18">
+        <f t="shared" si="38"/>
+        <v>0.84902999999999995</v>
+      </c>
+      <c r="AB34" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC33" s="11">
-        <f t="shared" si="3"/>
-        <v>1.8399999999999999</v>
-      </c>
-      <c r="AD33" s="26">
-        <v>3.65</v>
-      </c>
-      <c r="AE33" s="26">
-        <v>20.77</v>
-      </c>
-      <c r="AF33" s="26">
-        <v>2.82</v>
-      </c>
-      <c r="AG33" s="12">
-        <v>0.49</v>
-      </c>
-      <c r="AH33" s="12">
-        <v>1.25</v>
-      </c>
-      <c r="AI33" s="12">
-        <v>0.7</v>
-      </c>
-      <c r="AJ33" s="12">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="AK33" s="12">
-        <v>1</v>
-      </c>
-      <c r="AL33" s="12">
-        <v>0.1</v>
-      </c>
-      <c r="AM33" s="12">
-        <v>1</v>
-      </c>
-      <c r="AP33" s="10">
-        <v>0</v>
-      </c>
-      <c r="AS33" s="10">
-        <f t="shared" si="4"/>
-        <v>1.2943262411347518</v>
-      </c>
-      <c r="AT33" s="10">
-        <v>30</v>
-      </c>
-      <c r="AU33" s="10">
-        <f t="shared" si="18"/>
-        <v>16.97</v>
-      </c>
-      <c r="AV33" s="25">
-        <f t="shared" si="19"/>
-        <v>17.37</v>
-      </c>
-      <c r="AW33" s="25">
-        <f t="shared" si="20"/>
-        <v>0.40000000000000213</v>
-      </c>
-      <c r="AY33">
-        <f t="shared" si="8"/>
-        <v>1.8399999999999999</v>
-      </c>
-      <c r="AZ33">
-        <f t="shared" si="9"/>
-        <v>2.67</v>
-      </c>
-      <c r="BA33">
-        <f t="shared" si="10"/>
-        <v>4.9127999999999998</v>
-      </c>
-      <c r="BB33" s="21">
-        <f t="shared" si="11"/>
-        <v>2.54</v>
-      </c>
-      <c r="BC33" s="21">
-        <f t="shared" si="12"/>
-        <v>2.5</v>
-      </c>
-      <c r="BD33" s="21">
-        <f t="shared" si="21"/>
-        <v>17.2</v>
-      </c>
-      <c r="BE33" s="21">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="BG33" s="21">
-        <f t="shared" si="14"/>
-        <v>2.16</v>
-      </c>
-      <c r="BH33" s="21">
-        <f t="shared" si="15"/>
-        <v>19.77</v>
-      </c>
-      <c r="BI33" s="21">
-        <f t="shared" si="16"/>
-        <v>18.61</v>
-      </c>
-      <c r="BJ33" s="21">
-        <f t="shared" si="17"/>
-        <v>17.61</v>
-      </c>
-    </row>
-    <row r="34" spans="1:62" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="B34" s="11">
-        <f t="shared" si="5"/>
-        <v>0.49</v>
-      </c>
-      <c r="C34" s="10">
-        <v>3.4</v>
-      </c>
-      <c r="D34" s="12">
-        <v>0.65</v>
-      </c>
-      <c r="G34" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I34" s="23">
-        <v>3.1</v>
-      </c>
-      <c r="J34" s="23">
-        <v>5</v>
-      </c>
-      <c r="K34" s="23">
-        <v>0.3</v>
-      </c>
-      <c r="L34" s="23">
-        <v>1</v>
-      </c>
-      <c r="N34" s="22">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q34" s="22">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T34" s="11">
-        <f t="shared" si="7"/>
-        <v>0.49</v>
-      </c>
-      <c r="U34" s="23">
-        <v>0.44</v>
-      </c>
-      <c r="V34" s="23">
-        <v>2.16</v>
-      </c>
-      <c r="W34" s="23">
-        <v>0.85</v>
-      </c>
-      <c r="X34" s="23">
-        <v>3.66</v>
-      </c>
-      <c r="Y34" s="19"/>
-      <c r="Z34" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB34" s="11">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC34" s="11">
+        <v>0.84902999999999995</v>
+      </c>
+      <c r="AC34" s="8">
         <f t="shared" si="3"/>
         <v>1.75</v>
       </c>
-      <c r="AD34" s="26">
+      <c r="AD34" s="12">
         <v>3.55</v>
       </c>
-      <c r="AE34" s="26">
+      <c r="AE34" s="12">
         <v>19.82</v>
       </c>
-      <c r="AF34" s="26">
+      <c r="AF34" s="12">
         <v>2.73</v>
       </c>
-      <c r="AG34" s="12">
+      <c r="AG34" s="9">
         <v>0.49</v>
       </c>
-      <c r="AH34" s="12">
+      <c r="AH34" s="9">
         <v>1.25</v>
       </c>
-      <c r="AI34" s="12">
+      <c r="AI34" s="9">
         <v>0.7</v>
       </c>
-      <c r="AJ34" s="12">
+      <c r="AJ34" s="9">
         <v>4.0999999999999996</v>
       </c>
-      <c r="AK34" s="12">
-        <v>1</v>
-      </c>
-      <c r="AL34" s="12">
+      <c r="AK34" s="9">
+        <v>1</v>
+      </c>
+      <c r="AL34" s="9">
         <v>0.1</v>
       </c>
-      <c r="AM34" s="12">
-        <v>1</v>
-      </c>
-      <c r="AP34" s="10">
+      <c r="AM34" s="9">
+        <v>1</v>
+      </c>
+      <c r="AN34" s="18">
+        <f t="shared" si="39"/>
+        <v>0.39200000000000002</v>
+      </c>
+      <c r="AO34" s="3">
+        <f t="shared" si="40"/>
+        <v>2.0482</v>
+      </c>
+      <c r="AP34">
         <v>0</v>
       </c>
-      <c r="AS34" s="10">
+      <c r="AQ34"/>
+      <c r="AR34"/>
+      <c r="AS34" s="7">
         <f t="shared" si="4"/>
         <v>1.3003663003663004</v>
       </c>
-      <c r="AT34" s="10">
+      <c r="AT34" s="7">
         <v>31</v>
       </c>
-      <c r="AU34" s="10">
+      <c r="AU34" s="7">
+        <f t="shared" si="21"/>
+        <v>16.02</v>
+      </c>
+      <c r="AV34" s="7">
+        <f t="shared" si="22"/>
+        <v>16.420000000000002</v>
+      </c>
+      <c r="AW34" s="7">
+        <f t="shared" si="23"/>
+        <v>0.40000000000000213</v>
+      </c>
+      <c r="AY34">
+        <f t="shared" si="11"/>
+        <v>1.75</v>
+      </c>
+      <c r="AZ34">
+        <f t="shared" si="12"/>
+        <v>2.57</v>
+      </c>
+      <c r="BA34">
+        <f t="shared" si="13"/>
+        <v>4.4974999999999996</v>
+      </c>
+      <c r="BB34">
+        <f t="shared" si="14"/>
+        <v>2.44</v>
+      </c>
+      <c r="BC34">
+        <f t="shared" si="15"/>
+        <v>2.39</v>
+      </c>
+      <c r="BD34">
+        <f t="shared" si="32"/>
+        <v>17.2</v>
+      </c>
+      <c r="BE34">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="BG34">
+        <f t="shared" si="17"/>
+        <v>2.66</v>
+      </c>
+      <c r="BH34">
         <f t="shared" si="18"/>
-        <v>16.02</v>
-      </c>
-      <c r="AV34" s="25">
+        <v>37.57</v>
+      </c>
+      <c r="BI34">
         <f t="shared" si="19"/>
-        <v>16.420000000000002</v>
-      </c>
-      <c r="AW34" s="25">
+        <v>17.16</v>
+      </c>
+      <c r="BJ34">
         <f t="shared" si="20"/>
-        <v>0.40000000000000213</v>
-      </c>
-      <c r="AY34">
-        <f t="shared" si="8"/>
-        <v>1.75</v>
-      </c>
-      <c r="AZ34">
-        <f t="shared" si="9"/>
-        <v>2.57</v>
-      </c>
-      <c r="BA34">
-        <f t="shared" si="10"/>
-        <v>4.4974999999999996</v>
-      </c>
-      <c r="BB34" s="21">
-        <f t="shared" si="11"/>
-        <v>2.44</v>
-      </c>
-      <c r="BC34" s="21">
-        <f t="shared" si="12"/>
-        <v>2.39</v>
-      </c>
-      <c r="BD34" s="21">
-        <f t="shared" si="21"/>
-        <v>17.2</v>
-      </c>
-      <c r="BE34" s="21">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="BG34" s="21">
-        <f t="shared" si="14"/>
-        <v>2.16</v>
-      </c>
-      <c r="BH34" s="21">
-        <f t="shared" si="15"/>
-        <v>18.82</v>
-      </c>
-      <c r="BI34" s="21">
-        <f t="shared" si="16"/>
-        <v>17.66</v>
-      </c>
-      <c r="BJ34" s="21">
-        <f t="shared" si="17"/>
-        <v>16.66</v>
+        <v>34.909999999999997</v>
       </c>
     </row>
     <row r="35" spans="1:62" x14ac:dyDescent="0.25">
@@ -9762,7 +11018,7 @@
       <c r="V35" s="2"/>
       <c r="W35" s="2"/>
       <c r="X35" s="2"/>
-      <c r="Y35" s="21"/>
+      <c r="Y35" s="17"/>
       <c r="Z35" s="2"/>
       <c r="AB35" s="1">
         <f t="shared" si="2"/>

--- a/docs/PipeDetailedDimensions.xlsx
+++ b/docs/PipeDetailedDimensions.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\organ\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\organ\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DE240E3-473D-426A-8CB1-D8E0B3C2D57D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE08A34-B2FD-47A3-A8A9-65C247B67B4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="315" yWindow="2745" windowWidth="55605" windowHeight="23445" xr2:uid="{847D2A02-6D2F-45FA-AC97-53CF17BA2C7B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="31920" xr2:uid="{847D2A02-6D2F-45FA-AC97-53CF17BA2C7B}"/>
   </bookViews>
   <sheets>
     <sheet name="AncientBourdon" sheetId="1" r:id="rId1"/>
@@ -470,7 +470,7 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="2"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -483,15 +483,16 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="2" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="4"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="5"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="5" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="5" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="5" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="5" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="5" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="20% - Accent4" xfId="3" builtinId="42"/>
@@ -1189,28 +1190,28 @@
                   <c:v>6.9283500000000018</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>7.09765625</c:v>
+                  <c:v>7.2828125000000004</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>6.63415</c:v>
+                  <c:v>6.9934000000000003</c:v>
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>6.4263999999999992</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>6.2633999999999999</c:v>
+                  <c:v>5.8344000000000005</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>5.6963999999999997</c:v>
+                  <c:v>5.2924000000000007</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>5.2224000000000004</c:v>
+                  <c:v>4.8384</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>4.9127999999999998</c:v>
+                  <c:v>4.4527999999999999</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>4.4974999999999996</c:v>
+                  <c:v>4.0599999999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1572,28 +1573,28 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>3.875</c:v>
+                  <c:v>3.95</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>3.75</c:v>
+                  <c:v>3.9</c:v>
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>3.75</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>3.9</c:v>
+                  <c:v>3.7</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>3.8</c:v>
+                  <c:v>3.6</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>3.7</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>3.65</c:v>
+                  <c:v>3.4</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>3.55</c:v>
+                  <c:v>3.3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1848,28 +1849,28 @@
                   <c:v>6.9283500000000018</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>7.09765625</c:v>
+                  <c:v>7.2828125000000004</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>6.63415</c:v>
+                  <c:v>6.9934000000000003</c:v>
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>6.4263999999999992</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>6.2633999999999999</c:v>
+                  <c:v>5.8344000000000005</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>5.6963999999999997</c:v>
+                  <c:v>5.2924000000000007</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>5.2224000000000004</c:v>
+                  <c:v>4.8384</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>4.9127999999999998</c:v>
+                  <c:v>4.4527999999999999</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>4.4974999999999996</c:v>
+                  <c:v>4.0599999999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4239,6 +4240,7 @@
     <col min="28" max="28" width="18.5703125" customWidth="1"/>
     <col min="29" max="29" width="18.85546875" customWidth="1"/>
     <col min="30" max="30" width="14.7109375" customWidth="1"/>
+    <col min="32" max="32" width="12.7109375" customWidth="1"/>
     <col min="34" max="35" width="25.85546875" customWidth="1"/>
     <col min="36" max="36" width="25.28515625" customWidth="1"/>
     <col min="37" max="37" width="22.28515625" customWidth="1"/>
@@ -4246,6 +4248,10 @@
     <col min="39" max="39" width="21.7109375" customWidth="1"/>
     <col min="40" max="40" width="18" customWidth="1"/>
     <col min="55" max="55" width="11.42578125" customWidth="1"/>
+    <col min="59" max="59" width="20.28515625" customWidth="1"/>
+    <col min="60" max="60" width="15.85546875" customWidth="1"/>
+    <col min="61" max="61" width="17" customWidth="1"/>
+    <col min="62" max="62" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:62" x14ac:dyDescent="0.25">
@@ -4460,8 +4466,9 @@
       <c r="L3" s="2">
         <v>1</v>
       </c>
-      <c r="M3">
-        <v>2.2599999999999998</v>
+      <c r="M3" s="1">
+        <f>Q3</f>
+        <v>2.238</v>
       </c>
       <c r="N3" s="1">
         <f>E3</f>
@@ -4473,15 +4480,14 @@
       <c r="P3">
         <v>8</v>
       </c>
-      <c r="Q3" s="1">
-        <f t="shared" ref="Q3:Q34" si="1">M3</f>
-        <v>2.2599999999999998</v>
-      </c>
-      <c r="R3" s="17">
-        <v>1.5</v>
-      </c>
-      <c r="S3" s="17">
-        <v>1.5</v>
+      <c r="Q3">
+        <v>2.238</v>
+      </c>
+      <c r="R3" s="15">
+        <v>1.405</v>
+      </c>
+      <c r="S3" s="15">
+        <v>1.9910000000000001</v>
       </c>
       <c r="T3" s="1">
         <f>AG3</f>
@@ -4505,16 +4511,16 @@
       <c r="Z3" s="2">
         <v>1.5</v>
       </c>
-      <c r="AA3" s="17">
+      <c r="AA3" s="15">
         <f>AF3*0.377</f>
         <v>3.2987500000000001</v>
       </c>
       <c r="AB3" s="1">
-        <f t="shared" ref="AB3:AB35" si="2">AA3</f>
+        <f t="shared" ref="AB3:AB35" si="1">AA3</f>
         <v>3.2987500000000001</v>
       </c>
       <c r="AC3" s="1">
-        <f t="shared" ref="AC3:AC35" si="3">AF3-(AG3*2)</f>
+        <f t="shared" ref="AC3:AC35" si="2">AF3-(AG3*2)</f>
         <v>7.05</v>
       </c>
       <c r="AD3">
@@ -4547,7 +4553,7 @@
       <c r="AM3" s="2">
         <v>1.62</v>
       </c>
-      <c r="AN3" s="17">
+      <c r="AN3" s="15">
         <f>AG3*0.8</f>
         <v>0.68</v>
       </c>
@@ -4559,7 +4565,7 @@
         <v>1</v>
       </c>
       <c r="AS3">
-        <f t="shared" ref="AS3:AS35" si="4">AD3/AF3</f>
+        <f t="shared" ref="AS3:AS35" si="3">AD3/AF3</f>
         <v>1.1142857142857143</v>
       </c>
       <c r="AT3">
@@ -4616,7 +4622,7 @@
         <v>42</v>
       </c>
       <c r="B4" s="1">
-        <f t="shared" ref="B4:B34" si="5">AG4</f>
+        <f t="shared" ref="B4:B34" si="4">AG4</f>
         <v>0.85</v>
       </c>
       <c r="C4">
@@ -4650,8 +4656,9 @@
       <c r="L4" s="2">
         <v>1</v>
       </c>
-      <c r="M4">
-        <v>2.2599999999999998</v>
+      <c r="M4" s="1">
+        <f t="shared" ref="M4:M34" si="5">Q4</f>
+        <v>2.2450000000000001</v>
       </c>
       <c r="N4" s="1">
         <f t="shared" ref="N4:N34" si="6">E4</f>
@@ -4663,15 +4670,14 @@
       <c r="P4">
         <v>8</v>
       </c>
-      <c r="Q4" s="1">
-        <f t="shared" si="1"/>
-        <v>2.2599999999999998</v>
-      </c>
-      <c r="R4" s="17">
-        <v>1.5</v>
-      </c>
-      <c r="S4" s="17">
-        <v>1.5</v>
+      <c r="Q4">
+        <v>2.2450000000000001</v>
+      </c>
+      <c r="R4" s="15">
+        <v>1.468</v>
+      </c>
+      <c r="S4" s="15">
+        <v>2.952</v>
       </c>
       <c r="T4" s="1">
         <f t="shared" ref="T4:T34" si="7">AG4</f>
@@ -4695,16 +4701,16 @@
       <c r="Z4" s="2">
         <v>1.5</v>
       </c>
-      <c r="AA4" s="17">
+      <c r="AA4" s="15">
         <f t="shared" ref="AA4:AA5" si="8">AF4*0.377</f>
         <v>3.1102500000000002</v>
       </c>
       <c r="AB4" s="1">
+        <f t="shared" si="1"/>
+        <v>3.1102500000000002</v>
+      </c>
+      <c r="AC4" s="1">
         <f t="shared" si="2"/>
-        <v>3.1102500000000002</v>
-      </c>
-      <c r="AC4" s="1">
-        <f t="shared" si="3"/>
         <v>6.55</v>
       </c>
       <c r="AD4">
@@ -4737,7 +4743,7 @@
       <c r="AM4" s="2">
         <v>1.62</v>
       </c>
-      <c r="AN4" s="17">
+      <c r="AN4" s="15">
         <f t="shared" ref="AN4:AN5" si="9">AG4*0.8</f>
         <v>0.68</v>
       </c>
@@ -4749,7 +4755,7 @@
         <v>1</v>
       </c>
       <c r="AS4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.1515151515151516</v>
       </c>
       <c r="AT4">
@@ -4808,7 +4814,7 @@
         <v>43</v>
       </c>
       <c r="B5" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.85</v>
       </c>
       <c r="C5">
@@ -4842,8 +4848,9 @@
       <c r="L5" s="2">
         <v>1</v>
       </c>
-      <c r="M5">
-        <v>2.2599999999999998</v>
+      <c r="M5" s="1">
+        <f t="shared" si="5"/>
+        <v>2.2330000000000001</v>
       </c>
       <c r="N5" s="1">
         <f t="shared" si="6"/>
@@ -4855,15 +4862,14 @@
       <c r="P5">
         <v>8</v>
       </c>
-      <c r="Q5" s="1">
-        <f t="shared" si="1"/>
-        <v>2.2599999999999998</v>
-      </c>
-      <c r="R5" s="17">
-        <v>1.5</v>
-      </c>
-      <c r="S5" s="17">
-        <v>1.5</v>
+      <c r="Q5">
+        <v>2.2330000000000001</v>
+      </c>
+      <c r="R5" s="15">
+        <v>1.2809999999999999</v>
+      </c>
+      <c r="S5" s="15">
+        <v>2.8</v>
       </c>
       <c r="T5" s="1">
         <f t="shared" si="7"/>
@@ -4888,16 +4894,16 @@
       <c r="Z5" s="2">
         <v>1.5</v>
       </c>
-      <c r="AA5" s="17">
+      <c r="AA5" s="15">
         <f t="shared" si="8"/>
         <v>3.016</v>
       </c>
       <c r="AB5" s="1">
+        <f t="shared" si="1"/>
+        <v>3.016</v>
+      </c>
+      <c r="AC5" s="1">
         <f t="shared" si="2"/>
-        <v>3.016</v>
-      </c>
-      <c r="AC5" s="1">
-        <f t="shared" si="3"/>
         <v>6.3</v>
       </c>
       <c r="AD5">
@@ -4930,7 +4936,7 @@
       <c r="AM5" s="2">
         <v>1.62</v>
       </c>
-      <c r="AN5" s="17">
+      <c r="AN5" s="15">
         <f t="shared" si="9"/>
         <v>0.68</v>
       </c>
@@ -4942,7 +4948,7 @@
         <v>1</v>
       </c>
       <c r="AS5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.1375</v>
       </c>
       <c r="AT5">
@@ -5001,7 +5007,7 @@
         <v>44</v>
       </c>
       <c r="B6" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.85</v>
       </c>
       <c r="C6">
@@ -5035,8 +5041,9 @@
       <c r="L6" s="2">
         <v>1</v>
       </c>
-      <c r="M6">
-        <v>2.2599999999999998</v>
+      <c r="M6" s="1">
+        <f t="shared" si="5"/>
+        <v>2.2480000000000002</v>
       </c>
       <c r="N6" s="1">
         <f t="shared" si="6"/>
@@ -5048,15 +5055,14 @@
       <c r="P6">
         <v>8</v>
       </c>
-      <c r="Q6" s="1">
-        <f>M6</f>
-        <v>2.2599999999999998</v>
+      <c r="Q6">
+        <v>2.2480000000000002</v>
       </c>
       <c r="R6">
-        <v>1.19</v>
+        <v>1.2190000000000001</v>
       </c>
       <c r="S6">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="T6" s="1">
         <f t="shared" si="7"/>
@@ -5080,7 +5086,7 @@
       <c r="Z6" s="2">
         <v>1.5</v>
       </c>
-      <c r="AA6" s="17">
+      <c r="AA6" s="15">
         <v>2.875</v>
       </c>
       <c r="AB6" s="1">
@@ -5199,7 +5205,7 @@
         <v>45</v>
       </c>
       <c r="B7" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.85</v>
       </c>
       <c r="C7">
@@ -5208,19 +5214,19 @@
       <c r="D7" s="2">
         <v>0.88</v>
       </c>
-      <c r="E7" s="17">
-        <f>AF7*0.224</f>
-        <v>1.68</v>
-      </c>
-      <c r="F7" s="17">
+      <c r="E7" s="15">
+        <f>Q7*0.76</f>
+        <v>1.4326000000000001</v>
+      </c>
+      <c r="F7" s="15">
         <f>E7+0.6</f>
-        <v>2.2799999999999998</v>
+        <v>2.0326</v>
       </c>
       <c r="G7" s="1">
         <f t="shared" si="0"/>
-        <v>1.68</v>
-      </c>
-      <c r="H7" s="17">
+        <v>1.4326000000000001</v>
+      </c>
+      <c r="H7" s="15">
         <f>(P7-1)/2</f>
         <v>3</v>
       </c>
@@ -5236,30 +5242,29 @@
       <c r="L7" s="2">
         <v>1</v>
       </c>
-      <c r="M7" s="17">
-        <f>O7-0.4</f>
-        <v>2.08</v>
+      <c r="M7" s="1">
+        <f t="shared" si="5"/>
+        <v>1.885</v>
       </c>
       <c r="N7" s="1">
         <f t="shared" si="6"/>
-        <v>1.68</v>
-      </c>
-      <c r="O7" s="17">
+        <v>1.4326000000000001</v>
+      </c>
+      <c r="O7" s="15">
         <f>E7+0.8</f>
-        <v>2.48</v>
+        <v>2.2326000000000001</v>
       </c>
       <c r="P7">
         <v>7</v>
       </c>
-      <c r="Q7" s="1">
-        <f t="shared" si="1"/>
-        <v>2.08</v>
-      </c>
-      <c r="R7" s="17">
-        <v>1.5</v>
-      </c>
-      <c r="S7" s="20">
-        <v>1.5</v>
+      <c r="Q7">
+        <v>1.885</v>
+      </c>
+      <c r="R7" s="15">
+        <v>1.321</v>
+      </c>
+      <c r="S7" s="17">
+        <v>2.7570000000000001</v>
       </c>
       <c r="T7" s="1">
         <f t="shared" si="7"/>
@@ -5283,16 +5288,16 @@
       <c r="Z7" s="2">
         <v>1.5</v>
       </c>
-      <c r="AA7" s="17">
+      <c r="AA7" s="15">
         <f>AF7*0.377</f>
         <v>2.8275000000000001</v>
       </c>
       <c r="AB7" s="1">
+        <f t="shared" si="1"/>
+        <v>2.8275000000000001</v>
+      </c>
+      <c r="AC7" s="1">
         <f t="shared" si="2"/>
-        <v>2.8275000000000001</v>
-      </c>
-      <c r="AC7" s="1">
-        <f t="shared" si="3"/>
         <v>5.8</v>
       </c>
       <c r="AD7">
@@ -5326,7 +5331,7 @@
       <c r="AM7" s="2">
         <v>1.62</v>
       </c>
-      <c r="AN7" s="17">
+      <c r="AN7" s="15">
         <f>AG7*0.8</f>
         <v>0.68</v>
       </c>
@@ -5338,7 +5343,7 @@
         <v>1</v>
       </c>
       <c r="AS7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.1166666666666667</v>
       </c>
       <c r="AT7">
@@ -5405,7 +5410,7 @@
         <v>46</v>
       </c>
       <c r="B8" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.85</v>
       </c>
       <c r="C8">
@@ -5414,19 +5419,19 @@
       <c r="D8" s="2">
         <v>0.88</v>
       </c>
-      <c r="E8" s="17">
-        <f t="shared" ref="E8:E34" si="24">AF8*0.224</f>
-        <v>1.5960000000000001</v>
-      </c>
-      <c r="F8" s="17">
+      <c r="E8" s="15">
+        <f t="shared" ref="E8:E14" si="24">Q8*0.76</f>
+        <v>1.5352000000000001</v>
+      </c>
+      <c r="F8" s="15">
         <f t="shared" ref="F8:F24" si="25">E8+0.6</f>
-        <v>2.1960000000000002</v>
+        <v>2.1352000000000002</v>
       </c>
       <c r="G8" s="1">
         <f t="shared" si="0"/>
-        <v>1.5960000000000001</v>
-      </c>
-      <c r="H8" s="17">
+        <v>1.5352000000000001</v>
+      </c>
+      <c r="H8" s="15">
         <f t="shared" ref="H8:H34" si="26">(P8-1)/2</f>
         <v>8.875</v>
       </c>
@@ -5442,30 +5447,29 @@
       <c r="L8" s="2">
         <v>1</v>
       </c>
-      <c r="M8" s="17">
-        <f t="shared" ref="M8:M24" si="27">O8-0.4</f>
-        <v>1.996</v>
+      <c r="M8" s="1">
+        <f t="shared" si="5"/>
+        <v>2.02</v>
       </c>
       <c r="N8" s="1">
         <f t="shared" si="6"/>
-        <v>1.5960000000000001</v>
-      </c>
-      <c r="O8" s="17">
-        <f t="shared" ref="O8:O24" si="28">E8+0.8</f>
-        <v>2.3959999999999999</v>
+        <v>1.5352000000000001</v>
+      </c>
+      <c r="O8" s="15">
+        <f t="shared" ref="O8:O24" si="27">E8+0.8</f>
+        <v>2.3352000000000004</v>
       </c>
       <c r="P8">
         <v>18.75</v>
       </c>
-      <c r="Q8" s="1">
-        <f t="shared" si="1"/>
-        <v>1.996</v>
-      </c>
-      <c r="R8" s="17">
-        <v>1.5</v>
-      </c>
-      <c r="S8" s="20">
-        <v>1.5</v>
+      <c r="Q8">
+        <v>2.02</v>
+      </c>
+      <c r="R8" s="15">
+        <v>4.5819999999999999</v>
+      </c>
+      <c r="S8" s="17">
+        <v>2.5579999999999998</v>
       </c>
       <c r="T8" s="1">
         <f t="shared" si="7"/>
@@ -5483,22 +5487,22 @@
       <c r="X8" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y8" s="14">
+      <c r="Y8" s="13">
         <v>10.5</v>
       </c>
       <c r="Z8" s="2">
         <v>1.5</v>
       </c>
-      <c r="AA8" s="17">
-        <f t="shared" ref="AA8:AA24" si="29">AF8*0.377</f>
+      <c r="AA8" s="15">
+        <f t="shared" ref="AA8:AA14" si="28">AF8*0.377</f>
         <v>2.6861250000000001</v>
       </c>
       <c r="AB8" s="1">
+        <f t="shared" si="1"/>
+        <v>2.6861250000000001</v>
+      </c>
+      <c r="AC8" s="1">
         <f t="shared" si="2"/>
-        <v>2.6861250000000001</v>
-      </c>
-      <c r="AC8" s="1">
-        <f t="shared" si="3"/>
         <v>5.4249999999999998</v>
       </c>
       <c r="AD8">
@@ -5532,19 +5536,19 @@
       <c r="AM8" s="2">
         <v>1.62</v>
       </c>
-      <c r="AN8" s="17">
-        <f t="shared" ref="AN8:AN24" si="30">AG8*0.8</f>
+      <c r="AN8" s="15">
+        <f t="shared" ref="AN8:AN24" si="29">AG8*0.8</f>
         <v>0.68</v>
       </c>
       <c r="AO8">
-        <f t="shared" ref="AO8:AO24" si="31">AG8*4.18</f>
+        <f t="shared" ref="AO8:AO24" si="30">AG8*4.18</f>
         <v>3.5529999999999995</v>
       </c>
       <c r="AP8">
         <v>1</v>
       </c>
       <c r="AS8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.1403508771929824</v>
       </c>
       <c r="AT8">
@@ -5611,7 +5615,7 @@
         <v>47</v>
       </c>
       <c r="B9" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.85</v>
       </c>
       <c r="C9" s="7">
@@ -5620,91 +5624,90 @@
       <c r="D9" s="9">
         <v>0.88</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="18">
         <f t="shared" si="24"/>
-        <v>1.526</v>
-      </c>
-      <c r="F9" s="17">
+        <v>1.52</v>
+      </c>
+      <c r="F9" s="18">
         <f t="shared" si="25"/>
-        <v>2.1259999999999999</v>
-      </c>
-      <c r="G9" s="1">
+        <v>2.12</v>
+      </c>
+      <c r="G9" s="8">
         <f t="shared" si="0"/>
-        <v>1.526</v>
-      </c>
-      <c r="H9" s="17">
+        <v>1.52</v>
+      </c>
+      <c r="H9" s="18">
         <f t="shared" si="26"/>
         <v>3</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="9">
         <v>3.85</v>
       </c>
-      <c r="J9" s="2">
+      <c r="J9" s="9">
         <v>6</v>
       </c>
-      <c r="K9" s="2">
+      <c r="K9" s="9">
         <v>0.4</v>
       </c>
-      <c r="L9" s="2">
-        <v>1</v>
-      </c>
-      <c r="M9" s="17">
+      <c r="L9" s="9">
+        <v>1</v>
+      </c>
+      <c r="M9" s="8">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="N9" s="8">
+        <f t="shared" si="6"/>
+        <v>1.52</v>
+      </c>
+      <c r="O9" s="18">
         <f t="shared" si="27"/>
-        <v>1.9260000000000002</v>
-      </c>
-      <c r="N9" s="1">
-        <f t="shared" si="6"/>
-        <v>1.526</v>
-      </c>
-      <c r="O9" s="17">
-        <f t="shared" si="28"/>
-        <v>2.3260000000000001</v>
+        <v>2.3200000000000003</v>
       </c>
       <c r="P9" s="7">
         <v>7</v>
       </c>
-      <c r="Q9" s="1">
-        <f t="shared" si="1"/>
-        <v>1.9260000000000002</v>
-      </c>
-      <c r="R9" s="17">
+      <c r="Q9" s="7">
+        <v>2</v>
+      </c>
+      <c r="R9" s="18">
         <v>1.5</v>
       </c>
-      <c r="S9" s="20">
+      <c r="S9" s="19">
         <v>1.5</v>
       </c>
       <c r="T9" s="8">
         <f t="shared" si="7"/>
         <v>0.85</v>
       </c>
-      <c r="U9" s="2">
+      <c r="U9" s="9">
         <v>0.44</v>
       </c>
-      <c r="V9" s="2">
+      <c r="V9" s="9">
         <v>2.16</v>
       </c>
-      <c r="W9" s="2">
+      <c r="W9" s="9">
         <v>0.85</v>
       </c>
-      <c r="X9" s="2">
+      <c r="X9" s="9">
         <v>3.66</v>
       </c>
-      <c r="Y9" s="17">
+      <c r="Y9" s="18">
         <v>26</v>
       </c>
       <c r="Z9" s="9">
         <v>1.5</v>
       </c>
-      <c r="AA9">
-        <f t="shared" si="29"/>
+      <c r="AA9" s="7">
+        <f t="shared" si="28"/>
         <v>2.5683125000000002</v>
       </c>
       <c r="AB9" s="8">
+        <f t="shared" si="1"/>
+        <v>2.5683125000000002</v>
+      </c>
+      <c r="AC9" s="8">
         <f t="shared" si="2"/>
-        <v>2.5683125000000002</v>
-      </c>
-      <c r="AC9" s="8">
-        <f t="shared" si="3"/>
         <v>5.1124999999999998</v>
       </c>
       <c r="AD9" s="12">
@@ -5740,21 +5743,19 @@
       <c r="AM9" s="9">
         <v>1.62</v>
       </c>
-      <c r="AN9" s="17">
+      <c r="AN9" s="18">
+        <f t="shared" si="29"/>
+        <v>0.68</v>
+      </c>
+      <c r="AO9" s="7">
         <f t="shared" si="30"/>
-        <v>0.68</v>
-      </c>
-      <c r="AO9">
-        <f t="shared" si="31"/>
         <v>3.5529999999999995</v>
       </c>
-      <c r="AP9">
-        <v>1</v>
-      </c>
-      <c r="AQ9"/>
-      <c r="AR9"/>
+      <c r="AP9" s="7">
+        <v>1</v>
+      </c>
       <c r="AS9" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.1376146788990826</v>
       </c>
       <c r="AT9" s="7">
@@ -5764,7 +5765,7 @@
         <f t="shared" si="21"/>
         <v>67.88</v>
       </c>
-      <c r="AV9" s="13">
+      <c r="AV9" s="12">
         <f t="shared" si="22"/>
         <v>70.3125</v>
       </c>
@@ -5772,46 +5773,46 @@
         <f t="shared" si="23"/>
         <v>2.4325000000000045</v>
       </c>
-      <c r="AY9">
+      <c r="AY9" s="7">
         <f t="shared" si="11"/>
         <v>5.1124999999999998</v>
       </c>
-      <c r="AZ9">
+      <c r="AZ9" s="7">
         <f t="shared" si="12"/>
         <v>6.05</v>
       </c>
-      <c r="BA9">
+      <c r="BA9" s="7">
         <f t="shared" si="13"/>
         <v>30.930624999999999</v>
       </c>
-      <c r="BB9">
+      <c r="BB9" s="7">
         <f t="shared" si="14"/>
         <v>6.27</v>
       </c>
-      <c r="BC9">
+      <c r="BC9" s="7">
         <f t="shared" si="15"/>
         <v>6.28</v>
       </c>
-      <c r="BD9">
+      <c r="BD9" s="7">
         <v>13.7</v>
       </c>
-      <c r="BE9">
+      <c r="BE9" s="7">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BG9">
+      <c r="BG9" s="7">
         <f t="shared" si="17"/>
         <v>28.16</v>
       </c>
-      <c r="BH9">
+      <c r="BH9" s="7">
         <f t="shared" si="18"/>
         <v>81.1875</v>
       </c>
-      <c r="BI9">
+      <c r="BI9" s="7">
         <f t="shared" si="19"/>
         <v>47.027500000000003</v>
       </c>
-      <c r="BJ9">
+      <c r="BJ9" s="7">
         <f t="shared" si="20"/>
         <v>53.027500000000003</v>
       </c>
@@ -5821,7 +5822,7 @@
         <v>48</v>
       </c>
       <c r="B10" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.75</v>
       </c>
       <c r="C10">
@@ -5830,19 +5831,19 @@
       <c r="D10" s="2">
         <v>0.75</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="15">
         <f t="shared" si="24"/>
-        <v>1.456</v>
-      </c>
-      <c r="F10" s="17">
+        <v>1.52684</v>
+      </c>
+      <c r="F10" s="15">
         <f t="shared" si="25"/>
-        <v>2.056</v>
+        <v>2.1268400000000001</v>
       </c>
       <c r="G10" s="1">
         <f t="shared" si="0"/>
-        <v>1.456</v>
-      </c>
-      <c r="H10" s="17">
+        <v>1.52684</v>
+      </c>
+      <c r="H10" s="15">
         <f t="shared" si="26"/>
         <v>8.875</v>
       </c>
@@ -5858,30 +5859,30 @@
       <c r="L10" s="2">
         <v>1</v>
       </c>
-      <c r="M10" s="17">
-        <f t="shared" si="27"/>
-        <v>1.8560000000000003</v>
+      <c r="M10" s="1">
+        <f t="shared" si="5"/>
+        <v>2.0089999999999999</v>
       </c>
       <c r="N10" s="1">
         <f t="shared" si="6"/>
-        <v>1.456</v>
-      </c>
-      <c r="O10" s="17">
-        <f t="shared" si="28"/>
-        <v>2.2560000000000002</v>
+        <v>1.52684</v>
+      </c>
+      <c r="O10" s="15">
+        <f t="shared" si="27"/>
+        <v>2.3268399999999998</v>
       </c>
       <c r="P10">
         <v>18.75</v>
       </c>
-      <c r="Q10" s="1">
-        <f t="shared" si="1"/>
-        <v>1.8560000000000003</v>
-      </c>
-      <c r="R10" s="17">
-        <v>1.5</v>
-      </c>
-      <c r="S10" s="20">
-        <v>1.5</v>
+      <c r="Q10">
+        <v>2.0089999999999999</v>
+      </c>
+      <c r="R10" s="15">
+        <f>AD10-(Q10+1.461)</f>
+        <v>3.9050000000000002</v>
+      </c>
+      <c r="S10" s="17">
+        <v>2.19</v>
       </c>
       <c r="T10" s="1">
         <f t="shared" si="7"/>
@@ -5899,22 +5900,22 @@
       <c r="X10" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y10" s="14">
+      <c r="Y10" s="13">
         <v>7.25</v>
       </c>
       <c r="Z10" s="2">
         <v>1.5</v>
       </c>
-      <c r="AA10" s="17">
-        <f t="shared" si="29"/>
+      <c r="AA10" s="15">
+        <f t="shared" si="28"/>
         <v>2.4504999999999999</v>
       </c>
       <c r="AB10" s="1">
+        <f t="shared" si="1"/>
+        <v>2.4504999999999999</v>
+      </c>
+      <c r="AC10" s="1">
         <f t="shared" si="2"/>
-        <v>2.4504999999999999</v>
-      </c>
-      <c r="AC10" s="1">
-        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="AD10">
@@ -5949,19 +5950,19 @@
       <c r="AM10" s="2">
         <v>1</v>
       </c>
-      <c r="AN10" s="17">
+      <c r="AN10" s="15">
+        <f t="shared" si="29"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="AO10">
         <f t="shared" si="30"/>
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="AO10">
-        <f t="shared" si="31"/>
         <v>3.1349999999999998</v>
       </c>
       <c r="AP10">
         <v>1</v>
       </c>
       <c r="AS10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.1346153846153846</v>
       </c>
       <c r="AT10">
@@ -6028,7 +6029,7 @@
         <v>49</v>
       </c>
       <c r="B11" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.75</v>
       </c>
       <c r="C11">
@@ -6037,19 +6038,19 @@
       <c r="D11" s="2">
         <v>0.75</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="15">
         <f t="shared" si="24"/>
-        <v>1.4000000000000001</v>
-      </c>
-      <c r="F11" s="17">
+        <v>1.3999200000000001</v>
+      </c>
+      <c r="F11" s="15">
         <f t="shared" si="25"/>
-        <v>2</v>
+        <v>1.9999199999999999</v>
       </c>
       <c r="G11" s="1">
         <f t="shared" si="0"/>
-        <v>1.4000000000000001</v>
-      </c>
-      <c r="H11" s="17">
+        <v>1.3999200000000001</v>
+      </c>
+      <c r="H11" s="15">
         <f t="shared" si="26"/>
         <v>3</v>
       </c>
@@ -6065,30 +6066,29 @@
       <c r="L11" s="2">
         <v>1</v>
       </c>
-      <c r="M11" s="17">
-        <f t="shared" si="27"/>
-        <v>1.8000000000000003</v>
+      <c r="M11" s="1">
+        <f t="shared" si="5"/>
+        <v>1.8420000000000001</v>
       </c>
       <c r="N11" s="1">
         <f t="shared" si="6"/>
-        <v>1.4000000000000001</v>
-      </c>
-      <c r="O11" s="17">
-        <f t="shared" si="28"/>
-        <v>2.2000000000000002</v>
+        <v>1.3999200000000001</v>
+      </c>
+      <c r="O11" s="15">
+        <f t="shared" si="27"/>
+        <v>2.1999200000000001</v>
       </c>
       <c r="P11">
         <v>7</v>
       </c>
-      <c r="Q11" s="1">
-        <f t="shared" si="1"/>
-        <v>1.8000000000000003</v>
-      </c>
-      <c r="R11" s="17">
-        <v>1.5</v>
-      </c>
-      <c r="S11" s="20">
-        <v>1.5</v>
+      <c r="Q11">
+        <v>1.8420000000000001</v>
+      </c>
+      <c r="R11" s="15">
+        <v>1.2335</v>
+      </c>
+      <c r="S11" s="17">
+        <v>2.1629999999999998</v>
       </c>
       <c r="T11" s="1">
         <f t="shared" si="7"/>
@@ -6106,22 +6106,22 @@
       <c r="X11" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y11" s="15">
+      <c r="Y11" s="14">
         <v>21.25</v>
       </c>
       <c r="Z11" s="2">
         <v>1.5</v>
       </c>
-      <c r="AA11" s="17">
-        <f t="shared" si="29"/>
+      <c r="AA11" s="15">
+        <f t="shared" si="28"/>
         <v>2.3562500000000002</v>
       </c>
       <c r="AB11" s="1">
+        <f t="shared" si="1"/>
+        <v>2.3562500000000002</v>
+      </c>
+      <c r="AC11" s="1">
         <f t="shared" si="2"/>
-        <v>2.3562500000000002</v>
-      </c>
-      <c r="AC11" s="1">
-        <f t="shared" si="3"/>
         <v>4.75</v>
       </c>
       <c r="AD11">
@@ -6156,19 +6156,19 @@
       <c r="AM11" s="2">
         <v>1</v>
       </c>
-      <c r="AN11" s="17">
+      <c r="AN11" s="15">
+        <f t="shared" si="29"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="AO11">
         <f t="shared" si="30"/>
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="AO11">
-        <f t="shared" si="31"/>
         <v>3.1349999999999998</v>
       </c>
       <c r="AP11">
         <v>1</v>
       </c>
       <c r="AS11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.1399999999999999</v>
       </c>
       <c r="AT11">
@@ -6207,7 +6207,7 @@
         <v>5.83</v>
       </c>
       <c r="BD11">
-        <f t="shared" ref="BD11:BD34" si="32">BD10</f>
+        <f t="shared" ref="BD11:BD34" si="31">BD10</f>
         <v>15</v>
       </c>
       <c r="BE11">
@@ -6236,7 +6236,7 @@
         <v>50</v>
       </c>
       <c r="B12" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.75</v>
       </c>
       <c r="C12">
@@ -6245,19 +6245,19 @@
       <c r="D12" s="2">
         <v>0.75</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="15">
         <f t="shared" si="24"/>
-        <v>1.3160000000000001</v>
-      </c>
-      <c r="F12" s="17">
+        <v>1.5542</v>
+      </c>
+      <c r="F12" s="15">
         <f t="shared" si="25"/>
-        <v>1.9159999999999999</v>
+        <v>2.1541999999999999</v>
       </c>
       <c r="G12" s="1">
         <f t="shared" si="0"/>
-        <v>1.3160000000000001</v>
-      </c>
-      <c r="H12" s="17">
+        <v>1.5542</v>
+      </c>
+      <c r="H12" s="15">
         <f t="shared" si="26"/>
         <v>8.875</v>
       </c>
@@ -6273,30 +6273,29 @@
       <c r="L12" s="2">
         <v>1</v>
       </c>
-      <c r="M12" s="17">
-        <f t="shared" si="27"/>
-        <v>1.7160000000000002</v>
+      <c r="M12" s="1">
+        <f t="shared" si="5"/>
+        <v>2.0449999999999999</v>
       </c>
       <c r="N12" s="1">
         <f t="shared" si="6"/>
-        <v>1.3160000000000001</v>
-      </c>
-      <c r="O12" s="17">
-        <f t="shared" si="28"/>
-        <v>2.1160000000000001</v>
+        <v>1.5542</v>
+      </c>
+      <c r="O12" s="15">
+        <f t="shared" si="27"/>
+        <v>2.3542000000000001</v>
       </c>
       <c r="P12">
         <v>18.75</v>
       </c>
-      <c r="Q12" s="1">
-        <f t="shared" si="1"/>
-        <v>1.7160000000000002</v>
-      </c>
-      <c r="R12" s="17">
-        <v>1.5</v>
-      </c>
-      <c r="S12" s="20">
-        <v>1.5</v>
+      <c r="Q12">
+        <v>2.0449999999999999</v>
+      </c>
+      <c r="R12" s="15">
+        <v>3.5510000000000002</v>
+      </c>
+      <c r="S12" s="17">
+        <v>2.0049999999999999</v>
       </c>
       <c r="T12" s="1">
         <f t="shared" si="7"/>
@@ -6314,22 +6313,22 @@
       <c r="X12" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y12" s="14">
+      <c r="Y12" s="13">
         <v>5.5</v>
       </c>
       <c r="Z12" s="2">
         <v>1.25</v>
       </c>
-      <c r="AA12" s="17">
-        <f t="shared" si="29"/>
+      <c r="AA12" s="15">
+        <f t="shared" si="28"/>
         <v>2.2148750000000001</v>
       </c>
       <c r="AB12" s="1">
+        <f t="shared" si="1"/>
+        <v>2.2148750000000001</v>
+      </c>
+      <c r="AC12" s="1">
         <f t="shared" si="2"/>
-        <v>2.2148750000000001</v>
-      </c>
-      <c r="AC12" s="1">
-        <f t="shared" si="3"/>
         <v>4.375</v>
       </c>
       <c r="AD12">
@@ -6365,19 +6364,19 @@
       <c r="AM12" s="2">
         <v>1</v>
       </c>
-      <c r="AN12" s="17">
+      <c r="AN12" s="15">
+        <f t="shared" si="29"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="AO12">
         <f t="shared" si="30"/>
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="AO12">
-        <f t="shared" si="31"/>
         <v>3.1349999999999998</v>
       </c>
       <c r="AP12">
         <v>1</v>
       </c>
       <c r="AS12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.1702127659574468</v>
       </c>
       <c r="AT12">
@@ -6444,7 +6443,7 @@
         <v>51</v>
       </c>
       <c r="B13" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.75</v>
       </c>
       <c r="C13" s="7">
@@ -6453,91 +6452,90 @@
       <c r="D13" s="9">
         <v>0.75</v>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="18">
         <f t="shared" si="24"/>
-        <v>1.2768000000000002</v>
-      </c>
-      <c r="F13" s="17">
+        <v>1.3680000000000001</v>
+      </c>
+      <c r="F13" s="18">
         <f t="shared" si="25"/>
-        <v>1.8768000000000002</v>
-      </c>
-      <c r="G13" s="1">
+        <v>1.968</v>
+      </c>
+      <c r="G13" s="8">
         <f t="shared" si="0"/>
-        <v>1.2768000000000002</v>
-      </c>
-      <c r="H13" s="17">
+        <v>1.3680000000000001</v>
+      </c>
+      <c r="H13" s="18">
         <f t="shared" si="26"/>
         <v>3</v>
       </c>
-      <c r="I13" s="2">
+      <c r="I13" s="9">
         <v>3.85</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J13" s="9">
         <v>6</v>
       </c>
-      <c r="K13" s="2">
+      <c r="K13" s="9">
         <v>0.4</v>
       </c>
-      <c r="L13" s="2">
-        <v>1</v>
-      </c>
-      <c r="M13" s="17">
+      <c r="L13" s="9">
+        <v>1</v>
+      </c>
+      <c r="M13" s="8">
+        <f t="shared" si="5"/>
+        <v>1.8</v>
+      </c>
+      <c r="N13" s="8">
+        <f t="shared" si="6"/>
+        <v>1.3680000000000001</v>
+      </c>
+      <c r="O13" s="18">
         <f t="shared" si="27"/>
-        <v>1.6768000000000005</v>
-      </c>
-      <c r="N13" s="1">
-        <f t="shared" si="6"/>
-        <v>1.2768000000000002</v>
-      </c>
-      <c r="O13" s="17">
-        <f t="shared" si="28"/>
-        <v>2.0768000000000004</v>
+        <v>2.1680000000000001</v>
       </c>
       <c r="P13" s="7">
         <v>7</v>
       </c>
-      <c r="Q13" s="1">
-        <f t="shared" si="1"/>
-        <v>1.6768000000000005</v>
-      </c>
-      <c r="R13" s="17">
+      <c r="Q13" s="7">
+        <v>1.8</v>
+      </c>
+      <c r="R13" s="18">
         <v>1.5</v>
       </c>
-      <c r="S13" s="20">
+      <c r="S13" s="19">
         <v>1.5</v>
       </c>
       <c r="T13" s="8">
         <f t="shared" si="7"/>
         <v>0.75</v>
       </c>
-      <c r="U13" s="2">
+      <c r="U13" s="9">
         <v>0.44</v>
       </c>
-      <c r="V13" s="2">
+      <c r="V13" s="9">
         <v>2.16</v>
       </c>
-      <c r="W13" s="2">
+      <c r="W13" s="9">
         <v>0.85</v>
       </c>
-      <c r="X13" s="2">
+      <c r="X13" s="9">
         <v>3.66</v>
       </c>
-      <c r="Y13" s="17">
+      <c r="Y13" s="18">
         <v>17.5</v>
       </c>
       <c r="Z13" s="9">
         <v>1.25</v>
       </c>
-      <c r="AA13" s="17">
-        <f t="shared" si="29"/>
+      <c r="AA13" s="18">
+        <f t="shared" si="28"/>
         <v>2.1489000000000003</v>
       </c>
       <c r="AB13" s="8">
+        <f t="shared" si="1"/>
+        <v>2.1489000000000003</v>
+      </c>
+      <c r="AC13" s="8">
         <f t="shared" si="2"/>
-        <v>2.1489000000000003</v>
-      </c>
-      <c r="AC13" s="8">
-        <f t="shared" si="3"/>
         <v>4.2</v>
       </c>
       <c r="AD13" s="12">
@@ -6571,21 +6569,19 @@
       <c r="AM13" s="9">
         <v>1</v>
       </c>
-      <c r="AN13" s="17">
+      <c r="AN13" s="18">
+        <f t="shared" si="29"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="AO13" s="7">
         <f t="shared" si="30"/>
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="AO13">
-        <f t="shared" si="31"/>
         <v>3.1349999999999998</v>
       </c>
-      <c r="AP13">
-        <v>1</v>
-      </c>
-      <c r="AQ13"/>
-      <c r="AR13"/>
+      <c r="AP13" s="7">
+        <v>1</v>
+      </c>
       <c r="AS13" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.1666666666666667</v>
       </c>
       <c r="AT13" s="7">
@@ -6595,7 +6591,7 @@
         <f t="shared" si="21"/>
         <v>53.88</v>
       </c>
-      <c r="AV13" s="13">
+      <c r="AV13" s="12">
         <f t="shared" si="22"/>
         <v>55.625</v>
       </c>
@@ -6603,46 +6599,46 @@
         <f t="shared" si="23"/>
         <v>1.7449999999999974</v>
       </c>
-      <c r="AY13">
+      <c r="AY13" s="7">
         <f t="shared" si="11"/>
         <v>4.2</v>
       </c>
-      <c r="AZ13">
+      <c r="AZ13" s="7">
         <f t="shared" si="12"/>
         <v>5.15</v>
       </c>
-      <c r="BA13">
+      <c r="BA13" s="7">
         <f t="shared" si="13"/>
         <v>21.630000000000003</v>
       </c>
-      <c r="BB13">
+      <c r="BB13" s="7">
         <f t="shared" si="14"/>
         <v>5.35</v>
       </c>
-      <c r="BC13">
+      <c r="BC13" s="7">
         <f t="shared" si="15"/>
         <v>5.25</v>
       </c>
-      <c r="BD13">
+      <c r="BD13" s="7">
         <v>15</v>
       </c>
-      <c r="BE13">
+      <c r="BE13" s="7">
         <f t="shared" si="16"/>
         <v>-0.1</v>
       </c>
-      <c r="BG13">
+      <c r="BG13" s="7">
         <f t="shared" si="17"/>
         <v>19.66</v>
       </c>
-      <c r="BH13">
+      <c r="BH13" s="7">
         <f t="shared" si="18"/>
         <v>66.5</v>
       </c>
-      <c r="BI13">
+      <c r="BI13" s="7">
         <f t="shared" si="19"/>
         <v>40.840000000000003</v>
       </c>
-      <c r="BJ13">
+      <c r="BJ13" s="7">
         <f t="shared" si="20"/>
         <v>46.84</v>
       </c>
@@ -6652,7 +6648,7 @@
         <v>52</v>
       </c>
       <c r="B14" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.75</v>
       </c>
       <c r="C14" s="3">
@@ -6661,19 +6657,19 @@
       <c r="D14" s="4">
         <v>0.75</v>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="15">
         <f t="shared" si="24"/>
-        <v>1.26</v>
-      </c>
-      <c r="F14" s="17">
+        <v>1.254</v>
+      </c>
+      <c r="F14" s="15">
         <f t="shared" si="25"/>
-        <v>1.8599999999999999</v>
+        <v>1.8540000000000001</v>
       </c>
       <c r="G14" s="1">
         <f t="shared" si="0"/>
-        <v>1.26</v>
-      </c>
-      <c r="H14" s="17">
+        <v>1.254</v>
+      </c>
+      <c r="H14" s="15">
         <f t="shared" si="26"/>
         <v>8.875</v>
       </c>
@@ -6689,30 +6685,29 @@
       <c r="L14" s="2">
         <v>1</v>
       </c>
-      <c r="M14" s="17">
-        <f t="shared" si="27"/>
-        <v>1.6600000000000001</v>
+      <c r="M14" s="1">
+        <f t="shared" si="5"/>
+        <v>1.65</v>
       </c>
       <c r="N14" s="1">
         <f t="shared" si="6"/>
-        <v>1.26</v>
-      </c>
-      <c r="O14" s="17">
-        <f t="shared" si="28"/>
-        <v>2.06</v>
+        <v>1.254</v>
+      </c>
+      <c r="O14" s="15">
+        <f t="shared" si="27"/>
+        <v>2.0540000000000003</v>
       </c>
       <c r="P14" s="3">
         <v>18.75</v>
       </c>
-      <c r="Q14" s="1">
-        <f t="shared" si="1"/>
-        <v>1.6600000000000001</v>
-      </c>
-      <c r="R14" s="17">
-        <v>1.5</v>
-      </c>
-      <c r="S14" s="20">
-        <v>1.5</v>
+      <c r="Q14">
+        <v>1.65</v>
+      </c>
+      <c r="R14" s="15">
+        <v>3.39</v>
+      </c>
+      <c r="S14" s="17">
+        <v>1.95</v>
       </c>
       <c r="T14" s="6">
         <f t="shared" si="7"/>
@@ -6730,22 +6725,22 @@
       <c r="X14" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y14" s="14">
+      <c r="Y14" s="13">
         <v>3.5</v>
       </c>
       <c r="Z14" s="4">
         <v>1.25</v>
       </c>
-      <c r="AA14" s="17">
-        <f t="shared" si="29"/>
+      <c r="AA14" s="15">
+        <f t="shared" si="28"/>
         <v>2.120625</v>
       </c>
       <c r="AB14" s="6">
+        <f t="shared" si="1"/>
+        <v>2.120625</v>
+      </c>
+      <c r="AC14" s="6">
         <f t="shared" si="2"/>
-        <v>2.120625</v>
-      </c>
-      <c r="AC14" s="6">
-        <f t="shared" si="3"/>
         <v>4.125</v>
       </c>
       <c r="AD14" s="3">
@@ -6780,12 +6775,12 @@
       <c r="AM14" s="4">
         <v>1</v>
       </c>
-      <c r="AN14" s="17">
+      <c r="AN14" s="15">
+        <f t="shared" si="29"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="AO14">
         <f t="shared" si="30"/>
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="AO14">
-        <f t="shared" si="31"/>
         <v>3.1349999999999998</v>
       </c>
       <c r="AP14">
@@ -6794,7 +6789,7 @@
       <c r="AQ14"/>
       <c r="AR14"/>
       <c r="AS14" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.1555555555555554</v>
       </c>
       <c r="AT14">
@@ -6833,7 +6828,7 @@
         <v>5.12</v>
       </c>
       <c r="BD14">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>15</v>
       </c>
       <c r="BE14">
@@ -6862,7 +6857,7 @@
         <v>53</v>
       </c>
       <c r="B15" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.63</v>
       </c>
       <c r="C15">
@@ -6871,19 +6866,19 @@
       <c r="D15" s="2">
         <v>0.75</v>
       </c>
-      <c r="E15" s="17">
-        <f t="shared" si="24"/>
-        <v>1.19</v>
-      </c>
-      <c r="F15" s="17">
+      <c r="E15" s="15">
+        <f>Q15*0.6</f>
+        <v>1.0475999999999999</v>
+      </c>
+      <c r="F15" s="15">
         <f t="shared" si="25"/>
-        <v>1.79</v>
+        <v>1.6475999999999997</v>
       </c>
       <c r="G15" s="1">
         <f t="shared" si="0"/>
-        <v>1.19</v>
-      </c>
-      <c r="H15" s="17">
+        <v>1.0475999999999999</v>
+      </c>
+      <c r="H15" s="15">
         <f t="shared" si="26"/>
         <v>3</v>
       </c>
@@ -6899,30 +6894,29 @@
       <c r="L15" s="2">
         <v>1</v>
       </c>
-      <c r="M15" s="17">
-        <f t="shared" si="27"/>
-        <v>1.5899999999999999</v>
+      <c r="M15" s="1">
+        <f t="shared" si="5"/>
+        <v>1.746</v>
       </c>
       <c r="N15" s="1">
         <f t="shared" si="6"/>
-        <v>1.19</v>
-      </c>
-      <c r="O15" s="17">
-        <f t="shared" si="28"/>
-        <v>1.99</v>
+        <v>1.0475999999999999</v>
+      </c>
+      <c r="O15" s="15">
+        <f t="shared" si="27"/>
+        <v>1.8475999999999999</v>
       </c>
       <c r="P15">
         <v>7</v>
       </c>
-      <c r="Q15" s="1">
-        <f t="shared" si="1"/>
-        <v>1.5899999999999999</v>
-      </c>
-      <c r="R15" s="17">
-        <v>1.5</v>
-      </c>
-      <c r="S15" s="20">
-        <v>1.5</v>
+      <c r="Q15">
+        <v>1.746</v>
+      </c>
+      <c r="R15" s="15">
+        <v>1.37</v>
+      </c>
+      <c r="S15" s="17">
+        <v>1.8</v>
       </c>
       <c r="T15" s="5">
         <f t="shared" si="7"/>
@@ -6940,22 +6934,22 @@
       <c r="X15" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y15" s="15">
+      <c r="Y15" s="14">
         <v>14.25</v>
       </c>
       <c r="Z15" s="2">
         <v>1.25</v>
       </c>
-      <c r="AA15" s="17">
+      <c r="AA15" s="15">
         <f>AF15*0.344</f>
         <v>1.8274999999999999</v>
       </c>
       <c r="AB15" s="5">
+        <f t="shared" si="1"/>
+        <v>1.8274999999999999</v>
+      </c>
+      <c r="AC15" s="5">
         <f t="shared" si="2"/>
-        <v>1.8274999999999999</v>
-      </c>
-      <c r="AC15" s="5">
-        <f t="shared" si="3"/>
         <v>4.0525000000000002</v>
       </c>
       <c r="AD15">
@@ -6989,19 +6983,19 @@
       <c r="AM15" s="2">
         <v>1</v>
       </c>
-      <c r="AN15" s="17">
+      <c r="AN15" s="15">
+        <f t="shared" si="29"/>
+        <v>0.504</v>
+      </c>
+      <c r="AO15">
         <f t="shared" si="30"/>
-        <v>0.504</v>
-      </c>
-      <c r="AO15">
-        <f t="shared" si="31"/>
         <v>2.6334</v>
       </c>
       <c r="AP15">
         <v>0</v>
       </c>
       <c r="AS15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.1764705882352942</v>
       </c>
       <c r="AT15">
@@ -7068,7 +7062,7 @@
         <v>54</v>
       </c>
       <c r="B16" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.63</v>
       </c>
       <c r="C16">
@@ -7077,19 +7071,19 @@
       <c r="D16" s="2">
         <v>0.75</v>
       </c>
-      <c r="E16" s="17">
-        <f t="shared" si="24"/>
-        <v>1.1480000000000001</v>
-      </c>
-      <c r="F16" s="17">
+      <c r="E16" s="15">
+        <f t="shared" ref="E16:E24" si="32">Q16*0.6</f>
+        <v>1.0595999999999999</v>
+      </c>
+      <c r="F16" s="15">
         <f t="shared" si="25"/>
-        <v>1.7480000000000002</v>
+        <v>1.6595999999999997</v>
       </c>
       <c r="G16" s="1">
         <f t="shared" si="0"/>
-        <v>1.1480000000000001</v>
-      </c>
-      <c r="H16" s="17">
+        <v>1.0595999999999999</v>
+      </c>
+      <c r="H16" s="15">
         <f t="shared" si="26"/>
         <v>8.875</v>
       </c>
@@ -7105,30 +7099,29 @@
       <c r="L16" s="2">
         <v>1</v>
       </c>
-      <c r="M16" s="17">
-        <f t="shared" si="27"/>
-        <v>1.548</v>
+      <c r="M16" s="1">
+        <f t="shared" si="5"/>
+        <v>1.766</v>
       </c>
       <c r="N16" s="1">
         <f t="shared" si="6"/>
-        <v>1.1480000000000001</v>
-      </c>
-      <c r="O16" s="17">
-        <f t="shared" si="28"/>
-        <v>1.9480000000000002</v>
+        <v>1.0595999999999999</v>
+      </c>
+      <c r="O16" s="15">
+        <f t="shared" si="27"/>
+        <v>1.8595999999999999</v>
       </c>
       <c r="P16">
         <v>18.75</v>
       </c>
-      <c r="Q16" s="1">
-        <f t="shared" si="1"/>
-        <v>1.548</v>
-      </c>
-      <c r="R16" s="17">
-        <v>1.5</v>
-      </c>
-      <c r="S16" s="20">
-        <v>1.5</v>
+      <c r="Q16">
+        <v>1.766</v>
+      </c>
+      <c r="R16" s="15">
+        <v>2.9569999999999999</v>
+      </c>
+      <c r="S16" s="17">
+        <v>1.677</v>
       </c>
       <c r="T16" s="1">
         <f t="shared" si="7"/>
@@ -7146,23 +7139,23 @@
       <c r="X16" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y16" s="14">
+      <c r="Y16" s="13">
         <f>2+7/8</f>
         <v>2.875</v>
       </c>
       <c r="Z16" s="2">
         <v>1.25</v>
       </c>
-      <c r="AA16" s="17">
-        <f t="shared" ref="AA16:AA24" si="33">AF16*0.344</f>
+      <c r="AA16" s="15">
+        <f t="shared" ref="AA16:AA20" si="33">AF16*0.344</f>
         <v>1.7629999999999999</v>
       </c>
       <c r="AB16" s="1">
+        <f t="shared" si="1"/>
+        <v>1.7629999999999999</v>
+      </c>
+      <c r="AC16" s="1">
         <f t="shared" si="2"/>
-        <v>1.7629999999999999</v>
-      </c>
-      <c r="AC16" s="1">
-        <f t="shared" si="3"/>
         <v>3.8650000000000002</v>
       </c>
       <c r="AD16">
@@ -7198,19 +7191,19 @@
       <c r="AM16" s="2">
         <v>1</v>
       </c>
-      <c r="AN16" s="17">
+      <c r="AN16" s="15">
+        <f t="shared" si="29"/>
+        <v>0.504</v>
+      </c>
+      <c r="AO16">
         <f t="shared" si="30"/>
-        <v>0.504</v>
-      </c>
-      <c r="AO16">
-        <f t="shared" si="31"/>
         <v>2.6334</v>
       </c>
       <c r="AP16">
         <v>0</v>
       </c>
       <c r="AS16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.1463414634146341</v>
       </c>
       <c r="AT16">
@@ -7277,7 +7270,7 @@
         <v>55</v>
       </c>
       <c r="B17" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.63</v>
       </c>
       <c r="C17">
@@ -7286,19 +7279,19 @@
       <c r="D17" s="2">
         <v>0.75</v>
       </c>
-      <c r="E17" s="17">
-        <f t="shared" si="24"/>
-        <v>1.1060000000000001</v>
-      </c>
-      <c r="F17" s="17">
+      <c r="E17" s="15">
+        <f t="shared" si="32"/>
+        <v>1.0571999999999999</v>
+      </c>
+      <c r="F17" s="15">
         <f t="shared" si="25"/>
-        <v>1.706</v>
+        <v>1.6572</v>
       </c>
       <c r="G17" s="1">
         <f t="shared" si="0"/>
-        <v>1.1060000000000001</v>
-      </c>
-      <c r="H17" s="17">
+        <v>1.0571999999999999</v>
+      </c>
+      <c r="H17" s="15">
         <f t="shared" si="26"/>
         <v>3</v>
       </c>
@@ -7314,30 +7307,29 @@
       <c r="L17" s="2">
         <v>1</v>
       </c>
-      <c r="M17" s="17">
-        <f t="shared" si="27"/>
-        <v>1.5060000000000002</v>
+      <c r="M17" s="1">
+        <f t="shared" si="5"/>
+        <v>1.762</v>
       </c>
       <c r="N17" s="1">
         <f t="shared" si="6"/>
-        <v>1.1060000000000001</v>
-      </c>
-      <c r="O17" s="17">
-        <f t="shared" si="28"/>
-        <v>1.9060000000000001</v>
+        <v>1.0571999999999999</v>
+      </c>
+      <c r="O17" s="15">
+        <f t="shared" si="27"/>
+        <v>1.8572</v>
       </c>
       <c r="P17">
         <v>7</v>
       </c>
-      <c r="Q17" s="1">
-        <f t="shared" si="1"/>
-        <v>1.5060000000000002</v>
-      </c>
-      <c r="R17" s="17">
-        <v>1.5</v>
-      </c>
-      <c r="S17" s="20">
-        <v>1.5</v>
+      <c r="Q17">
+        <v>1.762</v>
+      </c>
+      <c r="R17" s="15">
+        <v>1.2749999999999999</v>
+      </c>
+      <c r="S17" s="17">
+        <v>1.5760000000000001</v>
       </c>
       <c r="T17" s="1">
         <f t="shared" si="7"/>
@@ -7355,22 +7347,22 @@
       <c r="X17" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y17" s="15">
+      <c r="Y17" s="14">
         <v>11.25</v>
       </c>
       <c r="Z17" s="2">
         <v>1.25</v>
       </c>
-      <c r="AA17" s="17">
+      <c r="AA17" s="15">
         <f t="shared" si="33"/>
         <v>1.6984999999999999</v>
       </c>
       <c r="AB17" s="1">
+        <f t="shared" si="1"/>
+        <v>1.6984999999999999</v>
+      </c>
+      <c r="AC17" s="1">
         <f t="shared" si="2"/>
-        <v>1.6984999999999999</v>
-      </c>
-      <c r="AC17" s="1">
-        <f t="shared" si="3"/>
         <v>3.6775000000000002</v>
       </c>
       <c r="AD17">
@@ -7406,19 +7398,19 @@
       <c r="AM17" s="2">
         <v>1</v>
       </c>
-      <c r="AN17" s="17">
+      <c r="AN17" s="15">
+        <f t="shared" si="29"/>
+        <v>0.504</v>
+      </c>
+      <c r="AO17">
         <f t="shared" si="30"/>
-        <v>0.504</v>
-      </c>
-      <c r="AO17">
-        <f t="shared" si="31"/>
         <v>2.6334</v>
       </c>
       <c r="AP17">
         <v>0</v>
       </c>
       <c r="AS17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.1518987341772151</v>
       </c>
       <c r="AT17">
@@ -7457,7 +7449,7 @@
         <v>4.55</v>
       </c>
       <c r="BD17">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>15.5</v>
       </c>
       <c r="BE17">
@@ -7486,7 +7478,7 @@
         <v>56</v>
       </c>
       <c r="B18" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.63</v>
       </c>
       <c r="C18">
@@ -7495,19 +7487,19 @@
       <c r="D18" s="2">
         <v>0.75</v>
       </c>
-      <c r="E18" s="17">
-        <f t="shared" si="24"/>
-        <v>1.0640000000000001</v>
-      </c>
-      <c r="F18" s="17">
+      <c r="E18" s="15">
+        <f t="shared" si="32"/>
+        <v>1.0451999999999999</v>
+      </c>
+      <c r="F18" s="15">
         <f t="shared" si="25"/>
-        <v>1.6640000000000001</v>
+        <v>1.6452</v>
       </c>
       <c r="G18" s="1">
         <f t="shared" si="0"/>
-        <v>1.0640000000000001</v>
-      </c>
-      <c r="H18" s="17">
+        <v>1.0451999999999999</v>
+      </c>
+      <c r="H18" s="15">
         <f t="shared" si="26"/>
         <v>8.875</v>
       </c>
@@ -7523,30 +7515,29 @@
       <c r="L18" s="2">
         <v>1</v>
       </c>
-      <c r="M18" s="17">
-        <f t="shared" si="27"/>
-        <v>1.464</v>
+      <c r="M18" s="1">
+        <f t="shared" si="5"/>
+        <v>1.742</v>
       </c>
       <c r="N18" s="1">
         <f t="shared" si="6"/>
-        <v>1.0640000000000001</v>
-      </c>
-      <c r="O18" s="17">
-        <f t="shared" si="28"/>
-        <v>1.8640000000000001</v>
+        <v>1.0451999999999999</v>
+      </c>
+      <c r="O18" s="15">
+        <f t="shared" si="27"/>
+        <v>1.8452</v>
       </c>
       <c r="P18">
         <v>18.75</v>
       </c>
-      <c r="Q18" s="1">
-        <f t="shared" si="1"/>
-        <v>1.464</v>
-      </c>
-      <c r="R18" s="17">
-        <v>1.5</v>
-      </c>
-      <c r="S18" s="20">
-        <v>1.5</v>
+      <c r="Q18">
+        <v>1.742</v>
+      </c>
+      <c r="R18" s="15">
+        <v>2.5920000000000001</v>
+      </c>
+      <c r="S18" s="17">
+        <v>1.6319999999999999</v>
       </c>
       <c r="T18" s="1">
         <f t="shared" si="7"/>
@@ -7564,22 +7555,22 @@
       <c r="X18" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y18" s="14">
+      <c r="Y18" s="13">
         <v>2</v>
       </c>
       <c r="Z18" s="2">
         <v>1.25</v>
       </c>
-      <c r="AA18" s="17">
+      <c r="AA18" s="15">
         <f t="shared" si="33"/>
         <v>1.6339999999999999</v>
       </c>
       <c r="AB18" s="1">
+        <f t="shared" si="1"/>
+        <v>1.6339999999999999</v>
+      </c>
+      <c r="AC18" s="1">
         <f t="shared" si="2"/>
-        <v>1.6339999999999999</v>
-      </c>
-      <c r="AC18" s="1">
-        <f t="shared" si="3"/>
         <v>3.49</v>
       </c>
       <c r="AD18">
@@ -7614,19 +7605,19 @@
       <c r="AM18" s="2">
         <v>1</v>
       </c>
-      <c r="AN18" s="17">
+      <c r="AN18" s="15">
+        <f t="shared" si="29"/>
+        <v>0.504</v>
+      </c>
+      <c r="AO18">
         <f t="shared" si="30"/>
-        <v>0.504</v>
-      </c>
-      <c r="AO18">
-        <f t="shared" si="31"/>
         <v>2.6334</v>
       </c>
       <c r="AP18">
         <v>0</v>
       </c>
       <c r="AS18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.1578947368421053</v>
       </c>
       <c r="AT18">
@@ -7665,7 +7656,7 @@
         <v>4.34</v>
       </c>
       <c r="BD18">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>15.5</v>
       </c>
       <c r="BE18">
@@ -7694,7 +7685,7 @@
         <v>57</v>
       </c>
       <c r="B19" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.63</v>
       </c>
       <c r="C19">
@@ -7703,19 +7694,19 @@
       <c r="D19" s="2">
         <v>0.75</v>
       </c>
-      <c r="E19" s="17">
-        <f t="shared" si="24"/>
-        <v>1.022</v>
-      </c>
-      <c r="F19" s="17">
+      <c r="E19" s="15">
+        <f t="shared" si="32"/>
+        <v>0.81989999999999996</v>
+      </c>
+      <c r="F19" s="15">
         <f t="shared" si="25"/>
-        <v>1.6219999999999999</v>
+        <v>1.4198999999999999</v>
       </c>
       <c r="G19" s="1">
         <f t="shared" si="0"/>
-        <v>1.022</v>
-      </c>
-      <c r="H19" s="17">
+        <v>0.81989999999999996</v>
+      </c>
+      <c r="H19" s="15">
         <f t="shared" si="26"/>
         <v>3</v>
       </c>
@@ -7731,30 +7722,29 @@
       <c r="L19" s="2">
         <v>1</v>
       </c>
-      <c r="M19" s="17">
-        <f t="shared" si="27"/>
-        <v>1.4220000000000002</v>
+      <c r="M19" s="1">
+        <f t="shared" si="5"/>
+        <v>1.3665</v>
       </c>
       <c r="N19" s="1">
         <f t="shared" si="6"/>
-        <v>1.022</v>
-      </c>
-      <c r="O19" s="17">
-        <f t="shared" si="28"/>
-        <v>1.8220000000000001</v>
+        <v>0.81989999999999996</v>
+      </c>
+      <c r="O19" s="15">
+        <f t="shared" si="27"/>
+        <v>1.6198999999999999</v>
       </c>
       <c r="P19">
         <v>7</v>
       </c>
-      <c r="Q19" s="1">
-        <f t="shared" si="1"/>
-        <v>1.4220000000000002</v>
-      </c>
-      <c r="R19" s="17">
-        <v>1.5</v>
-      </c>
-      <c r="S19" s="20">
-        <v>1.5</v>
+      <c r="Q19">
+        <v>1.3665</v>
+      </c>
+      <c r="R19" s="15">
+        <v>1.39</v>
+      </c>
+      <c r="S19" s="17">
+        <v>2.3929999999999998</v>
       </c>
       <c r="T19" s="1">
         <f t="shared" si="7"/>
@@ -7772,22 +7762,22 @@
       <c r="X19" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y19" s="15">
+      <c r="Y19" s="14">
         <v>9.5</v>
       </c>
       <c r="Z19" s="2">
         <v>1.25</v>
       </c>
-      <c r="AA19" s="17">
+      <c r="AA19" s="15">
         <f t="shared" si="33"/>
         <v>1.5694999999999999</v>
       </c>
       <c r="AB19" s="1">
+        <f t="shared" si="1"/>
+        <v>1.5694999999999999</v>
+      </c>
+      <c r="AC19" s="1">
         <f t="shared" si="2"/>
-        <v>1.5694999999999999</v>
-      </c>
-      <c r="AC19" s="1">
-        <f t="shared" si="3"/>
         <v>3.3025000000000002</v>
       </c>
       <c r="AD19">
@@ -7823,19 +7813,19 @@
       <c r="AM19" s="2">
         <v>1</v>
       </c>
-      <c r="AN19" s="17">
+      <c r="AN19" s="15">
+        <f t="shared" si="29"/>
+        <v>0.504</v>
+      </c>
+      <c r="AO19">
         <f t="shared" si="30"/>
-        <v>0.504</v>
-      </c>
-      <c r="AO19">
-        <f t="shared" si="31"/>
         <v>2.6334</v>
       </c>
       <c r="AP19">
         <v>0</v>
       </c>
       <c r="AS19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.1643835616438356</v>
       </c>
       <c r="AT19">
@@ -7874,7 +7864,7 @@
         <v>4.13</v>
       </c>
       <c r="BD19">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>15.5</v>
       </c>
       <c r="BE19">
@@ -7903,7 +7893,7 @@
         <v>58</v>
       </c>
       <c r="B20" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.63</v>
       </c>
       <c r="C20">
@@ -7912,19 +7902,19 @@
       <c r="D20" s="2">
         <v>0.65</v>
       </c>
-      <c r="E20" s="17">
-        <f t="shared" si="24"/>
-        <v>0.98</v>
-      </c>
-      <c r="F20" s="17">
+      <c r="E20" s="15">
+        <f t="shared" si="32"/>
+        <v>0.83579999999999999</v>
+      </c>
+      <c r="F20" s="15">
         <f t="shared" si="25"/>
-        <v>1.58</v>
+        <v>1.4358</v>
       </c>
       <c r="G20" s="1">
         <f t="shared" si="0"/>
-        <v>0.98</v>
-      </c>
-      <c r="H20" s="17">
+        <v>0.83579999999999999</v>
+      </c>
+      <c r="H20" s="15">
         <f t="shared" si="26"/>
         <v>8.875</v>
       </c>
@@ -7940,30 +7930,29 @@
       <c r="L20" s="2">
         <v>1</v>
       </c>
-      <c r="M20" s="17">
-        <f t="shared" si="27"/>
-        <v>1.38</v>
+      <c r="M20" s="1">
+        <f t="shared" si="5"/>
+        <v>1.393</v>
       </c>
       <c r="N20" s="1">
         <f t="shared" si="6"/>
-        <v>0.98</v>
-      </c>
-      <c r="O20" s="17">
-        <f t="shared" si="28"/>
-        <v>1.78</v>
+        <v>0.83579999999999999</v>
+      </c>
+      <c r="O20" s="15">
+        <f t="shared" si="27"/>
+        <v>1.6358000000000001</v>
       </c>
       <c r="P20">
         <v>18.75</v>
       </c>
-      <c r="Q20" s="1">
-        <f t="shared" si="1"/>
-        <v>1.38</v>
-      </c>
-      <c r="R20" s="17">
-        <v>1.5</v>
-      </c>
-      <c r="S20" s="20">
-        <v>1.5</v>
+      <c r="Q20">
+        <v>1.393</v>
+      </c>
+      <c r="R20" s="15">
+        <v>1.8779999999999999</v>
+      </c>
+      <c r="S20" s="17">
+        <v>1.512</v>
       </c>
       <c r="T20" s="1">
         <f t="shared" si="7"/>
@@ -7981,22 +7970,22 @@
       <c r="X20" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y20" s="14">
+      <c r="Y20" s="13">
         <v>1.75</v>
       </c>
       <c r="Z20" s="2">
         <v>1.25</v>
       </c>
-      <c r="AA20" s="17">
+      <c r="AA20" s="15">
         <f t="shared" si="33"/>
         <v>1.5049999999999999</v>
       </c>
       <c r="AB20" s="1">
+        <f t="shared" si="1"/>
+        <v>1.5049999999999999</v>
+      </c>
+      <c r="AC20" s="1">
         <f t="shared" si="2"/>
-        <v>1.5049999999999999</v>
-      </c>
-      <c r="AC20" s="1">
-        <f t="shared" si="3"/>
         <v>3.1150000000000002</v>
       </c>
       <c r="AD20">
@@ -8032,19 +8021,19 @@
       <c r="AM20" s="2">
         <v>1</v>
       </c>
-      <c r="AN20" s="17">
+      <c r="AN20" s="15">
+        <f t="shared" si="29"/>
+        <v>0.504</v>
+      </c>
+      <c r="AO20">
         <f t="shared" si="30"/>
-        <v>0.504</v>
-      </c>
-      <c r="AO20">
-        <f t="shared" si="31"/>
         <v>2.6334</v>
       </c>
       <c r="AP20">
         <v>0</v>
       </c>
       <c r="AS20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.1571428571428573</v>
       </c>
       <c r="AT20">
@@ -8111,7 +8100,7 @@
         <v>59</v>
       </c>
       <c r="B21" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.63</v>
       </c>
       <c r="C21">
@@ -8120,19 +8109,19 @@
       <c r="D21" s="2">
         <v>0.65</v>
       </c>
-      <c r="E21" s="17">
-        <f t="shared" si="24"/>
-        <v>0.95200000000000007</v>
-      </c>
-      <c r="F21" s="17">
+      <c r="E21" s="15">
+        <f t="shared" si="32"/>
+        <v>0.82979999999999998</v>
+      </c>
+      <c r="F21" s="15">
         <f t="shared" si="25"/>
-        <v>1.552</v>
+        <v>1.4298</v>
       </c>
       <c r="G21" s="1">
         <f t="shared" si="0"/>
-        <v>0.95200000000000007</v>
-      </c>
-      <c r="H21" s="17">
+        <v>0.82979999999999998</v>
+      </c>
+      <c r="H21" s="15">
         <f t="shared" si="26"/>
         <v>3</v>
       </c>
@@ -8148,30 +8137,29 @@
       <c r="L21" s="2">
         <v>1</v>
       </c>
-      <c r="M21" s="17">
-        <f t="shared" si="27"/>
-        <v>1.3520000000000003</v>
+      <c r="M21" s="1">
+        <f t="shared" si="5"/>
+        <v>1.383</v>
       </c>
       <c r="N21" s="1">
         <f t="shared" si="6"/>
-        <v>0.95200000000000007</v>
-      </c>
-      <c r="O21" s="17">
-        <f t="shared" si="28"/>
-        <v>1.7520000000000002</v>
+        <v>0.82979999999999998</v>
+      </c>
+      <c r="O21" s="15">
+        <f t="shared" si="27"/>
+        <v>1.6297999999999999</v>
       </c>
       <c r="P21">
         <v>7</v>
       </c>
-      <c r="Q21" s="1">
-        <f t="shared" si="1"/>
-        <v>1.3520000000000003</v>
-      </c>
-      <c r="R21" s="17">
-        <v>1.5</v>
-      </c>
-      <c r="S21" s="20">
-        <v>1.5</v>
+      <c r="Q21">
+        <v>1.383</v>
+      </c>
+      <c r="R21" s="15">
+        <v>1.37</v>
+      </c>
+      <c r="S21" s="17">
+        <v>0.40899999999999997</v>
       </c>
       <c r="T21" s="1">
         <f t="shared" si="7"/>
@@ -8189,23 +8177,23 @@
       <c r="X21" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y21" s="15">
+      <c r="Y21" s="14">
         <f>8+3/8</f>
         <v>8.375</v>
       </c>
       <c r="Z21" s="2">
         <v>1.25</v>
       </c>
-      <c r="AA21" s="17">
+      <c r="AA21" s="15">
         <f>AF21*0.322</f>
         <v>1.3685</v>
       </c>
       <c r="AB21" s="1">
+        <f t="shared" si="1"/>
+        <v>1.3685</v>
+      </c>
+      <c r="AC21" s="1">
         <f t="shared" si="2"/>
-        <v>1.3685</v>
-      </c>
-      <c r="AC21" s="1">
-        <f t="shared" si="3"/>
         <v>2.99</v>
       </c>
       <c r="AD21">
@@ -8240,19 +8228,19 @@
       <c r="AM21" s="2">
         <v>1</v>
       </c>
-      <c r="AN21" s="17">
+      <c r="AN21" s="15">
+        <f t="shared" si="29"/>
+        <v>0.504</v>
+      </c>
+      <c r="AO21">
         <f t="shared" si="30"/>
-        <v>0.504</v>
-      </c>
-      <c r="AO21">
-        <f t="shared" si="31"/>
         <v>2.6334</v>
       </c>
       <c r="AP21">
         <v>0</v>
       </c>
       <c r="AS21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.1323529411764706</v>
       </c>
       <c r="AT21">
@@ -8291,7 +8279,7 @@
         <v>3.68</v>
       </c>
       <c r="BD21">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>14.8</v>
       </c>
       <c r="BE21">
@@ -8320,7 +8308,7 @@
         <v>60</v>
       </c>
       <c r="B22" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.63</v>
       </c>
       <c r="C22" s="7">
@@ -8329,91 +8317,90 @@
       <c r="D22" s="9">
         <v>0.65</v>
       </c>
-      <c r="E22" s="17">
-        <f t="shared" si="24"/>
-        <v>0.93100000000000005</v>
-      </c>
-      <c r="F22" s="17">
+      <c r="E22" s="18">
+        <f t="shared" si="32"/>
+        <v>0.82799999999999996</v>
+      </c>
+      <c r="F22" s="18">
         <f t="shared" si="25"/>
-        <v>1.5310000000000001</v>
-      </c>
-      <c r="G22" s="1">
+        <v>1.4279999999999999</v>
+      </c>
+      <c r="G22" s="8">
         <f t="shared" si="0"/>
-        <v>0.93100000000000005</v>
-      </c>
-      <c r="H22" s="17">
+        <v>0.82799999999999996</v>
+      </c>
+      <c r="H22" s="18">
         <f t="shared" si="26"/>
         <v>8.875</v>
       </c>
-      <c r="I22" s="2">
+      <c r="I22" s="9">
         <v>3.1</v>
       </c>
-      <c r="J22" s="2">
+      <c r="J22" s="9">
         <v>5</v>
       </c>
-      <c r="K22" s="2">
+      <c r="K22" s="9">
         <v>0.3</v>
       </c>
-      <c r="L22" s="2">
-        <v>1</v>
-      </c>
-      <c r="M22" s="17">
+      <c r="L22" s="9">
+        <v>1</v>
+      </c>
+      <c r="M22" s="8">
+        <f t="shared" si="5"/>
+        <v>1.38</v>
+      </c>
+      <c r="N22" s="8">
+        <f t="shared" si="6"/>
+        <v>0.82799999999999996</v>
+      </c>
+      <c r="O22" s="18">
         <f t="shared" si="27"/>
-        <v>1.331</v>
-      </c>
-      <c r="N22" s="1">
-        <f t="shared" si="6"/>
-        <v>0.93100000000000005</v>
-      </c>
-      <c r="O22" s="17">
-        <f t="shared" si="28"/>
-        <v>1.7310000000000001</v>
+        <v>1.6280000000000001</v>
       </c>
       <c r="P22" s="7">
         <v>18.75</v>
       </c>
-      <c r="Q22" s="1">
-        <f t="shared" si="1"/>
-        <v>1.331</v>
-      </c>
-      <c r="R22" s="17">
+      <c r="Q22" s="7">
+        <v>1.38</v>
+      </c>
+      <c r="R22" s="18">
         <v>1.5</v>
       </c>
-      <c r="S22" s="20">
+      <c r="S22" s="19">
         <v>1.5</v>
       </c>
       <c r="T22" s="8">
         <f t="shared" si="7"/>
         <v>0.63</v>
       </c>
-      <c r="U22" s="2">
+      <c r="U22" s="9">
         <v>0.44</v>
       </c>
-      <c r="V22" s="2">
+      <c r="V22" s="9">
         <v>2.16</v>
       </c>
-      <c r="W22" s="2">
+      <c r="W22" s="9">
         <v>0.85</v>
       </c>
-      <c r="X22" s="2">
+      <c r="X22" s="9">
         <v>3.66</v>
       </c>
-      <c r="Y22" s="17">
+      <c r="Y22" s="18">
         <v>1.25</v>
       </c>
       <c r="Z22" s="9">
         <v>1.25</v>
       </c>
-      <c r="AA22" s="17">
+      <c r="AA22" s="18">
         <f t="shared" ref="AA22:AA24" si="34">AF22*0.322</f>
         <v>1.3383125</v>
       </c>
       <c r="AB22" s="8">
+        <f t="shared" si="1"/>
+        <v>1.3383125</v>
+      </c>
+      <c r="AC22" s="8">
         <f t="shared" si="2"/>
-        <v>1.3383125</v>
-      </c>
-      <c r="AC22" s="8">
-        <f t="shared" si="3"/>
         <v>2.8962500000000002</v>
       </c>
       <c r="AD22" s="12">
@@ -8449,21 +8436,19 @@
       <c r="AM22" s="9">
         <v>1</v>
       </c>
-      <c r="AN22" s="17">
+      <c r="AN22" s="18">
+        <f t="shared" si="29"/>
+        <v>0.504</v>
+      </c>
+      <c r="AO22" s="7">
         <f t="shared" si="30"/>
-        <v>0.504</v>
-      </c>
-      <c r="AO22">
-        <f t="shared" si="31"/>
         <v>2.6334</v>
       </c>
-      <c r="AP22">
+      <c r="AP22" s="7">
         <v>0</v>
       </c>
-      <c r="AQ22"/>
-      <c r="AR22"/>
       <c r="AS22" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.1278195488721805</v>
       </c>
       <c r="AT22" s="7">
@@ -8473,7 +8458,7 @@
         <f t="shared" si="21"/>
         <v>32.04</v>
       </c>
-      <c r="AV22" s="13">
+      <c r="AV22" s="12">
         <f t="shared" si="22"/>
         <v>32.950000000000003</v>
       </c>
@@ -8481,46 +8466,46 @@
         <f t="shared" si="23"/>
         <v>0.91000000000000369</v>
       </c>
-      <c r="AY22">
+      <c r="AY22" s="7">
         <f t="shared" si="11"/>
         <v>2.8962500000000002</v>
       </c>
-      <c r="AZ22">
+      <c r="AZ22" s="7">
         <f t="shared" si="12"/>
         <v>3.4275000000000002</v>
       </c>
-      <c r="BA22">
+      <c r="BA22" s="7">
         <f t="shared" si="13"/>
         <v>9.9268968750000006</v>
       </c>
-      <c r="BB22">
+      <c r="BB22" s="7">
         <f t="shared" si="14"/>
         <v>3.53</v>
       </c>
-      <c r="BC22">
+      <c r="BC22" s="7">
         <f t="shared" si="15"/>
         <v>3.56</v>
       </c>
-      <c r="BD22">
+      <c r="BD22" s="7">
         <v>15</v>
       </c>
-      <c r="BE22">
+      <c r="BE22" s="7">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BG22">
+      <c r="BG22" s="7">
         <f t="shared" si="17"/>
         <v>3.41</v>
       </c>
-      <c r="BH22">
+      <c r="BH22" s="7">
         <f t="shared" si="18"/>
         <v>54.75</v>
       </c>
-      <c r="BI22">
+      <c r="BI22" s="7">
         <f t="shared" si="19"/>
         <v>33.590000000000003</v>
       </c>
-      <c r="BJ22">
+      <c r="BJ22" s="7">
         <f t="shared" si="20"/>
         <v>51.34</v>
       </c>
@@ -8530,7 +8515,7 @@
         <v>61</v>
       </c>
       <c r="B23" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.63</v>
       </c>
       <c r="C23">
@@ -8539,19 +8524,19 @@
       <c r="D23" s="2">
         <v>0.65</v>
       </c>
-      <c r="E23" s="17">
-        <f t="shared" si="24"/>
-        <v>0.91</v>
-      </c>
-      <c r="F23" s="17">
+      <c r="E23" s="15">
+        <f t="shared" si="32"/>
+        <v>0.82619999999999993</v>
+      </c>
+      <c r="F23" s="15">
         <f t="shared" si="25"/>
-        <v>1.51</v>
+        <v>1.4261999999999999</v>
       </c>
       <c r="G23" s="1">
         <f t="shared" si="0"/>
-        <v>0.91</v>
-      </c>
-      <c r="H23" s="17">
+        <v>0.82619999999999993</v>
+      </c>
+      <c r="H23" s="15">
         <f t="shared" si="26"/>
         <v>3</v>
       </c>
@@ -8567,30 +8552,29 @@
       <c r="L23" s="2">
         <v>1</v>
       </c>
-      <c r="M23" s="17">
-        <f t="shared" si="27"/>
-        <v>1.31</v>
+      <c r="M23" s="1">
+        <f t="shared" si="5"/>
+        <v>1.377</v>
       </c>
       <c r="N23" s="1">
         <f t="shared" si="6"/>
-        <v>0.91</v>
-      </c>
-      <c r="O23" s="17">
-        <f t="shared" si="28"/>
-        <v>1.71</v>
+        <v>0.82619999999999993</v>
+      </c>
+      <c r="O23" s="15">
+        <f t="shared" si="27"/>
+        <v>1.6261999999999999</v>
       </c>
       <c r="P23">
         <v>7</v>
       </c>
-      <c r="Q23" s="1">
-        <f t="shared" si="1"/>
-        <v>1.31</v>
-      </c>
-      <c r="R23" s="17">
-        <v>1.5</v>
-      </c>
-      <c r="S23" s="20">
-        <v>1.5</v>
+      <c r="Q23">
+        <v>1.377</v>
+      </c>
+      <c r="R23" s="15">
+        <v>1.274</v>
+      </c>
+      <c r="S23" s="17">
+        <v>1.274</v>
       </c>
       <c r="T23" s="1">
         <f t="shared" si="7"/>
@@ -8608,22 +8592,22 @@
       <c r="X23" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y23" s="15">
+      <c r="Y23" s="14">
         <v>5.75</v>
       </c>
       <c r="Z23" s="2">
         <v>1.25</v>
       </c>
-      <c r="AA23" s="17">
+      <c r="AA23" s="15">
         <f t="shared" si="34"/>
         <v>1.308125</v>
       </c>
       <c r="AB23" s="1">
+        <f t="shared" si="1"/>
+        <v>1.308125</v>
+      </c>
+      <c r="AC23" s="1">
         <f t="shared" si="2"/>
-        <v>1.308125</v>
-      </c>
-      <c r="AC23" s="1">
-        <f t="shared" si="3"/>
         <v>2.8025000000000002</v>
       </c>
       <c r="AD23">
@@ -8658,19 +8642,19 @@
       <c r="AM23" s="2">
         <v>1</v>
       </c>
-      <c r="AN23" s="17">
+      <c r="AN23" s="15">
+        <f t="shared" si="29"/>
+        <v>0.504</v>
+      </c>
+      <c r="AO23">
         <f t="shared" si="30"/>
-        <v>0.504</v>
-      </c>
-      <c r="AO23">
-        <f t="shared" si="31"/>
         <v>2.6334</v>
       </c>
       <c r="AP23">
         <v>0</v>
       </c>
       <c r="AS23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.1230769230769231</v>
       </c>
       <c r="AT23">
@@ -8737,7 +8721,7 @@
         <v>62</v>
       </c>
       <c r="B24" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.63</v>
       </c>
       <c r="C24">
@@ -8746,19 +8730,19 @@
       <c r="D24" s="2">
         <v>0.65</v>
       </c>
-      <c r="E24" s="17">
-        <f t="shared" si="24"/>
-        <v>0.89600000000000002</v>
-      </c>
-      <c r="F24" s="17">
+      <c r="E24" s="15">
+        <f t="shared" si="32"/>
+        <v>0.82619999999999993</v>
+      </c>
+      <c r="F24" s="15">
         <f t="shared" si="25"/>
-        <v>1.496</v>
+        <v>1.4261999999999999</v>
       </c>
       <c r="G24" s="1">
         <f t="shared" si="0"/>
-        <v>0.89600000000000002</v>
-      </c>
-      <c r="H24" s="17">
+        <v>0.82619999999999993</v>
+      </c>
+      <c r="H24" s="15">
         <f t="shared" si="26"/>
         <v>8.875</v>
       </c>
@@ -8774,30 +8758,29 @@
       <c r="L24" s="2">
         <v>1</v>
       </c>
-      <c r="M24" s="17">
-        <f t="shared" si="27"/>
-        <v>1.2960000000000003</v>
+      <c r="M24" s="1">
+        <f t="shared" si="5"/>
+        <v>1.377</v>
       </c>
       <c r="N24" s="1">
         <f t="shared" si="6"/>
-        <v>0.89600000000000002</v>
-      </c>
-      <c r="O24" s="17">
-        <f t="shared" si="28"/>
-        <v>1.6960000000000002</v>
+        <v>0.82619999999999993</v>
+      </c>
+      <c r="O24" s="15">
+        <f t="shared" si="27"/>
+        <v>1.6261999999999999</v>
       </c>
       <c r="P24">
         <v>18.75</v>
       </c>
-      <c r="Q24" s="1">
-        <f t="shared" si="1"/>
-        <v>1.2960000000000003</v>
-      </c>
-      <c r="R24" s="17">
-        <v>1.5</v>
-      </c>
-      <c r="S24" s="20">
-        <v>1.5</v>
+      <c r="Q24">
+        <v>1.377</v>
+      </c>
+      <c r="R24" s="15">
+        <v>1.823</v>
+      </c>
+      <c r="S24" s="17">
+        <v>0.71399999999999997</v>
       </c>
       <c r="T24" s="1">
         <f t="shared" si="7"/>
@@ -8815,22 +8798,22 @@
       <c r="X24" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y24" s="14">
+      <c r="Y24" s="13">
         <v>0.75</v>
       </c>
       <c r="Z24" s="2">
         <v>1</v>
       </c>
-      <c r="AA24" s="17">
+      <c r="AA24" s="15">
         <f t="shared" si="34"/>
         <v>1.288</v>
       </c>
       <c r="AB24" s="1">
+        <f t="shared" si="1"/>
+        <v>1.288</v>
+      </c>
+      <c r="AC24" s="1">
         <f t="shared" si="2"/>
-        <v>1.288</v>
-      </c>
-      <c r="AC24" s="1">
-        <f t="shared" si="3"/>
         <v>2.74</v>
       </c>
       <c r="AD24">
@@ -8866,19 +8849,19 @@
       <c r="AM24" s="2">
         <v>1</v>
       </c>
-      <c r="AN24" s="17">
+      <c r="AN24" s="15">
+        <f t="shared" si="29"/>
+        <v>0.504</v>
+      </c>
+      <c r="AO24">
         <f t="shared" si="30"/>
-        <v>0.504</v>
-      </c>
-      <c r="AO24">
-        <f t="shared" si="31"/>
         <v>2.6334</v>
       </c>
       <c r="AP24">
         <v>0</v>
       </c>
       <c r="AS24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.09375</v>
       </c>
       <c r="AT24">
@@ -8917,7 +8900,7 @@
         <v>3.3</v>
       </c>
       <c r="BD24">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>15.2</v>
       </c>
       <c r="BE24">
@@ -8946,7 +8929,7 @@
         <v>63</v>
       </c>
       <c r="B25" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.56999999999999995</v>
       </c>
       <c r="C25">
@@ -8981,7 +8964,8 @@
       <c r="L25" s="2">
         <v>1</v>
       </c>
-      <c r="M25" s="19">
+      <c r="M25" s="1">
+        <f t="shared" si="5"/>
         <v>1.26</v>
       </c>
       <c r="N25" s="1">
@@ -8994,8 +8978,7 @@
       <c r="P25">
         <v>7</v>
       </c>
-      <c r="Q25" s="1">
-        <f t="shared" si="1"/>
+      <c r="Q25">
         <v>1.26</v>
       </c>
       <c r="R25">
@@ -9020,7 +9003,7 @@
       <c r="X25" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y25" s="15">
+      <c r="Y25" s="14">
         <v>4.43</v>
       </c>
       <c r="Z25" s="2">
@@ -9030,11 +9013,11 @@
         <v>1.22</v>
       </c>
       <c r="AB25" s="1">
+        <f t="shared" si="1"/>
+        <v>1.22</v>
+      </c>
+      <c r="AC25" s="1">
         <f t="shared" si="2"/>
-        <v>1.22</v>
-      </c>
-      <c r="AC25" s="1">
-        <f t="shared" si="3"/>
         <v>2.6399999999999997</v>
       </c>
       <c r="AD25">
@@ -9077,7 +9060,7 @@
         <v>0</v>
       </c>
       <c r="AS25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.1031746031746033</v>
       </c>
       <c r="AT25">
@@ -9144,7 +9127,7 @@
         <v>64</v>
       </c>
       <c r="B26" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.56999999999999995</v>
       </c>
       <c r="C26" s="3">
@@ -9153,19 +9136,19 @@
       <c r="D26" s="4">
         <v>0.65</v>
       </c>
-      <c r="E26" s="17">
-        <f t="shared" si="24"/>
-        <v>0.79800000000000004</v>
-      </c>
-      <c r="F26" s="3">
+      <c r="E26" s="15">
+        <f>Q26*0.6</f>
+        <v>0.75839999999999996</v>
+      </c>
+      <c r="F26" s="16">
         <f>E26+0.6</f>
-        <v>1.3980000000000001</v>
+        <v>1.3584000000000001</v>
       </c>
       <c r="G26" s="1">
         <f t="shared" si="0"/>
-        <v>0.79800000000000004</v>
-      </c>
-      <c r="H26" s="17">
+        <v>0.75839999999999996</v>
+      </c>
+      <c r="H26" s="15">
         <f t="shared" si="26"/>
         <v>8.875</v>
       </c>
@@ -9181,30 +9164,29 @@
       <c r="L26" s="2">
         <v>1</v>
       </c>
-      <c r="M26" s="18">
-        <f>O26-0.4</f>
-        <v>1.0979999999999999</v>
+      <c r="M26" s="1">
+        <f t="shared" si="5"/>
+        <v>1.264</v>
       </c>
       <c r="N26" s="1">
         <f t="shared" si="6"/>
-        <v>0.79800000000000004</v>
-      </c>
-      <c r="O26" s="18">
+        <v>0.75839999999999996</v>
+      </c>
+      <c r="O26" s="16">
         <f>E26+0.7</f>
-        <v>1.498</v>
+        <v>1.4583999999999999</v>
       </c>
       <c r="P26" s="3">
         <v>18.75</v>
       </c>
-      <c r="Q26" s="1">
-        <f t="shared" si="1"/>
-        <v>1.0979999999999999</v>
-      </c>
-      <c r="R26" s="18">
-        <v>1.3</v>
-      </c>
-      <c r="S26" s="18">
-        <v>1.3</v>
+      <c r="Q26">
+        <v>1.264</v>
+      </c>
+      <c r="R26" s="16">
+        <v>1.48</v>
+      </c>
+      <c r="S26" s="16">
+        <v>0.92800000000000005</v>
       </c>
       <c r="T26" s="6">
         <f t="shared" si="7"/>
@@ -9222,23 +9204,23 @@
       <c r="X26" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y26" s="14">
+      <c r="Y26" s="13">
         <f>5/8</f>
         <v>0.625</v>
       </c>
       <c r="Z26" s="4">
         <v>1</v>
       </c>
-      <c r="AA26" s="18">
+      <c r="AA26" s="16">
         <f>AF26*0.311</f>
         <v>1.1079375</v>
       </c>
       <c r="AB26" s="6">
+        <f t="shared" si="1"/>
+        <v>1.1079375</v>
+      </c>
+      <c r="AC26" s="6">
         <f t="shared" si="2"/>
-        <v>1.1079375</v>
-      </c>
-      <c r="AC26" s="6">
-        <f t="shared" si="3"/>
         <v>2.4225000000000003</v>
       </c>
       <c r="AD26" s="3">
@@ -9273,7 +9255,7 @@
       <c r="AM26" s="4">
         <v>1</v>
       </c>
-      <c r="AN26" s="18">
+      <c r="AN26" s="16">
         <f>AG26*0.8</f>
         <v>0.45599999999999996</v>
       </c>
@@ -9287,7 +9269,7 @@
       <c r="AQ26"/>
       <c r="AR26"/>
       <c r="AS26" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.1228070175438596</v>
       </c>
       <c r="AT26">
@@ -9354,7 +9336,7 @@
         <v>65</v>
       </c>
       <c r="B27" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="C27" s="7">
@@ -9363,96 +9345,95 @@
       <c r="D27" s="9">
         <v>0.65</v>
       </c>
-      <c r="E27" s="17">
-        <f t="shared" si="24"/>
-        <v>0.77700000000000002</v>
-      </c>
-      <c r="F27" s="3">
-        <f t="shared" ref="F27:F34" si="35">E27+0.6</f>
-        <v>1.377</v>
-      </c>
-      <c r="G27" s="1">
+      <c r="E27" s="18">
+        <f t="shared" ref="E27:E34" si="35">Q27*0.6</f>
+        <v>0.75600000000000001</v>
+      </c>
+      <c r="F27" s="20">
+        <f t="shared" ref="F27:F34" si="36">E27+0.6</f>
+        <v>1.3559999999999999</v>
+      </c>
+      <c r="G27" s="8">
         <f t="shared" si="0"/>
-        <v>0.77700000000000002</v>
-      </c>
-      <c r="H27" s="17">
+        <v>0.75600000000000001</v>
+      </c>
+      <c r="H27" s="18">
         <f t="shared" si="26"/>
         <v>3</v>
       </c>
-      <c r="I27" s="2">
+      <c r="I27" s="9">
         <v>3.1</v>
       </c>
-      <c r="J27" s="2">
+      <c r="J27" s="9">
         <v>5</v>
       </c>
-      <c r="K27" s="2">
+      <c r="K27" s="9">
         <v>0.3</v>
       </c>
-      <c r="L27" s="2">
-        <v>1</v>
-      </c>
-      <c r="M27" s="18">
-        <f t="shared" ref="M27:M34" si="36">O27-0.4</f>
-        <v>1.077</v>
-      </c>
-      <c r="N27" s="1">
+      <c r="L27" s="9">
+        <v>1</v>
+      </c>
+      <c r="M27" s="8">
+        <f t="shared" si="5"/>
+        <v>1.26</v>
+      </c>
+      <c r="N27" s="8">
         <f t="shared" si="6"/>
-        <v>0.77700000000000002</v>
-      </c>
-      <c r="O27" s="18">
+        <v>0.75600000000000001</v>
+      </c>
+      <c r="O27" s="21">
         <f t="shared" ref="O27:O34" si="37">E27+0.7</f>
-        <v>1.4769999999999999</v>
+        <v>1.456</v>
       </c>
       <c r="P27" s="7">
         <v>7</v>
       </c>
-      <c r="Q27" s="1">
-        <f t="shared" si="1"/>
-        <v>1.077</v>
-      </c>
-      <c r="R27" s="18">
+      <c r="Q27" s="7">
+        <v>1.26</v>
+      </c>
+      <c r="R27" s="21">
         <v>1.3</v>
       </c>
-      <c r="S27" s="18">
+      <c r="S27" s="21">
         <v>1.3</v>
       </c>
       <c r="T27" s="10">
         <f t="shared" si="7"/>
         <v>0.5</v>
       </c>
-      <c r="U27" s="2">
+      <c r="U27" s="9">
         <v>0.44</v>
       </c>
-      <c r="V27" s="2">
+      <c r="V27" s="9">
         <v>2.16</v>
       </c>
-      <c r="W27" s="2">
+      <c r="W27" s="9">
         <v>0.85</v>
       </c>
-      <c r="X27" s="2">
+      <c r="X27" s="9">
         <v>3.66</v>
       </c>
-      <c r="Y27" s="17">
+      <c r="Y27" s="18">
         <v>3</v>
       </c>
       <c r="Z27" s="9">
         <v>1</v>
       </c>
-      <c r="AA27" s="18">
+      <c r="AA27" s="21">
         <f t="shared" ref="AA27:AA34" si="38">AF27*0.311</f>
         <v>1.07878125</v>
       </c>
       <c r="AB27" s="10">
+        <f t="shared" si="1"/>
+        <v>1.07878125</v>
+      </c>
+      <c r="AC27" s="10">
         <f t="shared" si="2"/>
-        <v>1.07878125</v>
-      </c>
-      <c r="AC27" s="10">
-        <f t="shared" si="3"/>
         <v>2.46875</v>
       </c>
       <c r="AD27" s="12">
         <f>AD28+(AD26-AD28)/2</f>
-        <v>3.875</v>
+        <v>3.95</v>
       </c>
       <c r="AE27" s="12">
         <f>AE28+(AE26-AE28)/2</f>
@@ -9483,22 +9464,20 @@
       <c r="AM27" s="9">
         <v>1</v>
       </c>
-      <c r="AN27" s="18">
+      <c r="AN27" s="21">
         <f t="shared" ref="AN27:AN34" si="39">AG27*0.8</f>
         <v>0.4</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AO27" s="20">
         <f t="shared" ref="AO27:AO34" si="40">AG27*4.18</f>
         <v>2.09</v>
       </c>
-      <c r="AP27">
+      <c r="AP27" s="7">
         <v>0</v>
       </c>
-      <c r="AQ27"/>
-      <c r="AR27"/>
       <c r="AS27" s="7">
-        <f t="shared" si="4"/>
-        <v>1.117117117117117</v>
+        <f t="shared" si="3"/>
+        <v>1.1387387387387389</v>
       </c>
       <c r="AT27" s="7">
         <v>24</v>
@@ -9507,7 +9486,7 @@
         <f t="shared" si="21"/>
         <v>24</v>
       </c>
-      <c r="AV27" s="13">
+      <c r="AV27" s="12">
         <f t="shared" si="22"/>
         <v>24.612500000000001</v>
       </c>
@@ -9515,46 +9494,46 @@
         <f t="shared" si="23"/>
         <v>0.61250000000000071</v>
       </c>
-      <c r="AY27">
+      <c r="AY27" s="7">
         <f t="shared" si="11"/>
         <v>2.46875</v>
       </c>
-      <c r="AZ27">
+      <c r="AZ27" s="7">
         <f t="shared" si="12"/>
-        <v>2.875</v>
-      </c>
-      <c r="BA27">
+        <v>2.95</v>
+      </c>
+      <c r="BA27" s="7">
         <f t="shared" si="13"/>
-        <v>7.09765625</v>
-      </c>
-      <c r="BB27">
+        <v>7.2828125000000004</v>
+      </c>
+      <c r="BB27" s="7">
         <f t="shared" si="14"/>
         <v>3.01</v>
       </c>
-      <c r="BC27">
+      <c r="BC27" s="7">
         <f t="shared" si="15"/>
-        <v>3.01</v>
-      </c>
-      <c r="BD27">
+        <v>3.05</v>
+      </c>
+      <c r="BD27" s="7">
         <v>16</v>
       </c>
-      <c r="BE27">
+      <c r="BE27" s="7">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BG27">
+      <c r="BG27" s="7">
         <f t="shared" si="17"/>
         <v>5.16</v>
       </c>
-      <c r="BH27">
+      <c r="BH27" s="7">
         <f t="shared" si="18"/>
         <v>34.0625</v>
       </c>
-      <c r="BI27">
+      <c r="BI27" s="7">
         <f t="shared" si="19"/>
         <v>22.9025</v>
       </c>
-      <c r="BJ27">
+      <c r="BJ27" s="7">
         <f t="shared" si="20"/>
         <v>28.9025</v>
       </c>
@@ -9564,7 +9543,7 @@
         <v>66</v>
       </c>
       <c r="B28" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.49</v>
       </c>
       <c r="C28">
@@ -9573,19 +9552,19 @@
       <c r="D28" s="2">
         <v>0.65</v>
       </c>
-      <c r="E28" s="17">
-        <f t="shared" si="24"/>
-        <v>0.75600000000000001</v>
-      </c>
-      <c r="F28" s="3">
+      <c r="E28" s="15">
         <f t="shared" si="35"/>
-        <v>1.3559999999999999</v>
+        <v>0.75480000000000003</v>
+      </c>
+      <c r="F28" s="16">
+        <f t="shared" si="36"/>
+        <v>1.3548</v>
       </c>
       <c r="G28" s="1">
         <f t="shared" si="0"/>
-        <v>0.75600000000000001</v>
-      </c>
-      <c r="H28" s="17">
+        <v>0.75480000000000003</v>
+      </c>
+      <c r="H28" s="15">
         <f t="shared" si="26"/>
         <v>8.875</v>
       </c>
@@ -9601,30 +9580,29 @@
       <c r="L28" s="2">
         <v>1</v>
       </c>
-      <c r="M28" s="18">
-        <f t="shared" si="36"/>
-        <v>1.056</v>
+      <c r="M28" s="1">
+        <f t="shared" si="5"/>
+        <v>1.258</v>
       </c>
       <c r="N28" s="1">
         <f t="shared" si="6"/>
-        <v>0.75600000000000001</v>
-      </c>
-      <c r="O28" s="18">
+        <v>0.75480000000000003</v>
+      </c>
+      <c r="O28" s="16">
         <f t="shared" si="37"/>
-        <v>1.456</v>
-      </c>
-      <c r="P28" s="16">
+        <v>1.4548000000000001</v>
+      </c>
+      <c r="P28">
         <v>18.75</v>
       </c>
-      <c r="Q28" s="1">
-        <f t="shared" si="1"/>
-        <v>1.056</v>
-      </c>
-      <c r="R28" s="18">
-        <v>1.3</v>
-      </c>
-      <c r="S28" s="18">
-        <v>1.3</v>
+      <c r="Q28">
+        <v>1.258</v>
+      </c>
+      <c r="R28" s="16">
+        <v>1.3140000000000001</v>
+      </c>
+      <c r="S28" s="16">
+        <v>1.0549999999999999</v>
       </c>
       <c r="T28" s="1">
         <f t="shared" si="7"/>
@@ -9642,27 +9620,27 @@
       <c r="X28" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y28" s="14">
+      <c r="Y28" s="13">
         <f>3/8</f>
         <v>0.375</v>
       </c>
       <c r="Z28" s="2">
         <v>1</v>
       </c>
-      <c r="AA28" s="18">
+      <c r="AA28" s="16">
         <f t="shared" si="38"/>
         <v>1.049625</v>
       </c>
       <c r="AB28" s="1">
+        <f t="shared" si="1"/>
+        <v>1.049625</v>
+      </c>
+      <c r="AC28" s="1">
         <f t="shared" si="2"/>
-        <v>1.049625</v>
-      </c>
-      <c r="AC28" s="1">
-        <f t="shared" si="3"/>
         <v>2.395</v>
       </c>
       <c r="AD28">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AE28">
         <v>26.5</v>
@@ -9692,7 +9670,7 @@
       <c r="AM28" s="2">
         <v>1</v>
       </c>
-      <c r="AN28" s="18">
+      <c r="AN28" s="16">
         <f t="shared" si="39"/>
         <v>0.39200000000000002</v>
       </c>
@@ -9704,8 +9682,8 @@
         <v>0</v>
       </c>
       <c r="AS28">
-        <f t="shared" si="4"/>
-        <v>1.1111111111111112</v>
+        <f t="shared" si="3"/>
+        <v>1.1555555555555554</v>
       </c>
       <c r="AT28">
         <v>25</v>
@@ -9728,11 +9706,11 @@
       </c>
       <c r="AZ28">
         <f t="shared" si="12"/>
-        <v>2.77</v>
+        <v>2.92</v>
       </c>
       <c r="BA28">
         <f t="shared" si="13"/>
-        <v>6.63415</v>
+        <v>6.9934000000000003</v>
       </c>
       <c r="BB28">
         <f t="shared" si="14"/>
@@ -9740,15 +9718,15 @@
       </c>
       <c r="BC28">
         <f t="shared" si="15"/>
-        <v>2.91</v>
+        <v>2.98</v>
       </c>
       <c r="BD28">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>16</v>
       </c>
       <c r="BE28">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="BG28">
         <f t="shared" si="17"/>
@@ -9772,7 +9750,7 @@
         <v>67</v>
       </c>
       <c r="B29" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.49</v>
       </c>
       <c r="C29" s="7">
@@ -9781,91 +9759,90 @@
       <c r="D29" s="9">
         <v>0.65</v>
       </c>
-      <c r="E29" s="17">
-        <f t="shared" si="24"/>
-        <v>0.73919999999999997</v>
-      </c>
-      <c r="F29" s="3">
+      <c r="E29" s="18">
         <f t="shared" si="35"/>
-        <v>1.3391999999999999</v>
-      </c>
-      <c r="G29" s="1">
+        <v>0.75600000000000001</v>
+      </c>
+      <c r="F29" s="20">
+        <f t="shared" si="36"/>
+        <v>1.3559999999999999</v>
+      </c>
+      <c r="G29" s="8">
         <f t="shared" si="0"/>
-        <v>0.73919999999999997</v>
-      </c>
-      <c r="H29" s="17">
+        <v>0.75600000000000001</v>
+      </c>
+      <c r="H29" s="18">
         <f t="shared" si="26"/>
         <v>3</v>
       </c>
-      <c r="I29" s="2">
+      <c r="I29" s="9">
         <v>3.1</v>
       </c>
-      <c r="J29" s="2">
+      <c r="J29" s="9">
         <v>5</v>
       </c>
-      <c r="K29" s="2">
+      <c r="K29" s="9">
         <v>0.3</v>
       </c>
-      <c r="L29" s="2">
-        <v>1</v>
-      </c>
-      <c r="M29" s="18">
-        <f t="shared" si="36"/>
-        <v>1.0392000000000001</v>
-      </c>
-      <c r="N29" s="1">
+      <c r="L29" s="9">
+        <v>1</v>
+      </c>
+      <c r="M29" s="8">
+        <f t="shared" si="5"/>
+        <v>1.26</v>
+      </c>
+      <c r="N29" s="8">
         <f t="shared" si="6"/>
-        <v>0.73919999999999997</v>
-      </c>
-      <c r="O29" s="18">
+        <v>0.75600000000000001</v>
+      </c>
+      <c r="O29" s="21">
         <f t="shared" si="37"/>
-        <v>1.4392</v>
+        <v>1.456</v>
       </c>
       <c r="P29" s="7">
         <v>7</v>
       </c>
-      <c r="Q29" s="1">
-        <f t="shared" si="1"/>
-        <v>1.0392000000000001</v>
-      </c>
-      <c r="R29" s="18">
+      <c r="Q29" s="7">
+        <v>1.26</v>
+      </c>
+      <c r="R29" s="21">
         <v>1.3</v>
       </c>
-      <c r="S29" s="18">
+      <c r="S29" s="21">
         <v>1.3</v>
       </c>
       <c r="T29" s="8">
         <f t="shared" si="7"/>
         <v>0.49</v>
       </c>
-      <c r="U29" s="2">
+      <c r="U29" s="9">
         <v>0.44</v>
       </c>
-      <c r="V29" s="2">
+      <c r="V29" s="9">
         <v>2.16</v>
       </c>
-      <c r="W29" s="2">
+      <c r="W29" s="9">
         <v>0.85</v>
       </c>
-      <c r="X29" s="2">
+      <c r="X29" s="9">
         <v>3.66</v>
       </c>
-      <c r="Y29" s="17">
+      <c r="Y29" s="18">
         <v>2.5</v>
       </c>
       <c r="Z29" s="9">
         <v>1</v>
       </c>
-      <c r="AA29" s="18">
+      <c r="AA29" s="21">
         <f t="shared" si="38"/>
         <v>1.0263</v>
       </c>
       <c r="AB29" s="8">
+        <f t="shared" si="1"/>
+        <v>1.0263</v>
+      </c>
+      <c r="AC29" s="8">
         <f t="shared" si="2"/>
-        <v>1.0263</v>
-      </c>
-      <c r="AC29" s="8">
-        <f t="shared" si="3"/>
         <v>2.3199999999999998</v>
       </c>
       <c r="AD29" s="12">
@@ -9899,21 +9876,19 @@
       <c r="AM29" s="9">
         <v>1</v>
       </c>
-      <c r="AN29" s="18">
+      <c r="AN29" s="21">
         <f t="shared" si="39"/>
         <v>0.39200000000000002</v>
       </c>
-      <c r="AO29" s="3">
+      <c r="AO29" s="20">
         <f t="shared" si="40"/>
         <v>2.0482</v>
       </c>
-      <c r="AP29">
+      <c r="AP29" s="7">
         <v>0</v>
       </c>
-      <c r="AQ29"/>
-      <c r="AR29"/>
       <c r="AS29" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.1363636363636365</v>
       </c>
       <c r="AT29" s="7">
@@ -9923,7 +9898,7 @@
         <f t="shared" si="21"/>
         <v>21.38</v>
       </c>
-      <c r="AV29" s="13">
+      <c r="AV29" s="12">
         <f t="shared" si="22"/>
         <v>21.8</v>
       </c>
@@ -9931,46 +9906,46 @@
         <f t="shared" si="23"/>
         <v>0.42000000000000171</v>
       </c>
-      <c r="AY29">
+      <c r="AY29" s="7">
         <f t="shared" si="11"/>
         <v>2.3199999999999998</v>
       </c>
-      <c r="AZ29">
+      <c r="AZ29" s="7">
         <f t="shared" si="12"/>
         <v>2.77</v>
       </c>
-      <c r="BA29">
+      <c r="BA29" s="7">
         <f t="shared" si="13"/>
         <v>6.4263999999999992</v>
       </c>
-      <c r="BB29">
+      <c r="BB29" s="7">
         <f t="shared" si="14"/>
         <v>2.85</v>
       </c>
-      <c r="BC29">
+      <c r="BC29" s="7">
         <f t="shared" si="15"/>
         <v>2.86</v>
       </c>
-      <c r="BD29">
+      <c r="BD29" s="7">
         <v>16.5</v>
       </c>
-      <c r="BE29">
+      <c r="BE29" s="7">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BG29">
+      <c r="BG29" s="7">
         <f t="shared" si="17"/>
         <v>4.66</v>
       </c>
-      <c r="BH29">
+      <c r="BH29" s="7">
         <f t="shared" si="18"/>
         <v>31.25</v>
       </c>
-      <c r="BI29">
+      <c r="BI29" s="7">
         <f t="shared" si="19"/>
         <v>20.59</v>
       </c>
-      <c r="BJ29">
+      <c r="BJ29" s="7">
         <f t="shared" si="20"/>
         <v>26.59</v>
       </c>
@@ -9980,7 +9955,7 @@
         <v>68</v>
       </c>
       <c r="B30" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.49</v>
       </c>
       <c r="C30">
@@ -9989,19 +9964,19 @@
       <c r="D30" s="2">
         <v>0.65</v>
       </c>
-      <c r="E30" s="17">
-        <f t="shared" si="24"/>
-        <v>0.70000000000000007</v>
-      </c>
-      <c r="F30" s="3">
+      <c r="E30" s="15">
         <f t="shared" si="35"/>
-        <v>1.3</v>
+        <v>0.75659999999999994</v>
+      </c>
+      <c r="F30" s="16">
+        <f t="shared" si="36"/>
+        <v>1.3565999999999998</v>
       </c>
       <c r="G30" s="1">
         <f t="shared" si="0"/>
-        <v>0.70000000000000007</v>
-      </c>
-      <c r="H30" s="17">
+        <v>0.75659999999999994</v>
+      </c>
+      <c r="H30" s="15">
         <f t="shared" si="26"/>
         <v>8.875</v>
       </c>
@@ -10017,30 +9992,29 @@
       <c r="L30" s="2">
         <v>1</v>
       </c>
-      <c r="M30" s="18">
-        <f t="shared" si="36"/>
-        <v>0.99999999999999989</v>
+      <c r="M30" s="1">
+        <f t="shared" si="5"/>
+        <v>1.2609999999999999</v>
       </c>
       <c r="N30" s="1">
         <f t="shared" si="6"/>
-        <v>0.70000000000000007</v>
-      </c>
-      <c r="O30" s="18">
+        <v>0.75659999999999994</v>
+      </c>
+      <c r="O30" s="16">
         <f t="shared" si="37"/>
-        <v>1.4</v>
-      </c>
-      <c r="P30" s="16">
+        <v>1.4565999999999999</v>
+      </c>
+      <c r="P30">
         <v>18.75</v>
       </c>
-      <c r="Q30" s="1">
-        <f t="shared" si="1"/>
-        <v>0.99999999999999989</v>
-      </c>
-      <c r="R30" s="18">
-        <v>1.3</v>
-      </c>
-      <c r="S30" s="18">
-        <v>1.3</v>
+      <c r="Q30">
+        <v>1.2609999999999999</v>
+      </c>
+      <c r="R30" s="16">
+        <v>1.131</v>
+      </c>
+      <c r="S30" s="16">
+        <v>1.5189999999999999</v>
       </c>
       <c r="T30" s="1">
         <f t="shared" si="7"/>
@@ -10058,27 +10032,27 @@
       <c r="X30" s="2">
         <v>3.66</v>
       </c>
-      <c r="Y30" s="14">
+      <c r="Y30" s="13">
         <f>1+1/8</f>
         <v>1.125</v>
       </c>
       <c r="Z30" s="2">
         <v>1</v>
       </c>
-      <c r="AA30" s="18">
+      <c r="AA30" s="16">
         <f t="shared" si="38"/>
         <v>0.97187500000000004</v>
       </c>
       <c r="AB30" s="1">
+        <f t="shared" si="1"/>
+        <v>0.97187500000000004</v>
+      </c>
+      <c r="AC30" s="1">
         <f t="shared" si="2"/>
-        <v>0.97187500000000004</v>
-      </c>
-      <c r="AC30" s="1">
-        <f t="shared" si="3"/>
         <v>2.145</v>
       </c>
       <c r="AD30">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AE30">
         <v>24</v>
@@ -10108,7 +10082,7 @@
       <c r="AM30" s="2">
         <v>1</v>
       </c>
-      <c r="AN30" s="18">
+      <c r="AN30" s="16">
         <f t="shared" si="39"/>
         <v>0.39200000000000002</v>
       </c>
@@ -10120,8 +10094,8 @@
         <v>0</v>
       </c>
       <c r="AS30">
-        <f t="shared" si="4"/>
-        <v>1.248</v>
+        <f t="shared" si="3"/>
+        <v>1.1840000000000002</v>
       </c>
       <c r="AT30">
         <v>27</v>
@@ -10144,11 +10118,11 @@
       </c>
       <c r="AZ30">
         <f t="shared" si="12"/>
-        <v>2.92</v>
+        <v>2.72</v>
       </c>
       <c r="BA30">
         <f t="shared" si="13"/>
-        <v>6.2633999999999999</v>
+        <v>5.8344000000000005</v>
       </c>
       <c r="BB30">
         <f t="shared" si="14"/>
@@ -10156,14 +10130,14 @@
       </c>
       <c r="BC30">
         <f t="shared" si="15"/>
-        <v>2.82</v>
+        <v>2.73</v>
       </c>
       <c r="BD30">
         <v>16.8</v>
       </c>
       <c r="BE30">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="BG30">
         <f t="shared" si="17"/>
@@ -10187,7 +10161,7 @@
         <v>69</v>
       </c>
       <c r="B31" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.49</v>
       </c>
       <c r="C31" s="7">
@@ -10196,95 +10170,94 @@
       <c r="D31" s="9">
         <v>0.65</v>
       </c>
-      <c r="E31" s="17">
-        <f t="shared" si="24"/>
-        <v>0.67200000000000004</v>
-      </c>
-      <c r="F31" s="3">
+      <c r="E31" s="18">
         <f t="shared" si="35"/>
-        <v>1.272</v>
-      </c>
-      <c r="G31" s="1">
+        <v>0.75600000000000001</v>
+      </c>
+      <c r="F31" s="20">
+        <f t="shared" si="36"/>
+        <v>1.3559999999999999</v>
+      </c>
+      <c r="G31" s="8">
         <f t="shared" si="0"/>
-        <v>0.67200000000000004</v>
-      </c>
-      <c r="H31" s="17">
+        <v>0.75600000000000001</v>
+      </c>
+      <c r="H31" s="18">
         <f t="shared" si="26"/>
         <v>3</v>
       </c>
-      <c r="I31" s="2">
+      <c r="I31" s="9">
         <v>3.1</v>
       </c>
-      <c r="J31" s="2">
+      <c r="J31" s="9">
         <v>5</v>
       </c>
-      <c r="K31" s="2">
+      <c r="K31" s="9">
         <v>0.3</v>
       </c>
-      <c r="L31" s="2">
-        <v>1</v>
-      </c>
-      <c r="M31" s="18">
-        <f t="shared" si="36"/>
-        <v>0.97199999999999986</v>
-      </c>
-      <c r="N31" s="1">
+      <c r="L31" s="9">
+        <v>1</v>
+      </c>
+      <c r="M31" s="8">
+        <f t="shared" si="5"/>
+        <v>1.26</v>
+      </c>
+      <c r="N31" s="8">
         <f t="shared" si="6"/>
-        <v>0.67200000000000004</v>
-      </c>
-      <c r="O31" s="18">
+        <v>0.75600000000000001</v>
+      </c>
+      <c r="O31" s="21">
         <f t="shared" si="37"/>
-        <v>1.3719999999999999</v>
+        <v>1.456</v>
       </c>
       <c r="P31" s="7">
         <v>7</v>
       </c>
-      <c r="Q31" s="1">
-        <f t="shared" si="1"/>
-        <v>0.97199999999999986</v>
-      </c>
-      <c r="R31" s="18">
-        <v>1.3</v>
-      </c>
-      <c r="S31" s="18">
-        <v>1.3</v>
+      <c r="Q31" s="7">
+        <v>1.26</v>
+      </c>
+      <c r="R31" s="21">
+        <v>0.8</v>
+      </c>
+      <c r="S31" s="21">
+        <v>0.8</v>
       </c>
       <c r="T31" s="8">
         <f t="shared" si="7"/>
         <v>0.49</v>
       </c>
-      <c r="U31" s="2">
+      <c r="U31" s="9">
         <v>0.44</v>
       </c>
-      <c r="V31" s="2">
+      <c r="V31" s="9">
         <v>2.16</v>
       </c>
-      <c r="W31" s="2">
+      <c r="W31" s="9">
         <v>0.85</v>
       </c>
-      <c r="X31" s="2">
+      <c r="X31" s="9">
         <v>3.66</v>
       </c>
-      <c r="Y31" s="17">
+      <c r="Y31" s="18">
         <v>2.25</v>
       </c>
       <c r="Z31" s="9">
         <v>1</v>
       </c>
-      <c r="AA31" s="18">
+      <c r="AA31" s="21">
         <f t="shared" si="38"/>
         <v>0.93300000000000005</v>
       </c>
       <c r="AB31" s="8">
+        <f t="shared" si="1"/>
+        <v>0.93300000000000005</v>
+      </c>
+      <c r="AC31" s="8">
         <f t="shared" si="2"/>
-        <v>0.93300000000000005</v>
-      </c>
-      <c r="AC31" s="8">
-        <f t="shared" si="3"/>
         <v>2.02</v>
       </c>
       <c r="AD31" s="12">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AE31" s="12">
         <v>22.85</v>
@@ -10313,22 +10286,20 @@
       <c r="AM31" s="9">
         <v>1</v>
       </c>
-      <c r="AN31" s="18">
+      <c r="AN31" s="21">
         <f t="shared" si="39"/>
         <v>0.39200000000000002</v>
       </c>
-      <c r="AO31" s="3">
+      <c r="AO31" s="20">
         <f t="shared" si="40"/>
         <v>2.0482</v>
       </c>
-      <c r="AP31">
+      <c r="AP31" s="7">
         <v>0</v>
       </c>
-      <c r="AQ31"/>
-      <c r="AR31"/>
       <c r="AS31" s="7">
-        <f t="shared" si="4"/>
-        <v>1.2666666666666666</v>
+        <f t="shared" si="3"/>
+        <v>1.2</v>
       </c>
       <c r="AT31" s="7">
         <v>28</v>
@@ -10345,46 +10316,46 @@
         <f t="shared" si="23"/>
         <v>0.40000000000000213</v>
       </c>
-      <c r="AY31">
+      <c r="AY31" s="7">
         <f t="shared" si="11"/>
         <v>2.02</v>
       </c>
-      <c r="AZ31">
+      <c r="AZ31" s="7">
         <f t="shared" si="12"/>
-        <v>2.82</v>
-      </c>
-      <c r="BA31">
+        <v>2.62</v>
+      </c>
+      <c r="BA31" s="7">
         <f t="shared" si="13"/>
-        <v>5.6963999999999997</v>
-      </c>
-      <c r="BB31">
+        <v>5.2924000000000007</v>
+      </c>
+      <c r="BB31" s="7">
         <f t="shared" si="14"/>
         <v>2.71</v>
       </c>
-      <c r="BC31">
+      <c r="BC31" s="7">
         <f t="shared" si="15"/>
-        <v>2.69</v>
-      </c>
-      <c r="BD31">
+        <v>2.6</v>
+      </c>
+      <c r="BD31" s="7">
         <v>17</v>
       </c>
-      <c r="BE31">
+      <c r="BE31" s="7">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="BG31">
+        <v>-0.1</v>
+      </c>
+      <c r="BG31" s="7">
         <f t="shared" si="17"/>
         <v>4.41</v>
       </c>
-      <c r="BH31">
+      <c r="BH31" s="7">
         <f t="shared" si="18"/>
         <v>28.85</v>
       </c>
-      <c r="BI31">
+      <c r="BI31" s="7">
         <f t="shared" si="19"/>
         <v>18.440000000000001</v>
       </c>
-      <c r="BJ31">
+      <c r="BJ31" s="7">
         <f t="shared" si="20"/>
         <v>24.44</v>
       </c>
@@ -10394,7 +10365,7 @@
         <v>70</v>
       </c>
       <c r="B32" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.49</v>
       </c>
       <c r="C32" s="7">
@@ -10403,95 +10374,94 @@
       <c r="D32" s="9">
         <v>0.65</v>
       </c>
-      <c r="E32" s="17">
-        <f t="shared" si="24"/>
-        <v>0.64959999999999996</v>
-      </c>
-      <c r="F32" s="3">
+      <c r="E32" s="18">
         <f t="shared" si="35"/>
-        <v>1.2496</v>
-      </c>
-      <c r="G32" s="1">
+        <v>0.75600000000000001</v>
+      </c>
+      <c r="F32" s="20">
+        <f t="shared" si="36"/>
+        <v>1.3559999999999999</v>
+      </c>
+      <c r="G32" s="8">
         <f t="shared" si="0"/>
-        <v>0.64959999999999996</v>
-      </c>
-      <c r="H32" s="17">
+        <v>0.75600000000000001</v>
+      </c>
+      <c r="H32" s="18">
         <f t="shared" si="26"/>
         <v>8.875</v>
       </c>
-      <c r="I32" s="2">
+      <c r="I32" s="9">
         <v>3.1</v>
       </c>
-      <c r="J32" s="2">
+      <c r="J32" s="9">
         <v>5</v>
       </c>
-      <c r="K32" s="2">
+      <c r="K32" s="9">
         <v>0.3</v>
       </c>
-      <c r="L32" s="2">
-        <v>1</v>
-      </c>
-      <c r="M32" s="18">
-        <f t="shared" si="36"/>
-        <v>0.94959999999999989</v>
-      </c>
-      <c r="N32" s="1">
+      <c r="L32" s="9">
+        <v>1</v>
+      </c>
+      <c r="M32" s="8">
+        <f t="shared" si="5"/>
+        <v>1.26</v>
+      </c>
+      <c r="N32" s="8">
         <f t="shared" si="6"/>
-        <v>0.64959999999999996</v>
-      </c>
-      <c r="O32" s="18">
+        <v>0.75600000000000001</v>
+      </c>
+      <c r="O32" s="21">
         <f t="shared" si="37"/>
-        <v>1.3495999999999999</v>
+        <v>1.456</v>
       </c>
       <c r="P32" s="7">
         <v>18.75</v>
       </c>
-      <c r="Q32" s="1">
-        <f t="shared" si="1"/>
-        <v>0.94959999999999989</v>
-      </c>
-      <c r="R32" s="18">
-        <v>1.3</v>
-      </c>
-      <c r="S32" s="18">
-        <v>1.3</v>
+      <c r="Q32" s="7">
+        <v>1.26</v>
+      </c>
+      <c r="R32" s="21">
+        <v>0.8</v>
+      </c>
+      <c r="S32" s="21">
+        <v>0.8</v>
       </c>
       <c r="T32" s="8">
         <f t="shared" si="7"/>
         <v>0.49</v>
       </c>
-      <c r="U32" s="2">
+      <c r="U32" s="9">
         <v>0.44</v>
       </c>
-      <c r="V32" s="2">
+      <c r="V32" s="9">
         <v>2.16</v>
       </c>
-      <c r="W32" s="2">
+      <c r="W32" s="9">
         <v>0.85</v>
       </c>
-      <c r="X32" s="2">
+      <c r="X32" s="9">
         <v>3.66</v>
       </c>
-      <c r="Y32" s="17">
+      <c r="Y32" s="18">
         <v>0.8</v>
       </c>
       <c r="Z32" s="9">
         <v>1</v>
       </c>
-      <c r="AA32" s="18">
+      <c r="AA32" s="21">
         <f t="shared" si="38"/>
         <v>0.90189999999999992</v>
       </c>
       <c r="AB32" s="8">
+        <f t="shared" si="1"/>
+        <v>0.90189999999999992</v>
+      </c>
+      <c r="AC32" s="8">
         <f t="shared" si="2"/>
-        <v>0.90189999999999992</v>
-      </c>
-      <c r="AC32" s="8">
-        <f t="shared" si="3"/>
         <v>1.92</v>
       </c>
       <c r="AD32" s="12">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AE32" s="12">
         <v>21.78</v>
@@ -10520,22 +10490,20 @@
       <c r="AM32" s="9">
         <v>1</v>
       </c>
-      <c r="AN32" s="18">
+      <c r="AN32" s="21">
         <f t="shared" si="39"/>
         <v>0.39200000000000002</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AO32" s="20">
         <f t="shared" si="40"/>
         <v>2.0482</v>
       </c>
-      <c r="AP32">
+      <c r="AP32" s="7">
         <v>0</v>
       </c>
-      <c r="AQ32"/>
-      <c r="AR32"/>
       <c r="AS32" s="7">
-        <f t="shared" si="4"/>
-        <v>1.2758620689655173</v>
+        <f t="shared" si="3"/>
+        <v>1.2068965517241379</v>
       </c>
       <c r="AT32" s="7">
         <v>29</v>
@@ -10552,46 +10520,46 @@
         <f t="shared" si="23"/>
         <v>0.40000000000000213</v>
       </c>
-      <c r="AY32">
+      <c r="AY32" s="7">
         <f t="shared" si="11"/>
         <v>1.92</v>
       </c>
-      <c r="AZ32">
+      <c r="AZ32" s="7">
         <f t="shared" si="12"/>
-        <v>2.72</v>
-      </c>
-      <c r="BA32">
+        <v>2.52</v>
+      </c>
+      <c r="BA32" s="7">
         <f t="shared" si="13"/>
-        <v>5.2224000000000004</v>
-      </c>
-      <c r="BB32">
+        <v>4.8384</v>
+      </c>
+      <c r="BB32" s="7">
         <f t="shared" si="14"/>
         <v>2.64</v>
       </c>
-      <c r="BC32">
+      <c r="BC32" s="7">
         <f t="shared" si="15"/>
-        <v>2.58</v>
-      </c>
-      <c r="BD32">
+        <v>2.48</v>
+      </c>
+      <c r="BD32" s="7">
         <v>17.2</v>
       </c>
-      <c r="BE32">
+      <c r="BE32" s="7">
         <f t="shared" si="16"/>
-        <v>-0.1</v>
-      </c>
-      <c r="BG32">
+        <v>-0.2</v>
+      </c>
+      <c r="BG32" s="7">
         <f t="shared" si="17"/>
         <v>2.96</v>
       </c>
-      <c r="BH32">
+      <c r="BH32" s="7">
         <f t="shared" si="18"/>
         <v>39.53</v>
       </c>
-      <c r="BI32">
+      <c r="BI32" s="7">
         <f t="shared" si="19"/>
         <v>18.82</v>
       </c>
-      <c r="BJ32">
+      <c r="BJ32" s="7">
         <f t="shared" si="20"/>
         <v>36.57</v>
       </c>
@@ -10601,7 +10569,7 @@
         <v>71</v>
       </c>
       <c r="B33" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.49</v>
       </c>
       <c r="C33" s="7">
@@ -10610,95 +10578,94 @@
       <c r="D33" s="9">
         <v>0.65</v>
       </c>
-      <c r="E33" s="17">
-        <f t="shared" si="24"/>
-        <v>0.63168000000000002</v>
-      </c>
-      <c r="F33" s="3">
+      <c r="E33" s="18">
         <f t="shared" si="35"/>
-        <v>1.2316799999999999</v>
-      </c>
-      <c r="G33" s="1">
+        <v>0.75600000000000001</v>
+      </c>
+      <c r="F33" s="20">
+        <f t="shared" si="36"/>
+        <v>1.3559999999999999</v>
+      </c>
+      <c r="G33" s="8">
         <f t="shared" si="0"/>
-        <v>0.63168000000000002</v>
-      </c>
-      <c r="H33" s="17">
+        <v>0.75600000000000001</v>
+      </c>
+      <c r="H33" s="18">
         <f t="shared" si="26"/>
         <v>3</v>
       </c>
-      <c r="I33" s="2">
+      <c r="I33" s="9">
         <v>3.1</v>
       </c>
-      <c r="J33" s="2">
+      <c r="J33" s="9">
         <v>5</v>
       </c>
-      <c r="K33" s="2">
+      <c r="K33" s="9">
         <v>0.3</v>
       </c>
-      <c r="L33" s="2">
-        <v>1</v>
-      </c>
-      <c r="M33" s="18">
-        <f t="shared" si="36"/>
-        <v>0.93167999999999995</v>
-      </c>
-      <c r="N33" s="1">
+      <c r="L33" s="9">
+        <v>1</v>
+      </c>
+      <c r="M33" s="8">
+        <f t="shared" si="5"/>
+        <v>1.26</v>
+      </c>
+      <c r="N33" s="8">
         <f t="shared" si="6"/>
-        <v>0.63168000000000002</v>
-      </c>
-      <c r="O33" s="18">
+        <v>0.75600000000000001</v>
+      </c>
+      <c r="O33" s="21">
         <f t="shared" si="37"/>
-        <v>1.33168</v>
+        <v>1.456</v>
       </c>
       <c r="P33" s="7">
         <v>7</v>
       </c>
-      <c r="Q33" s="1">
-        <f t="shared" si="1"/>
-        <v>0.93167999999999995</v>
-      </c>
-      <c r="R33" s="18">
-        <v>1.3</v>
-      </c>
-      <c r="S33" s="18">
-        <v>1.3</v>
+      <c r="Q33" s="7">
+        <v>1.26</v>
+      </c>
+      <c r="R33" s="21">
+        <v>0.8</v>
+      </c>
+      <c r="S33" s="21">
+        <v>0.8</v>
       </c>
       <c r="T33" s="8">
         <f t="shared" si="7"/>
         <v>0.49</v>
       </c>
-      <c r="U33" s="2">
+      <c r="U33" s="9">
         <v>0.44</v>
       </c>
-      <c r="V33" s="2">
+      <c r="V33" s="9">
         <v>2.16</v>
       </c>
-      <c r="W33" s="2">
+      <c r="W33" s="9">
         <v>0.85</v>
       </c>
-      <c r="X33" s="2">
+      <c r="X33" s="9">
         <v>3.66</v>
       </c>
-      <c r="Y33" s="17">
+      <c r="Y33" s="18">
         <v>2</v>
       </c>
       <c r="Z33" s="9">
         <v>1</v>
       </c>
-      <c r="AA33" s="18">
+      <c r="AA33" s="21">
         <f t="shared" si="38"/>
         <v>0.87701999999999991</v>
       </c>
       <c r="AB33" s="8">
+        <f t="shared" si="1"/>
+        <v>0.87701999999999991</v>
+      </c>
+      <c r="AC33" s="8">
         <f t="shared" si="2"/>
-        <v>0.87701999999999991</v>
-      </c>
-      <c r="AC33" s="8">
-        <f t="shared" si="3"/>
         <v>1.8399999999999999</v>
       </c>
       <c r="AD33" s="12">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="AE33" s="12">
         <v>20.77</v>
@@ -10727,22 +10694,20 @@
       <c r="AM33" s="9">
         <v>1</v>
       </c>
-      <c r="AN33" s="18">
+      <c r="AN33" s="21">
         <f t="shared" si="39"/>
         <v>0.39200000000000002</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AO33" s="20">
         <f t="shared" si="40"/>
         <v>2.0482</v>
       </c>
-      <c r="AP33">
+      <c r="AP33" s="7">
         <v>0</v>
       </c>
-      <c r="AQ33"/>
-      <c r="AR33"/>
       <c r="AS33" s="7">
-        <f t="shared" si="4"/>
-        <v>1.2943262411347518</v>
+        <f t="shared" si="3"/>
+        <v>1.2056737588652482</v>
       </c>
       <c r="AT33" s="7">
         <v>30</v>
@@ -10759,47 +10724,47 @@
         <f t="shared" si="23"/>
         <v>0.40000000000000213</v>
       </c>
-      <c r="AY33">
+      <c r="AY33" s="7">
         <f t="shared" si="11"/>
         <v>1.8399999999999999</v>
       </c>
-      <c r="AZ33">
+      <c r="AZ33" s="7">
         <f t="shared" si="12"/>
-        <v>2.67</v>
-      </c>
-      <c r="BA33">
+        <v>2.42</v>
+      </c>
+      <c r="BA33" s="7">
         <f t="shared" si="13"/>
-        <v>4.9127999999999998</v>
-      </c>
-      <c r="BB33">
+        <v>4.4527999999999999</v>
+      </c>
+      <c r="BB33" s="7">
         <f t="shared" si="14"/>
         <v>2.54</v>
       </c>
-      <c r="BC33">
+      <c r="BC33" s="7">
         <f t="shared" si="15"/>
-        <v>2.5</v>
-      </c>
-      <c r="BD33">
-        <f t="shared" si="32"/>
+        <v>2.38</v>
+      </c>
+      <c r="BD33" s="7">
+        <f t="shared" si="31"/>
         <v>17.2</v>
       </c>
-      <c r="BE33">
+      <c r="BE33" s="7">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="BG33">
+        <v>-0.2</v>
+      </c>
+      <c r="BG33" s="7">
         <f t="shared" si="17"/>
         <v>4.16</v>
       </c>
-      <c r="BH33">
+      <c r="BH33" s="7">
         <f t="shared" si="18"/>
         <v>26.77</v>
       </c>
-      <c r="BI33">
+      <c r="BI33" s="7">
         <f t="shared" si="19"/>
         <v>16.61</v>
       </c>
-      <c r="BJ33">
+      <c r="BJ33" s="7">
         <f t="shared" si="20"/>
         <v>22.61</v>
       </c>
@@ -10809,7 +10774,7 @@
         <v>72</v>
       </c>
       <c r="B34" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.49</v>
       </c>
       <c r="C34" s="7">
@@ -10818,95 +10783,94 @@
       <c r="D34" s="9">
         <v>0.65</v>
       </c>
-      <c r="E34" s="17">
-        <f t="shared" si="24"/>
-        <v>0.61152000000000006</v>
-      </c>
-      <c r="F34" s="3">
+      <c r="E34" s="18">
         <f t="shared" si="35"/>
-        <v>1.2115200000000002</v>
-      </c>
-      <c r="G34" s="1">
+        <v>0.75600000000000001</v>
+      </c>
+      <c r="F34" s="20">
+        <f t="shared" si="36"/>
+        <v>1.3559999999999999</v>
+      </c>
+      <c r="G34" s="8">
         <f t="shared" si="0"/>
-        <v>0.61152000000000006</v>
-      </c>
-      <c r="H34" s="17">
+        <v>0.75600000000000001</v>
+      </c>
+      <c r="H34" s="18">
         <f t="shared" si="26"/>
         <v>8.875</v>
       </c>
-      <c r="I34" s="2">
+      <c r="I34" s="9">
         <v>3.1</v>
       </c>
-      <c r="J34" s="2">
+      <c r="J34" s="9">
         <v>5</v>
       </c>
-      <c r="K34" s="2">
+      <c r="K34" s="9">
         <v>0.3</v>
       </c>
-      <c r="L34" s="2">
-        <v>1</v>
-      </c>
-      <c r="M34" s="18">
-        <f t="shared" si="36"/>
-        <v>0.91152</v>
-      </c>
-      <c r="N34" s="1">
+      <c r="L34" s="9">
+        <v>1</v>
+      </c>
+      <c r="M34" s="8">
+        <f t="shared" si="5"/>
+        <v>1.26</v>
+      </c>
+      <c r="N34" s="8">
         <f t="shared" si="6"/>
-        <v>0.61152000000000006</v>
-      </c>
-      <c r="O34" s="18">
+        <v>0.75600000000000001</v>
+      </c>
+      <c r="O34" s="21">
         <f t="shared" si="37"/>
-        <v>1.31152</v>
+        <v>1.456</v>
       </c>
       <c r="P34" s="7">
         <v>18.75</v>
       </c>
-      <c r="Q34" s="1">
-        <f t="shared" si="1"/>
-        <v>0.91152</v>
-      </c>
-      <c r="R34" s="18">
-        <v>1.3</v>
-      </c>
-      <c r="S34" s="18">
-        <v>1.3</v>
+      <c r="Q34" s="7">
+        <v>1.26</v>
+      </c>
+      <c r="R34" s="21">
+        <v>0.8</v>
+      </c>
+      <c r="S34" s="21">
+        <v>0.8</v>
       </c>
       <c r="T34" s="8">
         <f t="shared" si="7"/>
         <v>0.49</v>
       </c>
-      <c r="U34" s="2">
+      <c r="U34" s="9">
         <v>0.44</v>
       </c>
-      <c r="V34" s="2">
+      <c r="V34" s="9">
         <v>2.16</v>
       </c>
-      <c r="W34" s="2">
+      <c r="W34" s="9">
         <v>0.85</v>
       </c>
-      <c r="X34" s="2">
+      <c r="X34" s="9">
         <v>3.66</v>
       </c>
-      <c r="Y34" s="17">
+      <c r="Y34" s="18">
         <v>0.5</v>
       </c>
       <c r="Z34" s="9">
         <v>1</v>
       </c>
-      <c r="AA34" s="18">
+      <c r="AA34" s="21">
         <f t="shared" si="38"/>
         <v>0.84902999999999995</v>
       </c>
       <c r="AB34" s="8">
+        <f t="shared" si="1"/>
+        <v>0.84902999999999995</v>
+      </c>
+      <c r="AC34" s="8">
         <f t="shared" si="2"/>
-        <v>0.84902999999999995</v>
-      </c>
-      <c r="AC34" s="8">
-        <f t="shared" si="3"/>
         <v>1.75</v>
       </c>
       <c r="AD34" s="12">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="AE34" s="12">
         <v>19.82</v>
@@ -10935,22 +10899,20 @@
       <c r="AM34" s="9">
         <v>1</v>
       </c>
-      <c r="AN34" s="18">
+      <c r="AN34" s="21">
         <f t="shared" si="39"/>
         <v>0.39200000000000002</v>
       </c>
-      <c r="AO34" s="3">
+      <c r="AO34" s="20">
         <f t="shared" si="40"/>
         <v>2.0482</v>
       </c>
-      <c r="AP34">
+      <c r="AP34" s="7">
         <v>0</v>
       </c>
-      <c r="AQ34"/>
-      <c r="AR34"/>
       <c r="AS34" s="7">
-        <f t="shared" si="4"/>
-        <v>1.3003663003663004</v>
+        <f t="shared" si="3"/>
+        <v>1.2087912087912087</v>
       </c>
       <c r="AT34" s="7">
         <v>31</v>
@@ -10967,47 +10929,47 @@
         <f t="shared" si="23"/>
         <v>0.40000000000000213</v>
       </c>
-      <c r="AY34">
+      <c r="AY34" s="7">
         <f t="shared" si="11"/>
         <v>1.75</v>
       </c>
-      <c r="AZ34">
+      <c r="AZ34" s="7">
         <f t="shared" si="12"/>
-        <v>2.57</v>
-      </c>
-      <c r="BA34">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="BA34" s="7">
         <f t="shared" si="13"/>
-        <v>4.4974999999999996</v>
-      </c>
-      <c r="BB34">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="BB34" s="7">
         <f t="shared" si="14"/>
         <v>2.44</v>
       </c>
-      <c r="BC34">
+      <c r="BC34" s="7">
         <f t="shared" si="15"/>
-        <v>2.39</v>
-      </c>
-      <c r="BD34">
-        <f t="shared" si="32"/>
+        <v>2.27</v>
+      </c>
+      <c r="BD34" s="7">
+        <f t="shared" si="31"/>
         <v>17.2</v>
       </c>
-      <c r="BE34">
+      <c r="BE34" s="7">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="BG34">
+        <v>-0.2</v>
+      </c>
+      <c r="BG34" s="7">
         <f t="shared" si="17"/>
         <v>2.66</v>
       </c>
-      <c r="BH34">
+      <c r="BH34" s="7">
         <f t="shared" si="18"/>
         <v>37.57</v>
       </c>
-      <c r="BI34">
+      <c r="BI34" s="7">
         <f t="shared" si="19"/>
         <v>17.16</v>
       </c>
-      <c r="BJ34">
+      <c r="BJ34" s="7">
         <f t="shared" si="20"/>
         <v>34.909999999999997</v>
       </c>
@@ -11018,44 +10980,17 @@
       <c r="V35" s="2"/>
       <c r="W35" s="2"/>
       <c r="X35" s="2"/>
-      <c r="Y35" s="17"/>
+      <c r="Y35" s="15"/>
       <c r="Z35" s="2"/>
-      <c r="AB35" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC35" s="1">
-        <f t="shared" si="3"/>
-        <v>-0.98</v>
-      </c>
-      <c r="AG35" s="2">
-        <v>0.49</v>
-      </c>
-      <c r="AH35" s="2">
-        <v>1.25</v>
-      </c>
-      <c r="AI35" s="2">
-        <v>0.7</v>
-      </c>
-      <c r="AJ35" s="2">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="AK35" s="2">
-        <v>1</v>
-      </c>
-      <c r="AL35" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="AM35" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS35" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AT35">
-        <v>32</v>
-      </c>
+      <c r="AB35" s="1"/>
+      <c r="AC35" s="1"/>
+      <c r="AG35" s="2"/>
+      <c r="AH35" s="2"/>
+      <c r="AI35" s="2"/>
+      <c r="AJ35" s="2"/>
+      <c r="AK35" s="2"/>
+      <c r="AL35" s="2"/>
+      <c r="AM35" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
